--- a/irf/irf/Paper IRFs.xlsx
+++ b/irf/irf/Paper IRFs.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="28">
   <si>
     <t>t</t>
   </si>
@@ -106,6 +106,12 @@
   </si>
   <si>
     <t>2025-12-18T15:29:26.11</t>
+  </si>
+  <si>
+    <t>2026-02-10T13:49:09.578</t>
+  </si>
+  <si>
+    <t>2026-02-10T13:51:34.338</t>
   </si>
 </sst>
 </file>
@@ -501,13 +507,13 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
       </c>
       <c r="K1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -533,7 +539,7 @@
         <v>2.5793795815169456</v>
       </c>
       <c r="H2">
-        <v>-6.355787355569827e-15</v>
+        <v>-1.0776287571287195</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -559,7 +565,7 @@
         <v>1.4953394328181018</v>
       </c>
       <c r="H3">
-        <v>-1.6480533826595375e-15</v>
+        <v>-1.0901798523912853</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -585,7 +591,7 @@
         <v>1.1447890872423834</v>
       </c>
       <c r="H4">
-        <v>-2.081899328946869e-15</v>
+        <v>-1.1050722210876067</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -611,7 +617,7 @@
         <v>0.9056919935333063</v>
       </c>
       <c r="H5">
-        <v>-1.6504474741377359e-15</v>
+        <v>-1.1161558581396847</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -637,7 +643,7 @@
         <v>0.7319914235132261</v>
       </c>
       <c r="H6">
-        <v>-1.0682857281982889e-15</v>
+        <v>-1.124275171477677</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -663,7 +669,7 @@
         <v>0.5973427245187732</v>
       </c>
       <c r="H7">
-        <v>-3.351537685000903e-16</v>
+        <v>-1.1300125312110396</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -689,7 +695,7 @@
         <v>-0.1711148877063895</v>
       </c>
       <c r="H8">
-        <v>2.1604510794098216e-15</v>
+        <v>-0.8589162460761607</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -715,7 +721,7 @@
         <v>-0.48020139575093257</v>
       </c>
       <c r="H9">
-        <v>3.1695275586680018e-15</v>
+        <v>-0.6527917857811548</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -741,7 +747,7 @@
         <v>-0.5768324684811983</v>
       </c>
       <c r="H10">
-        <v>4.25340167117954e-15</v>
+        <v>-0.518379630721563</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -767,7 +773,7 @@
         <v>-0.5871768624011784</v>
       </c>
       <c r="H11">
-        <v>5.334502974659489e-15</v>
+        <v>-0.4302230951401023</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -793,7 +799,7 @@
         <v>-0.5655516135502099</v>
       </c>
       <c r="H12">
-        <v>6.374359255433715e-15</v>
+        <v>-0.37025101988486603</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -819,7 +825,7 @@
         <v>-0.5334958471292568</v>
       </c>
       <c r="H13">
-        <v>7.348022928166114e-15</v>
+        <v>-0.32798101284319414</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -845,7 +851,7 @@
         <v>-0.499029394560659</v>
       </c>
       <c r="H14">
-        <v>8.238600942484928e-15</v>
+        <v>-0.29728557226249874</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -871,7 +877,7 @@
         <v>-0.46490712897908937</v>
       </c>
       <c r="H15">
-        <v>9.035400836782848e-15</v>
+        <v>-0.27435118561052385</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -897,7 +903,7 @@
         <v>-0.43193786324030503</v>
       </c>
       <c r="H16">
-        <v>9.732723232297122e-15</v>
+        <v>-0.2566500422596416</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -923,7 +929,7 @@
         <v>-0.4002656212734461</v>
       </c>
       <c r="H17">
-        <v>1.0328839915493663e-14</v>
+        <v>-0.24243423152081073</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -949,7 +955,7 @@
         <v>-0.3698442820958281</v>
       </c>
       <c r="H18">
-        <v>1.0825107183252934e-14</v>
+        <v>-0.23047147775076154</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -975,7 +981,7 @@
         <v>-0.34060187362750494</v>
       </c>
       <c r="H19">
-        <v>1.1225210005760732e-14</v>
+        <v>-0.2198922430955447</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1001,7 +1007,7 @@
         <v>-0.31248901919794614</v>
       </c>
       <c r="H20">
-        <v>1.1534528912238757e-14</v>
+        <v>-0.21009142183175822</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1027,7 +1033,7 @@
         <v>-0.2854862761513888</v>
       </c>
       <c r="H21">
-        <v>1.175961705074767e-14</v>
+        <v>-0.20065974270055495</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1053,7 +1059,7 @@
         <v>-0.259598482828578</v>
       </c>
       <c r="H22">
-        <v>1.1907773598333052e-14</v>
+        <v>-0.19133336646627905</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1079,7 +1085,7 @@
         <v>-0.23484632667295546</v>
       </c>
       <c r="H23">
-        <v>1.198670019418404e-14</v>
+        <v>-0.1819558083010112</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1105,7 +1111,7 @@
         <v>-0.2112585709882856</v>
       </c>
       <c r="H24">
-        <v>1.2004228239577581e-14</v>
+        <v>-0.1724488035363658</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1131,7 +1137,7 @@
         <v>-0.18886587385927223</v>
       </c>
       <c r="H25">
-        <v>1.1968106244614112e-14</v>
+        <v>-0.16278992968392045</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1157,7 +1163,7 @@
         <v>-0.1676962516278695</v>
       </c>
       <c r="H26">
-        <v>1.188583770482846e-14</v>
+        <v>-0.15299544177405125</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1183,7 +1189,7 @@
         <v>-0.14777196505869047</v>
       </c>
       <c r="H27">
-        <v>1.1764561194408282e-14</v>
+        <v>-0.14310717159366784</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1209,7 +1215,7 @@
         <v>-0.12910755184239306</v>
       </c>
       <c r="H28">
-        <v>1.1610965451139909e-14</v>
+        <v>-0.1331826081151621</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1235,7 +1241,7 @@
         <v>-0.11170874851067299</v>
       </c>
       <c r="H29">
-        <v>1.1431233203186396e-14</v>
+        <v>-0.12328747034328749</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1261,7 +1267,7 @@
         <v>-0.09557208436693596</v>
       </c>
       <c r="H30">
-        <v>1.1231008356708719e-14</v>
+        <v>-0.11349023077698193</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1287,7 +1293,7 @@
         <v>-0.08068497073909373</v>
       </c>
       <c r="H31">
-        <v>1.1015381934708296e-14</v>
+        <v>-0.10385816158716517</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1313,7 +1319,7 @@
         <v>-0.06702614481783115</v>
       </c>
       <c r="H32">
-        <v>1.0788892839714788e-14</v>
+        <v>-0.09445456493197307</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1339,7 +1345,7 @@
         <v>-0.05456635734818738</v>
       </c>
       <c r="H33">
-        <v>1.0555540114031386e-14</v>
+        <v>-0.08533691930916376</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1365,7 +1371,7 @@
         <v>-0.0432692178717905</v>
       </c>
       <c r="H34">
-        <v>1.031880389865131e-14</v>
+        <v>-0.07655572964759738</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1391,7 +1397,7 @@
         <v>-0.03309213088256757</v>
       </c>
       <c r="H35">
-        <v>1.0081672752685079e-14</v>
+        <v>-0.0681539131143121</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -1417,7 +1423,7 @@
         <v>-0.02398727199936468</v>
       </c>
       <c r="H36">
-        <v>9.84667539576943e-15</v>
+        <v>-0.06016658779289161</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1443,7 +1449,7 @@
         <v>-0.015902565816211744</v>
       </c>
       <c r="H37">
-        <v>9.61591528263049e-15</v>
+        <v>-0.0526211593726106</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -1469,7 +1475,7 @@
         <v>-0.00878263708310384</v>
       </c>
       <c r="H38">
-        <v>9.391106717500169e-15</v>
+        <v>-0.04553762326926426</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -1495,7 +1501,7 @@
         <v>-0.002569714800012668</v>
       </c>
       <c r="H39">
-        <v>9.173611471779087e-15</v>
+        <v>-0.03892901735440936</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -1521,7 +1527,7 @@
         <v>0.002795524920532755</v>
       </c>
       <c r="H40">
-        <v>8.964475086133226e-15</v>
+        <v>-0.03280197462915188</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -1547,7 +1553,7 @@
         <v>0.007373186426717637</v>
       </c>
       <c r="H41">
-        <v>8.764462222628797e-15</v>
+        <v>-0.02715733647615541</v>
       </c>
     </row>
   </sheetData>
@@ -1571,19 +1577,19 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F1" t="s">
         <v>20</v>
       </c>
       <c r="G1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="H1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
@@ -1597,16 +1603,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>-3.4528186345588288</v>
+        <v>8.102500031716193</v>
       </c>
       <c r="C2">
         <v>0.0</v>
       </c>
       <c r="D2">
-        <v>-1.0000000000000002</v>
+        <v>-1.0</v>
       </c>
       <c r="E2">
-        <v>-0.6724381448767072</v>
+        <v>0.3002694365653483</v>
       </c>
       <c r="F2">
         <v>-1.8240941779797443e-14</v>
@@ -1623,7 +1629,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>-2.2470266251559217</v>
+        <v>3.7924900644128168</v>
       </c>
       <c r="C3">
         <v>0.0</v>
@@ -1632,7 +1638,7 @@
         <v>-1.0</v>
       </c>
       <c r="E3">
-        <v>-0.6754920439440941</v>
+        <v>0.34132427283477856</v>
       </c>
       <c r="F3">
         <v>-1.815767595640473e-14</v>
@@ -1649,16 +1655,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>-1.620532378859584</v>
+        <v>1.535682253088882</v>
       </c>
       <c r="C4">
         <v>0.0</v>
       </c>
       <c r="D4">
-        <v>-1.0</v>
+        <v>-1.0000000000000002</v>
       </c>
       <c r="E4">
-        <v>-0.6914267332173135</v>
+        <v>0.3262395395059982</v>
       </c>
       <c r="F4">
         <v>-1.7990016981340348e-14</v>
@@ -1675,7 +1681,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>-1.2672896844330825</v>
+        <v>0.314417515476746</v>
       </c>
       <c r="C5">
         <v>0.0</v>
@@ -1684,7 +1690,7 @@
         <v>-1.0</v>
       </c>
       <c r="E5">
-        <v>-0.7126190796009902</v>
+        <v>0.297172637639562</v>
       </c>
       <c r="F5">
         <v>-1.7750026373046594e-14</v>
@@ -1701,16 +1707,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>-1.0342703989673754</v>
+        <v>-0.3714566512920629</v>
       </c>
       <c r="C6">
         <v>0.0</v>
       </c>
       <c r="D6">
-        <v>-0.9999999999999999</v>
+        <v>-1.0000000000000002</v>
       </c>
       <c r="E6">
-        <v>-0.7369490309361146</v>
+        <v>0.26450237048056346</v>
       </c>
       <c r="F6">
         <v>-1.7449311279723872e-14</v>
@@ -1727,7 +1733,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>-0.8446534793547582</v>
+        <v>-0.7682647916323465</v>
       </c>
       <c r="C7">
         <v>0.0</v>
@@ -1736,7 +1742,7 @@
         <v>-1.0</v>
       </c>
       <c r="E7">
-        <v>-0.7634137716033613</v>
+        <v>0.23168373759607122</v>
       </c>
       <c r="F7">
         <v>-1.7098845668544484e-14</v>
@@ -1753,16 +1759,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>-0.6587311709284003</v>
+        <v>-0.9983762771240359</v>
       </c>
       <c r="C8">
         <v>0.0</v>
       </c>
       <c r="D8">
-        <v>1.0018733440900038</v>
+        <v>-0.8228559440075205</v>
       </c>
       <c r="E8">
-        <v>1.2106152491219866</v>
+        <v>0.20029060488665273</v>
       </c>
       <c r="F8">
         <v>-1.6708846025861055e-14</v>
@@ -1779,16 +1785,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.24680905953848103</v>
+        <v>-1.0615234494165005</v>
       </c>
       <c r="C9">
         <v>0.0</v>
       </c>
       <c r="D9">
-        <v>1.0184154340610958</v>
+        <v>-0.6802281125838083</v>
       </c>
       <c r="E9">
-        <v>1.1997204343437553</v>
+        <v>0.17117303992476582</v>
       </c>
       <c r="F9">
         <v>-1.628869161461582e-14</v>
@@ -1805,16 +1811,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.7263675921425222</v>
+        <v>-1.0428589933721009</v>
       </c>
       <c r="C10">
         <v>0.0</v>
       </c>
       <c r="D10">
-        <v>0.8156573832361733</v>
+        <v>-0.5839658177105793</v>
       </c>
       <c r="E10">
-        <v>0.9711631474977384</v>
+        <v>0.14469354968982942</v>
       </c>
       <c r="F10">
         <v>-1.5846880766101665e-14</v>
@@ -1831,16 +1837,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.8982855718353012</v>
+        <v>-0.9921377386601233</v>
       </c>
       <c r="C11">
         <v>0.0</v>
       </c>
       <c r="D11">
-        <v>0.6586264335291566</v>
+        <v>-0.5204572812941362</v>
       </c>
       <c r="E11">
-        <v>0.7905470542901465</v>
+        <v>0.1209314480216968</v>
       </c>
       <c r="F11">
         <v>-1.5391015939674246e-14</v>
@@ -1857,16 +1863,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.9255227013030343</v>
+        <v>-0.9313171317033377</v>
       </c>
       <c r="C12">
         <v>0.0</v>
       </c>
       <c r="D12">
-        <v>0.5570036467058181</v>
+        <v>-0.4780823352039272</v>
       </c>
       <c r="E12">
-        <v>0.6677310999777817</v>
+        <v>0.0998197529172179</v>
       </c>
       <c r="F12">
         <v>-1.492781138475873e-14</v>
@@ -1883,16 +1889,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.8946469763358686</v>
+        <v>-0.8688979012157303</v>
       </c>
       <c r="C13">
         <v>0.0</v>
       </c>
       <c r="D13">
-        <v>0.49186589094678723</v>
+        <v>-0.44914320705740507</v>
       </c>
       <c r="E13">
-        <v>0.5837699848463117</v>
+        <v>0.08122018743975548</v>
       </c>
       <c r="F13">
         <v>-1.4463118201713377e-14</v>
@@ -1909,16 +1915,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.8432769678272334</v>
+        <v>-0.8077995380727517</v>
       </c>
       <c r="C14">
         <v>0.0</v>
       </c>
       <c r="D14">
-        <v>0.4488642256802755</v>
+        <v>-0.42862347099199605</v>
       </c>
       <c r="E14">
-        <v>0.5242002936670479</v>
+        <v>0.06496131838760792</v>
       </c>
       <c r="F14">
         <v>-1.4001962437076097e-14</v>
@@ -1935,16 +1941,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.7862841894323267</v>
+        <v>-0.7488403124163857</v>
       </c>
       <c r="C15">
         <v>0.0</v>
       </c>
       <c r="D15">
-        <v>0.4193036627477743</v>
+        <v>-0.41317369462819337</v>
       </c>
       <c r="E15">
-        <v>0.48017247947465613</v>
+        <v>0.05085802283127187</v>
       </c>
       <c r="F15">
         <v>-1.3548592577989773e-14</v>
@@ -1961,16 +1967,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.7291287172948163</v>
+        <v>-0.6921339810602081</v>
       </c>
       <c r="C16">
         <v>0.0</v>
       </c>
       <c r="D16">
-        <v>0.39794057515986725</v>
+        <v>-0.4005166921982795</v>
       </c>
       <c r="E16">
-        <v>0.44627304444263516</v>
+        <v>0.03872194353595661</v>
       </c>
       <c r="F16">
         <v>-1.3106533442287815e-14</v>
@@ -1987,16 +1993,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.6736313551308237</v>
+        <v>-0.6376112097334082</v>
       </c>
       <c r="C17">
         <v>0.0</v>
       </c>
       <c r="D17">
-        <v>0.3814757938431972</v>
+        <v>-0.38910425750694966</v>
       </c>
       <c r="E17">
-        <v>0.41902976580950124</v>
+        <v>0.028367498022029917</v>
       </c>
       <c r="F17">
         <v>-1.2678644005712723e-14</v>
@@ -2013,16 +2019,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.6202949310831237</v>
+        <v>-0.5851956049269981</v>
       </c>
       <c r="C18">
         <v>0.0</v>
       </c>
       <c r="D18">
-        <v>0.36775375988493847</v>
+        <v>-0.3779051514818019</v>
       </c>
       <c r="E18">
-        <v>0.3961171599492469</v>
+        <v>0.019615529123016506</v>
       </c>
       <c r="F18">
         <v>-1.2267177175878604e-14</v>
@@ -2039,16 +2045,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.5691926844693418</v>
+        <v>-0.5348503251242684</v>
       </c>
       <c r="C19">
         <v>0.0</v>
       </c>
       <c r="D19">
-        <v>0.35534378731108784</v>
+        <v>-0.36626309791247713</v>
       </c>
       <c r="E19">
-        <v>0.375941241585227</v>
+        <v>0.012295576831416185</v>
       </c>
       <c r="F19">
         <v>-1.1873839922785759e-14</v>
@@ -2065,16 +2071,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.5202897774842149</v>
+        <v>-0.4865796943485873</v>
       </c>
       <c r="C20">
         <v>0.0</v>
       </c>
       <c r="D20">
-        <v>0.3433055700353413</v>
+        <v>-0.35379549635816077</v>
       </c>
       <c r="E20">
-        <v>0.3574070387942579</v>
+        <v>0.006247266563694634</v>
       </c>
       <c r="F20">
         <v>-1.1499852516027993e-14</v>
@@ -2091,16 +2097,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.473548341248213</v>
+        <v>-0.4404176585643645</v>
       </c>
       <c r="C21">
         <v>0.0</v>
       </c>
       <c r="D21">
-        <v>0.3310444218815106</v>
+        <v>-0.34031834310639586</v>
       </c>
       <c r="E21">
-        <v>0.33977496936123824</v>
+        <v>0.00132109198404053</v>
       </c>
       <c r="F21">
         <v>-1.1146005906605964e-14</v>
@@ -2117,16 +2123,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.4289533027672345</v>
+        <v>-0.39641449189423267</v>
       </c>
       <c r="C22">
         <v>0.0</v>
       </c>
       <c r="D22">
-        <v>0.31821371106204765</v>
+        <v>-0.32578948348292586</v>
       </c>
       <c r="E22">
-        <v>0.3225638534647222</v>
+        <v>-0.0026212333665151647</v>
       </c>
       <c r="F22">
         <v>-1.0812716533065178e-14</v>
@@ -2143,16 +2149,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.3865114381510728</v>
+        <v>-0.35462541134890396</v>
       </c>
       <c r="C23">
         <v>0.0</v>
       </c>
       <c r="D23">
-        <v>0.3046449940301095</v>
+        <v>-0.31026540410425607</v>
       </c>
       <c r="E23">
-        <v>0.3054812462371977</v>
+        <v>-0.0057067365597778365</v>
       </c>
       <c r="F23">
         <v>-1.0500078033443117e-14</v>
@@ -2169,16 +2175,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.34624309946252885</v>
+        <v>-0.3151019201212323</v>
       </c>
       <c r="C24">
         <v>0.0</v>
       </c>
       <c r="D24">
-        <v>0.2902962371523612</v>
+        <v>-0.2938683385363192</v>
       </c>
       <c r="E24">
-        <v>0.2883715920369886</v>
+        <v>-0.008051371764514897</v>
       </c>
       <c r="F24">
         <v>-1.0207909511547629e-14</v>
@@ -2195,16 +2201,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.30817343957405235</v>
+        <v>-0.2778857293158672</v>
       </c>
       <c r="C25">
         <v>0.0</v>
       </c>
       <c r="D25">
-        <v>0.2752128316575503</v>
+        <v>-0.2767613519160847</v>
       </c>
       <c r="E25">
-        <v>0.2711769839938415</v>
+        <v>-0.009760368411796552</v>
       </c>
       <c r="F25">
         <v>-9.935800143135421e-15</v>
@@ -2221,16 +2227,16 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>0.2723252291489793</v>
+        <v>-0.24300483263028988</v>
       </c>
       <c r="C26">
         <v>0.0</v>
       </c>
       <c r="D26">
-        <v>0.2594981156297165</v>
+        <v>-0.2591296411091694</v>
       </c>
       <c r="E26">
-        <v>0.25390729921700655</v>
+        <v>-0.010928692249962738</v>
       </c>
       <c r="F26">
         <v>-9.683150018825644e-15</v>
@@ -2247,16 +2253,16 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0.2387136511414243</v>
+        <v>-0.2104712802923241</v>
       </c>
       <c r="C27">
         <v>0.0</v>
       </c>
       <c r="D27">
-        <v>0.24329115253479333</v>
+        <v>-0.24116668668256175</v>
       </c>
       <c r="E27">
-        <v>0.2366175013392508</v>
+        <v>-0.011641582036532809</v>
       </c>
       <c r="F27">
         <v>-9.449207209792284e-15</v>
@@ -2273,16 +2279,16 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0.20734289002415335</v>
+        <v>-0.18028024939896087</v>
       </c>
       <c r="C28">
         <v>0.0</v>
       </c>
       <c r="D28">
-        <v>0.22675012020918134</v>
+        <v>-0.22306418926392452</v>
       </c>
       <c r="E28">
-        <v>0.2193904961467077</v>
+        <v>-0.011975133399397053</v>
       </c>
       <c r="F28">
         <v>-9.233101112711743e-15</v>
@@ -2299,16 +2305,16 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.17820418491658996</v>
+        <v>-0.15241007639848064</v>
       </c>
       <c r="C29">
         <v>0.0</v>
       </c>
       <c r="D29">
-        <v>0.2100400594585057</v>
+        <v>-0.20500494976223432</v>
       </c>
       <c r="E29">
-        <v>0.20232431352900054</v>
+        <v>-0.011996908170405237</v>
       </c>
       <c r="F29">
         <v>-9.033872184976306e-15</v>
@@ -2325,16 +2331,16 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>0.15127501466405358</v>
+        <v>-0.12682298287541582</v>
       </c>
       <c r="C30">
         <v>0.0</v>
       </c>
       <c r="D30">
-        <v>0.19332401223674595</v>
+        <v>-0.18715802973435192</v>
       </c>
       <c r="E30">
-        <v>0.18552266391158495</v>
+        <v>-0.011766552744396662</v>
       </c>
       <c r="F30">
         <v>-8.850498222334385e-15</v>
@@ -2351,16 +2357,16 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.1265191267727281</v>
+        <v>-0.10346628204886194</v>
       </c>
       <c r="C31">
         <v>0.0</v>
       </c>
       <c r="D31">
-        <v>0.1767567894266234</v>
+        <v>-0.16967566721733235</v>
       </c>
       <c r="E31">
-        <v>0.1690881228443292</v>
+        <v>-0.01133641309897367</v>
       </c>
       <c r="F31">
         <v>-8.681917361073525e-15</v>
@@ -2377,16 +2383,16 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>0.10388717416473889</v>
+        <v>-0.0822738998007228</v>
       </c>
       <c r="C32">
         <v>0.0</v>
       </c>
       <c r="D32">
-        <v>0.16048076990975907</v>
+        <v>-0.1526915332110001</v>
       </c>
       <c r="E32">
-        <v>0.15311735557648556</v>
+        <v>-0.010752137288434079</v>
       </c>
       <c r="F32">
         <v>-8.527048007516854e-15</v>
@@ -2403,16 +2409,16 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.08331777173485576</v>
+        <v>-0.06316808163341717</v>
       </c>
       <c r="C33">
         <v>0.0</v>
       </c>
       <c r="D33">
-        <v>0.14462325893598377</v>
+        <v>-0.13632000105110623</v>
       </c>
       <c r="E33">
-        <v>0.13769791704712447</v>
+        <v>-0.010053258700306674</v>
       </c>
       <c r="F33">
         <v>-8.384805910596488e-15</v>
@@ -2429,16 +2435,16 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>0.06473882543354056</v>
+        <v>-0.046061187124972265</v>
       </c>
       <c r="C34">
         <v>0.0</v>
       </c>
       <c r="D34">
-        <v>0.12929503328462028</v>
+        <v>-0.12065617001690093</v>
       </c>
       <c r="E34">
-        <v>0.12290626009298944</v>
+        <v>-0.009273755289992894</v>
       </c>
       <c r="F34">
         <v>-8.254118600003628e-15</v>
@@ -2455,16 +2461,16 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0.04806901999222726</v>
+        <v>-0.03085749755064561</v>
       </c>
       <c r="C35">
         <v>0.0</v>
       </c>
       <c r="D35">
-        <v>0.1145897793898969</v>
+        <v>-0.10577643943910728</v>
       </c>
       <c r="E35">
-        <v>0.10880666171970085</v>
+        <v>-0.008442581508415481</v>
       </c>
       <c r="F35">
         <v>-8.133937414100203e-15</v>
@@ -2481,16 +2487,16 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>0.03321937833689396</v>
+        <v>-0.01745498153316079</v>
       </c>
       <c r="C36">
         <v>0.0</v>
       </c>
       <c r="D36">
-        <v>0.10058419297843774</v>
+        <v>-0.09173947326853786</v>
       </c>
       <c r="E36">
-        <v>0.09545083839271665</v>
+        <v>-0.007584170802837485</v>
       </c>
       <c r="F36">
         <v>-8.023247339437343e-15</v>
@@ -2507,16 +2513,16 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.020094827277761112</v>
+        <v>-0.005746978823673742</v>
       </c>
       <c r="C37">
         <v>0.0</v>
       </c>
       <c r="D37">
-        <v>0.08733855829167206</v>
+        <v>-0.07858742985557152</v>
       </c>
       <c r="E37">
-        <v>0.08287806985257444</v>
+        <v>-0.006718907474924289</v>
       </c>
       <c r="F37">
         <v>-7.92107487823219e-15</v>
@@ -2533,16 +2539,16 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0.00859572120902587</v>
+        <v>0.0043762256228740805</v>
       </c>
       <c r="C38">
         <v>0.0</v>
       </c>
       <c r="D38">
-        <v>0.07489766432802991</v>
+        <v>-0.06634735940908407</v>
       </c>
       <c r="E38">
-        <v>0.07111568956938276</v>
+        <v>-0.0058635673793306885</v>
       </c>
       <c r="F38">
         <v>-7.826494152242911e-15</v>
@@ -2559,16 +2565,16 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>-0.0013807108535275074</v>
+        <v>0.013025955608796925</v>
       </c>
       <c r="C39">
         <v>0.0</v>
       </c>
       <c r="D39">
-        <v>0.06329194684754574</v>
+        <v>-0.05503269369781794</v>
       </c>
       <c r="E39">
-        <v>0.06017983068364183</v>
+        <v>-0.0050317274847183355</v>
       </c>
       <c r="F39">
         <v>-7.738631441769198e-15</v>
@@ -2585,16 +2591,16 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>-0.009939018834928658</v>
+        <v>0.020313836572422195</v>
       </c>
       <c r="C40">
         <v>0.0</v>
       </c>
       <c r="D40">
-        <v>0.05253876979570426</v>
+        <v>-0.04464477017242626</v>
       </c>
       <c r="E40">
-        <v>0.050076340756670765</v>
+        <v>-0.004234144731499447</v>
       </c>
       <c r="F40">
         <v>-7.656668347508482e-15</v>
@@ -2611,16 +2617,16 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>-0.017184301266061693</v>
+        <v>0.026350632471733648</v>
       </c>
       <c r="C41">
         <v>0.0</v>
       </c>
       <c r="D41">
-        <v>0.04264377963499199</v>
+        <v>-0.035174346728825516</v>
       </c>
       <c r="E41">
-        <v>0.040801798155347124</v>
+        <v>-0.003479104933536299</v>
       </c>
       <c r="F41">
         <v>-7.579843751144125e-15</v>

--- a/irf/irf/Paper IRFs.xlsx
+++ b/irf/irf/Paper IRFs.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="29">
   <si>
     <t>t</t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>2026-02-10T13:51:34.338</t>
+  </si>
+  <si>
+    <t>2026-02-23T14:36:29.843</t>
   </si>
 </sst>
 </file>
@@ -513,7 +516,7 @@
         <v>8</v>
       </c>
       <c r="K1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:11">

--- a/irf/irf/Paper IRFs.xlsx
+++ b/irf/irf/Paper IRFs.xlsx
@@ -17,6 +17,9 @@
     <sheet name="FTPL_Equilibrium_IRF_Policy_rat" r:id="rId5" sheetId="2"/>
     <sheet name="FG_6horizon_policy_rate_output_" r:id="rId7" sheetId="3"/>
     <sheet name="FG_6horizon_shock_weights" r:id="rId8" sheetId="4"/>
+    <sheet name="Interest_rate_peg_IRF_Policy_ra" r:id="rId9" sheetId="5"/>
+    <sheet name="stanadard_interest_rate_peg_wit" r:id="rId10" sheetId="6"/>
+    <sheet name="interest_rate_peg_with_only_FG_" r:id="rId11" sheetId="7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="51">
   <si>
     <t>t</t>
   </si>
@@ -115,6 +118,72 @@
   </si>
   <si>
     <t>2026-02-23T14:36:29.843</t>
+  </si>
+  <si>
+    <t>2026-02-26T12:54:28.153</t>
+  </si>
+  <si>
+    <t>2026-02-26T12:55:03.234</t>
+  </si>
+  <si>
+    <t>2026-02-26T12:55:08.508</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:05:39.525</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:05:56.585</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:06:01.228</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:06:07.945</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:06:10.979</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:06:37.014</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:14:52.476</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:15:57.219</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:16:00.719</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:16:03.9</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:16:06.861</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:16:10.012</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:16:13.832</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:19:49.297</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:19:55.616</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:20:00.281</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:20:04.254</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:20:07.563</t>
+  </si>
+  <si>
+    <t>2026-02-27T23:20:10.748</t>
   </si>
 </sst>
 </file>
@@ -495,16 +564,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
@@ -516,7 +585,7 @@
         <v>8</v>
       </c>
       <c r="K1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -527,22 +596,22 @@
         <v>-1.0</v>
       </c>
       <c r="C2">
-        <v>-1.6915336844286093</v>
+        <v>0.0</v>
       </c>
       <c r="D2">
-        <v>0.0</v>
+        <v>3.111383456359226e-15</v>
       </c>
       <c r="E2">
-        <v>5.148080382766119e-15</v>
+        <v>0.07166727228172108</v>
       </c>
       <c r="F2">
-        <v>0.0716672722817191</v>
+        <v>-1.69153368442861</v>
       </c>
       <c r="G2">
-        <v>2.5793795815169456</v>
+        <v>2.5793795815169407</v>
       </c>
       <c r="H2">
-        <v>-1.0776287571287195</v>
+        <v>-1.077628757128724</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -553,22 +622,22 @@
         <v>-1.0</v>
       </c>
       <c r="C3">
-        <v>-0.7378682177184183</v>
+        <v>0.0</v>
       </c>
       <c r="D3">
-        <v>0.0</v>
+        <v>3.898465206358163e-15</v>
       </c>
       <c r="E3">
-        <v>6.2791836394635625e-15</v>
+        <v>0.09633801591550874</v>
       </c>
       <c r="F3">
-        <v>0.09633801591550183</v>
+        <v>-0.7378682177184217</v>
       </c>
       <c r="G3">
-        <v>1.4953394328181018</v>
+        <v>1.495339432818104</v>
       </c>
       <c r="H3">
-        <v>-1.0901798523912853</v>
+        <v>-1.0901798523912902</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -579,22 +648,22 @@
         <v>-1.0</v>
       </c>
       <c r="C4">
-        <v>-0.6713986913636436</v>
+        <v>0.0</v>
       </c>
       <c r="D4">
-        <v>0.0</v>
+        <v>4.940492912591414e-15</v>
       </c>
       <c r="E4">
-        <v>7.804041398192428e-15</v>
+        <v>0.11514371513779122</v>
       </c>
       <c r="F4">
-        <v>0.11514371513778257</v>
+        <v>-0.6713986913636477</v>
       </c>
       <c r="G4">
-        <v>1.1447890872423834</v>
+        <v>1.144789087242387</v>
       </c>
       <c r="H4">
-        <v>-1.1050722210876067</v>
+        <v>-1.105072221087612</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -605,22 +674,22 @@
         <v>-1.0</v>
       </c>
       <c r="C5">
-        <v>-0.6279689939410035</v>
+        <v>0.0</v>
       </c>
       <c r="D5">
-        <v>0.0</v>
+        <v>5.93655304045774e-15</v>
       </c>
       <c r="E5">
-        <v>9.213698585158189e-15</v>
+        <v>0.12932449243634242</v>
       </c>
       <c r="F5">
-        <v>0.12932449243633257</v>
+        <v>-0.6279689939410079</v>
       </c>
       <c r="G5">
         <v>0.9056919935333063</v>
       </c>
       <c r="H5">
-        <v>-1.1161558581396847</v>
+        <v>-1.1161558581396904</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -631,22 +700,22 @@
         <v>-1.0</v>
       </c>
       <c r="C6">
-        <v>-0.5973455825607836</v>
+        <v>0.0</v>
       </c>
       <c r="D6">
-        <v>0.0</v>
+        <v>6.895917639831189e-15</v>
       </c>
       <c r="E6">
-        <v>1.0529939632425284e-14</v>
+        <v>0.13989587911805162</v>
       </c>
       <c r="F6">
-        <v>0.1398958791180408</v>
+        <v>-0.5973455825607896</v>
       </c>
       <c r="G6">
-        <v>0.7319914235132261</v>
+        <v>0.7319914235132314</v>
       </c>
       <c r="H6">
-        <v>-1.124275171477677</v>
+        <v>-1.124275171477683</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -657,22 +726,22 @@
         <v>-1.0</v>
       </c>
       <c r="C7">
-        <v>-0.5737467099099121</v>
+        <v>0.0</v>
       </c>
       <c r="D7">
-        <v>0.0</v>
+        <v>7.822472301516801e-15</v>
       </c>
       <c r="E7">
-        <v>1.1764561194408219e-14</v>
+        <v>0.14757978149828713</v>
       </c>
       <c r="F7">
-        <v>0.14757978149827572</v>
+        <v>-0.5737467099099169</v>
       </c>
       <c r="G7">
-        <v>0.5973427245187732</v>
+        <v>0.5973427245187759</v>
       </c>
       <c r="H7">
-        <v>-1.1300125312110396</v>
+        <v>-1.1300125312110456</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -680,25 +749,25 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>-0.7449269414029471</v>
+        <v>-0.7449269414029468</v>
       </c>
       <c r="C8">
-        <v>-0.12249492256576702</v>
+        <v>0.0</v>
       </c>
       <c r="D8">
-        <v>0.0</v>
+        <v>7.92371673135295e-15</v>
       </c>
       <c r="E8">
-        <v>1.1610965451139857e-14</v>
+        <v>0.13461497481591014</v>
       </c>
       <c r="F8">
-        <v>0.13461497481589896</v>
+        <v>-0.12249492256576862</v>
       </c>
       <c r="G8">
         <v>-0.1711148877063895</v>
       </c>
       <c r="H8">
-        <v>-0.8589162460761607</v>
+        <v>-0.8589162460761651</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -706,25 +775,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>-0.5546326047314784</v>
+        <v>-0.5546326047314788</v>
       </c>
       <c r="C9">
-        <v>-0.02615266596779151</v>
+        <v>0.0</v>
       </c>
       <c r="D9">
-        <v>0.0</v>
+        <v>7.993945003915494e-15</v>
       </c>
       <c r="E9">
-        <v>1.1431233203186344e-14</v>
+        <v>0.11802452605864389</v>
       </c>
       <c r="F9">
-        <v>0.11802452605863416</v>
+        <v>-0.026152665967792765</v>
       </c>
       <c r="G9">
-        <v>-0.48020139575093257</v>
+        <v>-0.4802013957509361</v>
       </c>
       <c r="H9">
-        <v>-0.6527917857811548</v>
+        <v>-0.652791785781159</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -732,25 +801,25 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>-0.4349253801348609</v>
+        <v>-0.4349253801348624</v>
       </c>
       <c r="C10">
-        <v>-0.005583594184123434</v>
+        <v>0.0</v>
       </c>
       <c r="D10">
-        <v>0.0</v>
+        <v>8.036648733937131e-15</v>
       </c>
       <c r="E10">
-        <v>1.1231008356708664e-14</v>
+        <v>0.1016340160588325</v>
       </c>
       <c r="F10">
-        <v>0.10163401605882434</v>
+        <v>-0.005583594184124898</v>
       </c>
       <c r="G10">
-        <v>-0.5768324684811983</v>
+        <v>-0.5768324684812018</v>
       </c>
       <c r="H10">
-        <v>-0.518379630721563</v>
+        <v>-0.5183796307215672</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -758,25 +827,25 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>-0.36010806827413905</v>
+        <v>-0.36010806827414216</v>
       </c>
       <c r="C11">
-        <v>-0.0011920973583099271</v>
+        <v>0.0</v>
       </c>
       <c r="D11">
-        <v>0.0</v>
+        <v>8.055177528238005e-15</v>
       </c>
       <c r="E11">
-        <v>1.1015381934708258e-14</v>
+        <v>0.08640853105746768</v>
       </c>
       <c r="F11">
-        <v>0.08640853105746107</v>
+        <v>-0.001192097358311618</v>
       </c>
       <c r="G11">
-        <v>-0.5871768624011784</v>
+        <v>-0.5871768624011837</v>
       </c>
       <c r="H11">
-        <v>-0.4302230951401023</v>
+        <v>-0.4302230951401071</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -784,25 +853,25 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>-0.31207784837616204</v>
+        <v>-0.3120778483761672</v>
       </c>
       <c r="C12">
-        <v>-0.0002545127859985</v>
+        <v>0.0</v>
       </c>
       <c r="D12">
-        <v>0.0</v>
+        <v>8.052694231048553e-15</v>
       </c>
       <c r="E12">
-        <v>1.078889283971475e-14</v>
+        <v>0.0725970988170137</v>
       </c>
       <c r="F12">
-        <v>0.07259709881700852</v>
+        <v>-0.0002545127860002641</v>
       </c>
       <c r="G12">
-        <v>-0.5655516135502099</v>
+        <v>-0.565551613550217</v>
       </c>
       <c r="H12">
-        <v>-0.37025101988486603</v>
+        <v>-0.37025101988487197</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -810,25 +879,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>-0.2803966295926651</v>
+        <v>-0.28039662959267125</v>
       </c>
       <c r="C13">
-        <v>-5.4338479809878387e-5</v>
+        <v>0.0</v>
       </c>
       <c r="D13">
-        <v>0.0</v>
+        <v>8.03214546479992e-15</v>
       </c>
       <c r="E13">
-        <v>1.0555540114031353e-14</v>
+        <v>0.06023250178010655</v>
       </c>
       <c r="F13">
-        <v>0.060232501780102726</v>
+        <v>-5.4338479811570196e-5</v>
       </c>
       <c r="G13">
-        <v>-0.5334958471292568</v>
+        <v>-0.5334958471292577</v>
       </c>
       <c r="H13">
-        <v>-0.32798101284319414</v>
+        <v>-0.32798101284320025</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -836,25 +905,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>-0.2590128761764773</v>
+        <v>-0.25901287617648544</v>
       </c>
       <c r="C14">
-        <v>-1.1601265438559588e-5</v>
+        <v>0.0</v>
       </c>
       <c r="D14">
-        <v>0.0</v>
+        <v>7.996244402227264e-15</v>
       </c>
       <c r="E14">
-        <v>1.0318803898651284e-14</v>
+        <v>0.04926887041759134</v>
       </c>
       <c r="F14">
-        <v>0.04926887041758877</v>
+        <v>-1.1601265440080863e-5</v>
       </c>
       <c r="G14">
-        <v>-0.499029394560659</v>
+        <v>-0.4990293945606652</v>
       </c>
       <c r="H14">
-        <v>-0.29728557226249874</v>
+        <v>-0.29728557226250607</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -862,25 +931,25 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>-0.244202943146743</v>
+        <v>-0.24420294314675212</v>
       </c>
       <c r="C15">
-        <v>-2.47687017037748e-6</v>
+        <v>0.0</v>
       </c>
       <c r="D15">
-        <v>0.0</v>
+        <v>7.947463158533916e-15</v>
       </c>
       <c r="E15">
-        <v>1.0081672752685055e-14</v>
+        <v>0.03962754952745947</v>
       </c>
       <c r="F15">
-        <v>0.039627549527458145</v>
+        <v>-2.476870171681697e-6</v>
       </c>
       <c r="G15">
-        <v>-0.46490712897908937</v>
+        <v>-0.46490712897909026</v>
       </c>
       <c r="H15">
-        <v>-0.27435118561052385</v>
+        <v>-0.2743511856105313</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -888,25 +957,25 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>-0.2335344033664392</v>
+        <v>-0.2335344033664497</v>
       </c>
       <c r="C16">
-        <v>-5.288117807193205e-7</v>
+        <v>0.0</v>
       </c>
       <c r="D16">
-        <v>0.0</v>
+        <v>7.888032605038842e-15</v>
       </c>
       <c r="E16">
-        <v>9.84667539576941e-15</v>
+        <v>0.031215490246990683</v>
       </c>
       <c r="F16">
-        <v>0.031215490246990597</v>
+        <v>-5.288117817913485e-7</v>
       </c>
       <c r="G16">
-        <v>-0.43193786324030503</v>
+        <v>-0.4319378632403077</v>
       </c>
       <c r="H16">
-        <v>-0.2566500422596416</v>
+        <v>-0.25665004225964966</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -914,25 +983,25 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>-0.22535571436970298</v>
+        <v>-0.22535571436971474</v>
       </c>
       <c r="C17">
-        <v>-1.1290131462664847e-7</v>
+        <v>0.0</v>
       </c>
       <c r="D17">
-        <v>0.0</v>
+        <v>7.819947773804995e-15</v>
       </c>
       <c r="E17">
-        <v>9.615915282630472e-15</v>
+        <v>0.023933932510013023</v>
       </c>
       <c r="F17">
-        <v>0.02393393251001406</v>
+        <v>-1.1290131546558792e-7</v>
       </c>
       <c r="G17">
-        <v>-0.4002656212734461</v>
+        <v>-0.4002656212734492</v>
       </c>
       <c r="H17">
-        <v>-0.24243423152081073</v>
+        <v>-0.24243423152081936</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -940,25 +1009,25 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>-0.21852925238737592</v>
+        <v>-0.2185292523873888</v>
       </c>
       <c r="C18">
-        <v>-2.4104430213144082e-8</v>
+        <v>0.0</v>
       </c>
       <c r="D18">
-        <v>0.0</v>
+        <v>7.744977345828397e-15</v>
       </c>
       <c r="E18">
-        <v>9.391106717500153e-15</v>
+        <v>0.017683096658247664</v>
       </c>
       <c r="F18">
-        <v>0.017683096658249697</v>
+        <v>-2.41044308264451e-8</v>
       </c>
       <c r="G18">
-        <v>-0.3698442820958281</v>
+        <v>-0.36984428209583076</v>
       </c>
       <c r="H18">
-        <v>-0.23047147775076154</v>
+        <v>-0.23047147775077065</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -966,25 +1035,25 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>-0.21227671283745408</v>
+        <v>-0.2122767128374673</v>
       </c>
       <c r="C19">
-        <v>-5.146295484060616e-9</v>
+        <v>0.0</v>
       </c>
       <c r="D19">
-        <v>0.0</v>
+        <v>7.664675995318849e-15</v>
       </c>
       <c r="E19">
-        <v>9.173611471779076e-15</v>
+        <v>0.012364980141239663</v>
       </c>
       <c r="F19">
-        <v>0.012364980141242678</v>
+        <v>-5.14629588454877e-9</v>
       </c>
       <c r="G19">
-        <v>-0.34060187362750494</v>
+        <v>-0.34060187362750627</v>
       </c>
       <c r="H19">
-        <v>-0.2198922430955447</v>
+        <v>-0.21989224309555344</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -992,25 +1061,25 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>-0.2060797172707384</v>
+        <v>-0.2060797172707516</v>
       </c>
       <c r="C20">
-        <v>-1.098733807066088e-9</v>
+        <v>0.0</v>
       </c>
       <c r="D20">
-        <v>0.0</v>
+        <v>7.580398602510176e-15</v>
       </c>
       <c r="E20">
-        <v>8.964475086133216e-15</v>
+        <v>0.007885120029216744</v>
       </c>
       <c r="F20">
-        <v>0.007885120029220665</v>
+        <v>-1.0987340110261482e-9</v>
       </c>
       <c r="G20">
-        <v>-0.31248901919794614</v>
+        <v>-0.3124890191979479</v>
       </c>
       <c r="H20">
-        <v>-0.21009142183175822</v>
+        <v>-0.21009142183176638</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1018,25 +1087,25 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>-0.19961054127213992</v>
+        <v>-0.19961054127215333</v>
       </c>
       <c r="C21">
-        <v>-2.34579470172812e-10</v>
+        <v>0.0</v>
       </c>
       <c r="D21">
-        <v>0.0</v>
+        <v>7.49331555098882e-15</v>
       </c>
       <c r="E21">
-        <v>8.76446222262879e-15</v>
+        <v>0.0041537189024692745</v>
       </c>
       <c r="F21">
-        <v>0.004153718902474034</v>
+        <v>-2.345794959814191e-10</v>
       </c>
       <c r="G21">
-        <v>-0.2854862761513888</v>
+        <v>-0.28548627615138966</v>
       </c>
       <c r="H21">
-        <v>-0.20065974270055495</v>
+        <v>-0.20065974270056278</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1592,13 +1661,13 @@
         <v>8</v>
       </c>
       <c r="H1" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
       </c>
       <c r="K1" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1606,25 +1675,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>8.102500031716193</v>
+        <v>8.102500031716206</v>
       </c>
       <c r="C2">
         <v>0.0</v>
       </c>
       <c r="D2">
-        <v>-1.0</v>
+        <v>-0.9999999999999997</v>
       </c>
       <c r="E2">
-        <v>0.3002694365653483</v>
+        <v>0.30026943656535576</v>
       </c>
       <c r="F2">
-        <v>-1.8240941779797443e-14</v>
+        <v>1.1945048918812522e-14</v>
       </c>
       <c r="G2">
-        <v>0.4586028719414255</v>
+        <v>-3.200818256209439</v>
       </c>
       <c r="H2">
-        <v>-0.2916108571679106</v>
+        <v>0.30026943656535576</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1632,25 +1701,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.7924900644128168</v>
+        <v>11.894990096129039</v>
       </c>
       <c r="C3">
         <v>0.0</v>
       </c>
       <c r="D3">
-        <v>-1.0</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="E3">
-        <v>0.34132427283477856</v>
+        <v>0.341324272834796</v>
       </c>
       <c r="F3">
-        <v>-1.815767595640473e-14</v>
+        <v>1.236786245210933e-14</v>
       </c>
       <c r="G3">
-        <v>0.22319313455430967</v>
+        <v>-0.8007358613175596</v>
       </c>
       <c r="H3">
-        <v>-0.33915754479465826</v>
+        <v>0.341324272834796</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1658,25 +1727,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.535682253088882</v>
+        <v>13.430672349217918</v>
       </c>
       <c r="C4">
         <v>0.0</v>
       </c>
       <c r="D4">
-        <v>-1.0000000000000002</v>
+        <v>-0.9999999999999999</v>
       </c>
       <c r="E4">
-        <v>0.3262395395059982</v>
+        <v>0.3262395395060162</v>
       </c>
       <c r="F4">
-        <v>-1.7990016981340348e-14</v>
+        <v>1.2712130219558677e-14</v>
       </c>
       <c r="G4">
-        <v>0.1733771867033961</v>
+        <v>-0.6225725146161963</v>
       </c>
       <c r="H4">
-        <v>-0.3359955377002835</v>
+        <v>0.3262395395060162</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1684,25 +1753,25 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.314417515476746</v>
+        <v>13.74508986469466</v>
       </c>
       <c r="C5">
         <v>0.0</v>
       </c>
       <c r="D5">
-        <v>-1.0</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="E5">
-        <v>0.297172637639562</v>
+        <v>0.29717263763957846</v>
       </c>
       <c r="F5">
-        <v>-1.7750026373046594e-14</v>
+        <v>1.2984205210219286e-14</v>
       </c>
       <c r="G5">
-        <v>0.13606624062531894</v>
+        <v>-0.4304117562920385</v>
       </c>
       <c r="H5">
-        <v>-0.3194967604267872</v>
+        <v>0.29717263763957846</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1710,25 +1779,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>-0.3714566512920629</v>
+        <v>13.373633213402588</v>
       </c>
       <c r="C6">
         <v>0.0</v>
       </c>
       <c r="D6">
-        <v>-1.0000000000000002</v>
+        <v>-1.0</v>
       </c>
       <c r="E6">
-        <v>0.26450237048056346</v>
+        <v>0.26450237048057795</v>
       </c>
       <c r="F6">
-        <v>-1.7449311279723872e-14</v>
+        <v>1.3190713735165675e-14</v>
       </c>
       <c r="G6">
-        <v>0.10077323633482921</v>
+        <v>-0.3107196037060323</v>
       </c>
       <c r="H6">
-        <v>-0.2975542049811292</v>
+        <v>0.26450237048057795</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1736,25 +1805,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>-0.7682647916323465</v>
+        <v>12.605368421770233</v>
       </c>
       <c r="C7">
         <v>0.0</v>
       </c>
       <c r="D7">
-        <v>-1.0</v>
+        <v>-0.9999999999999999</v>
       </c>
       <c r="E7">
-        <v>0.23168373759607122</v>
+        <v>0.23168373759608402</v>
       </c>
       <c r="F7">
-        <v>-1.7098845668544484e-14</v>
+        <v>1.3338330603505361e-14</v>
       </c>
       <c r="G7">
-        <v>2.063782970431286</v>
+        <v>-0.231532170537758</v>
       </c>
       <c r="H7">
-        <v>-0.27236297336873977</v>
+        <v>0.23168373759608402</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1762,25 +1831,25 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>-0.9983762771240359</v>
+        <v>11.60699214464619</v>
       </c>
       <c r="C8">
         <v>0.0</v>
       </c>
       <c r="D8">
-        <v>-0.8228559440075205</v>
+        <v>-0.8228559440075245</v>
       </c>
       <c r="E8">
-        <v>0.20029060488665273</v>
+        <v>0.20029060488666367</v>
       </c>
       <c r="F8">
-        <v>-1.6708846025861055e-14</v>
+        <v>1.3433608185646603e-14</v>
       </c>
       <c r="G8">
         <v>0.0</v>
       </c>
       <c r="H8">
-        <v>-0.2449613808818707</v>
+        <v>0.20029060488666367</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1788,25 +1857,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>-1.0615234494165005</v>
+        <v>10.545468695229683</v>
       </c>
       <c r="C9">
         <v>0.0</v>
       </c>
       <c r="D9">
-        <v>-0.6802281125838083</v>
+        <v>-0.6802281125838165</v>
       </c>
       <c r="E9">
-        <v>0.17117303992476582</v>
+        <v>0.17117303992477478</v>
       </c>
       <c r="F9">
-        <v>-1.628869161461582e-14</v>
+        <v>1.3482850291698822e-14</v>
       </c>
       <c r="G9">
         <v>0.0</v>
       </c>
       <c r="H9">
-        <v>-0.21613136847009748</v>
+        <v>0.17117303992477478</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1814,25 +1883,25 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>-1.0428589933721009</v>
+        <v>9.502609701857576</v>
       </c>
       <c r="C10">
         <v>0.0</v>
       </c>
       <c r="D10">
-        <v>-0.5839658177105793</v>
+        <v>-0.5839658177105909</v>
       </c>
       <c r="E10">
-        <v>0.14469354968982942</v>
+        <v>0.1446935496898365</v>
       </c>
       <c r="F10">
-        <v>-1.5846880766101665e-14</v>
+        <v>1.3492022862886328e-14</v>
       </c>
       <c r="G10">
         <v>0.0</v>
       </c>
       <c r="H10">
-        <v>-0.18772319729264852</v>
+        <v>0.1446935496898365</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1840,25 +1909,25 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>-0.9921377386601233</v>
+        <v>8.51047196319744</v>
       </c>
       <c r="C11">
         <v>0.0</v>
       </c>
       <c r="D11">
-        <v>-0.5204572812941362</v>
+        <v>-0.5204572812941508</v>
       </c>
       <c r="E11">
-        <v>0.1209314480216968</v>
+        <v>0.12093144802170196</v>
       </c>
       <c r="F11">
-        <v>-1.5391015939674246e-14</v>
+        <v>1.3466694517385076e-14</v>
       </c>
       <c r="G11">
         <v>0.0</v>
       </c>
       <c r="H11">
-        <v>-0.16101066831640803</v>
+        <v>0.12093144802170196</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1866,25 +1935,25 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>-0.9313171317033377</v>
+        <v>7.579154831494095</v>
       </c>
       <c r="C12">
         <v>0.0</v>
       </c>
       <c r="D12">
-        <v>-0.4780823352039272</v>
+        <v>-0.4780823352039434</v>
       </c>
       <c r="E12">
-        <v>0.0998197529172179</v>
+        <v>0.0998197529172211</v>
       </c>
       <c r="F12">
-        <v>-1.492781138475873e-14</v>
+        <v>1.3412000973304146e-14</v>
       </c>
       <c r="G12">
         <v>0.0</v>
       </c>
       <c r="H12">
-        <v>-0.13659061073591336</v>
+        <v>0.0998197529172211</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1892,25 +1961,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>-0.8688979012157303</v>
+        <v>6.710256930278353</v>
       </c>
       <c r="C13">
         <v>0.0</v>
       </c>
       <c r="D13">
-        <v>-0.44914320705740507</v>
+        <v>-0.4491432070574239</v>
       </c>
       <c r="E13">
-        <v>0.08122018743975548</v>
+        <v>0.08122018743975679</v>
       </c>
       <c r="F13">
-        <v>-1.4463118201713377e-14</v>
+        <v>1.3332628271158423e-14</v>
       </c>
       <c r="G13">
         <v>0.0</v>
       </c>
       <c r="H13">
-        <v>-0.11464720511777625</v>
+        <v>0.08122018743975679</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1918,25 +1987,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>-0.8077995380727517</v>
+        <v>5.9024573922055925</v>
       </c>
       <c r="C14">
         <v>0.0</v>
       </c>
       <c r="D14">
-        <v>-0.42862347099199605</v>
+        <v>-0.42862347099201664</v>
       </c>
       <c r="E14">
-        <v>0.06496131838760792</v>
+        <v>0.06496131838760731</v>
       </c>
       <c r="F14">
-        <v>-1.4001962437076097e-14</v>
+        <v>1.323281052728338e-14</v>
       </c>
       <c r="G14">
         <v>0.0</v>
       </c>
       <c r="H14">
-        <v>-0.09515749882355357</v>
+        <v>0.06496131838760731</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1944,25 +2013,25 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>-0.7488403124163857</v>
+        <v>5.153617079789201</v>
       </c>
       <c r="C15">
         <v>0.0</v>
       </c>
       <c r="D15">
-        <v>-0.41317369462819337</v>
+        <v>-0.4131736946282153</v>
       </c>
       <c r="E15">
-        <v>0.05085802283127187</v>
+        <v>0.05085802283126942</v>
       </c>
       <c r="F15">
-        <v>-1.3548592577989773e-14</v>
+        <v>1.3116338666312405e-14</v>
       </c>
       <c r="G15">
         <v>0.0</v>
       </c>
       <c r="H15">
-        <v>-0.07800296479349081</v>
+        <v>0.05085802283126942</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1970,25 +2039,25 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>-0.6921339810602081</v>
+        <v>4.461483098728982</v>
       </c>
       <c r="C16">
         <v>0.0</v>
       </c>
       <c r="D16">
-        <v>-0.4005166921982795</v>
+        <v>-0.40051669219830294</v>
       </c>
       <c r="E16">
-        <v>0.03872194353595661</v>
+        <v>0.038721943535952465</v>
       </c>
       <c r="F16">
-        <v>-1.3106533442287815e-14</v>
+        <v>1.2986577207574162e-14</v>
       </c>
       <c r="G16">
         <v>0.0</v>
       </c>
       <c r="H16">
-        <v>-0.0630235728390008</v>
+        <v>0.038721943535952465</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1996,25 +2065,25 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>-0.6376112097334082</v>
+        <v>3.8238718889955634</v>
       </c>
       <c r="C17">
         <v>0.0</v>
       </c>
       <c r="D17">
-        <v>-0.38910425750694966</v>
+        <v>-0.38910425750697364</v>
       </c>
       <c r="E17">
-        <v>0.028367498022029917</v>
+        <v>0.028367498022024082</v>
       </c>
       <c r="F17">
-        <v>-1.2678644005712723e-14</v>
+        <v>1.2846486722289322e-14</v>
       </c>
       <c r="G17">
         <v>0.0</v>
       </c>
       <c r="H17">
-        <v>-0.050043438695366003</v>
+        <v>0.028367498022024082</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2022,25 +2091,25 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>-0.5851956049269981</v>
+        <v>3.238676284068557</v>
       </c>
       <c r="C18">
         <v>0.0</v>
       </c>
       <c r="D18">
-        <v>-0.3779051514818019</v>
+        <v>-0.37790515148182624</v>
       </c>
       <c r="E18">
-        <v>0.019615529123016506</v>
+        <v>0.01961552912300906</v>
       </c>
       <c r="F18">
-        <v>-1.2267177175878604e-14</v>
+        <v>1.2698650042513726e-14</v>
       </c>
       <c r="G18">
         <v>0.0</v>
       </c>
       <c r="H18">
-        <v>-0.038883382573900116</v>
+        <v>0.01961552912300906</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2048,25 +2117,25 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>-0.5348503251242684</v>
+        <v>2.703825958944279</v>
       </c>
       <c r="C19">
         <v>0.0</v>
       </c>
       <c r="D19">
-        <v>-0.36626309791247713</v>
+        <v>-0.3662630979125017</v>
       </c>
       <c r="E19">
-        <v>0.012295576831416185</v>
+        <v>0.012295576831407232</v>
       </c>
       <c r="F19">
-        <v>-1.1873839922785759e-14</v>
+        <v>1.2545300696393843e-14</v>
       </c>
       <c r="G19">
         <v>0.0</v>
       </c>
       <c r="H19">
-        <v>-0.029367464426574542</v>
+        <v>0.012295576831407232</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2074,25 +2143,25 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>-0.4865796943485873</v>
+        <v>2.217246264595686</v>
       </c>
       <c r="C20">
         <v>0.0</v>
       </c>
       <c r="D20">
-        <v>-0.35379549635816077</v>
+        <v>-0.35379549635818497</v>
       </c>
       <c r="E20">
-        <v>0.006247266563694634</v>
+        <v>0.00624726656368428</v>
       </c>
       <c r="F20">
-        <v>-1.1499852516027993e-14</v>
+        <v>1.2388352375174012e-14</v>
       </c>
       <c r="G20">
         <v>0.0</v>
       </c>
       <c r="H20">
-        <v>-0.021326604155434102</v>
+        <v>0.00624726656368428</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2100,25 +2169,25 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>-0.4404176585643645</v>
+        <v>1.7768286060313154</v>
       </c>
       <c r="C21">
         <v>0.0</v>
       </c>
       <c r="D21">
-        <v>-0.34031834310639586</v>
+        <v>-0.3403183431064198</v>
       </c>
       <c r="E21">
-        <v>0.00132109198404053</v>
+        <v>0.0013210919840288618</v>
       </c>
       <c r="F21">
-        <v>-1.1146005906605964e-14</v>
+        <v>1.2229428513066768e-14</v>
       </c>
       <c r="G21">
         <v>0.0</v>
       </c>
       <c r="H21">
-        <v>-0.014600660752973445</v>
+        <v>0.0013210919840288618</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2665,7 +2734,7 @@
         <v>8</v>
       </c>
       <c r="F1" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2673,7 +2742,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>-3.2008182562094296</v>
+        <v>-3.200818256209439</v>
       </c>
       <c r="C2">
         <v>0.0</v>
@@ -2684,7 +2753,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>-0.8007358613175475</v>
+        <v>-0.8007358613175596</v>
       </c>
       <c r="C3">
         <v>0.0</v>
@@ -2695,7 +2764,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>-0.6225725146161908</v>
+        <v>-0.6225725146161963</v>
       </c>
       <c r="C4">
         <v>0.0</v>
@@ -2706,7 +2775,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>-0.43041175629203515</v>
+        <v>-0.4304117562920385</v>
       </c>
       <c r="C5">
         <v>0.0</v>
@@ -2717,7 +2786,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>-0.31071960370603274</v>
+        <v>-0.3107196037060323</v>
       </c>
       <c r="C6">
         <v>0.0</v>
@@ -2728,7 +2797,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>-0.2315321705377608</v>
+        <v>-0.231532170537758</v>
       </c>
       <c r="C7">
         <v>0.0</v>
@@ -3106,6 +3175,1692 @@
       </c>
       <c r="C41">
         <v>0.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>-1.0</v>
+      </c>
+      <c r="C2">
+        <v>-1.69153368442861</v>
+      </c>
+      <c r="D2">
+        <v>0.0</v>
+      </c>
+      <c r="E2">
+        <v>3.111383456359226e-15</v>
+      </c>
+      <c r="F2">
+        <v>0.07166727228172108</v>
+      </c>
+      <c r="G2">
+        <v>2.5793795815169407</v>
+      </c>
+      <c r="H2">
+        <v>-1.077628757128724</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>-1.0</v>
+      </c>
+      <c r="C3">
+        <v>-0.7378682177184217</v>
+      </c>
+      <c r="D3">
+        <v>0.0</v>
+      </c>
+      <c r="E3">
+        <v>3.898465206358163e-15</v>
+      </c>
+      <c r="F3">
+        <v>0.09633801591550874</v>
+      </c>
+      <c r="G3">
+        <v>1.495339432818104</v>
+      </c>
+      <c r="H3">
+        <v>-1.0901798523912902</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>-1.0</v>
+      </c>
+      <c r="C4">
+        <v>-0.6713986913636477</v>
+      </c>
+      <c r="D4">
+        <v>0.0</v>
+      </c>
+      <c r="E4">
+        <v>4.940492912591414e-15</v>
+      </c>
+      <c r="F4">
+        <v>0.11514371513779122</v>
+      </c>
+      <c r="G4">
+        <v>1.144789087242387</v>
+      </c>
+      <c r="H4">
+        <v>-1.105072221087612</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>-1.0</v>
+      </c>
+      <c r="C5">
+        <v>-0.6279689939410079</v>
+      </c>
+      <c r="D5">
+        <v>0.0</v>
+      </c>
+      <c r="E5">
+        <v>5.93655304045774e-15</v>
+      </c>
+      <c r="F5">
+        <v>0.12932449243634242</v>
+      </c>
+      <c r="G5">
+        <v>0.9056919935333063</v>
+      </c>
+      <c r="H5">
+        <v>-1.1161558581396904</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>-1.0</v>
+      </c>
+      <c r="C6">
+        <v>-0.5973455825607896</v>
+      </c>
+      <c r="D6">
+        <v>0.0</v>
+      </c>
+      <c r="E6">
+        <v>6.895917639831189e-15</v>
+      </c>
+      <c r="F6">
+        <v>0.13989587911805162</v>
+      </c>
+      <c r="G6">
+        <v>0.7319914235132314</v>
+      </c>
+      <c r="H6">
+        <v>-1.124275171477683</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>-1.0</v>
+      </c>
+      <c r="C7">
+        <v>-0.5737467099099169</v>
+      </c>
+      <c r="D7">
+        <v>0.0</v>
+      </c>
+      <c r="E7">
+        <v>7.822472301516801e-15</v>
+      </c>
+      <c r="F7">
+        <v>0.14757978149828713</v>
+      </c>
+      <c r="G7">
+        <v>0.5973427245187759</v>
+      </c>
+      <c r="H7">
+        <v>-1.1300125312110456</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>-0.7449269414029468</v>
+      </c>
+      <c r="C8">
+        <v>-0.12249492256576862</v>
+      </c>
+      <c r="D8">
+        <v>0.0</v>
+      </c>
+      <c r="E8">
+        <v>7.92371673135295e-15</v>
+      </c>
+      <c r="F8">
+        <v>0.13461497481591014</v>
+      </c>
+      <c r="G8">
+        <v>-0.1711148877063895</v>
+      </c>
+      <c r="H8">
+        <v>-0.8589162460761651</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>-0.5546326047314788</v>
+      </c>
+      <c r="C9">
+        <v>-0.026152665967792765</v>
+      </c>
+      <c r="D9">
+        <v>0.0</v>
+      </c>
+      <c r="E9">
+        <v>7.993945003915494e-15</v>
+      </c>
+      <c r="F9">
+        <v>0.11802452605864389</v>
+      </c>
+      <c r="G9">
+        <v>-0.4802013957509361</v>
+      </c>
+      <c r="H9">
+        <v>-0.652791785781159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>-0.4349253801348624</v>
+      </c>
+      <c r="C10">
+        <v>-0.005583594184124898</v>
+      </c>
+      <c r="D10">
+        <v>0.0</v>
+      </c>
+      <c r="E10">
+        <v>8.036648733937131e-15</v>
+      </c>
+      <c r="F10">
+        <v>0.1016340160588325</v>
+      </c>
+      <c r="G10">
+        <v>-0.5768324684812018</v>
+      </c>
+      <c r="H10">
+        <v>-0.5183796307215672</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>-0.36010806827414216</v>
+      </c>
+      <c r="C11">
+        <v>-0.001192097358311618</v>
+      </c>
+      <c r="D11">
+        <v>0.0</v>
+      </c>
+      <c r="E11">
+        <v>8.055177528238005e-15</v>
+      </c>
+      <c r="F11">
+        <v>0.08640853105746768</v>
+      </c>
+      <c r="G11">
+        <v>-0.5871768624011837</v>
+      </c>
+      <c r="H11">
+        <v>-0.4302230951401071</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>-0.3120778483761672</v>
+      </c>
+      <c r="C12">
+        <v>-0.0002545127860002641</v>
+      </c>
+      <c r="D12">
+        <v>0.0</v>
+      </c>
+      <c r="E12">
+        <v>8.052694231048553e-15</v>
+      </c>
+      <c r="F12">
+        <v>0.0725970988170137</v>
+      </c>
+      <c r="G12">
+        <v>-0.565551613550217</v>
+      </c>
+      <c r="H12">
+        <v>-0.37025101988487197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>-0.28039662959267125</v>
+      </c>
+      <c r="C13">
+        <v>-5.4338479811570196e-5</v>
+      </c>
+      <c r="D13">
+        <v>0.0</v>
+      </c>
+      <c r="E13">
+        <v>8.03214546479992e-15</v>
+      </c>
+      <c r="F13">
+        <v>0.06023250178010655</v>
+      </c>
+      <c r="G13">
+        <v>-0.5334958471292577</v>
+      </c>
+      <c r="H13">
+        <v>-0.32798101284320025</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>-0.25901287617648544</v>
+      </c>
+      <c r="C14">
+        <v>-1.1601265440080863e-5</v>
+      </c>
+      <c r="D14">
+        <v>0.0</v>
+      </c>
+      <c r="E14">
+        <v>7.996244402227264e-15</v>
+      </c>
+      <c r="F14">
+        <v>0.04926887041759134</v>
+      </c>
+      <c r="G14">
+        <v>-0.4990293945606652</v>
+      </c>
+      <c r="H14">
+        <v>-0.29728557226250607</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>-0.24420294314675212</v>
+      </c>
+      <c r="C15">
+        <v>-2.476870171681697e-6</v>
+      </c>
+      <c r="D15">
+        <v>0.0</v>
+      </c>
+      <c r="E15">
+        <v>7.947463158533916e-15</v>
+      </c>
+      <c r="F15">
+        <v>0.03962754952745947</v>
+      </c>
+      <c r="G15">
+        <v>-0.46490712897909026</v>
+      </c>
+      <c r="H15">
+        <v>-0.2743511856105313</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>-0.2335344033664497</v>
+      </c>
+      <c r="C16">
+        <v>-5.288117817913485e-7</v>
+      </c>
+      <c r="D16">
+        <v>0.0</v>
+      </c>
+      <c r="E16">
+        <v>7.888032605038842e-15</v>
+      </c>
+      <c r="F16">
+        <v>0.031215490246990683</v>
+      </c>
+      <c r="G16">
+        <v>-0.4319378632403077</v>
+      </c>
+      <c r="H16">
+        <v>-0.25665004225964966</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>-0.22535571436971474</v>
+      </c>
+      <c r="C17">
+        <v>-1.1290131546558792e-7</v>
+      </c>
+      <c r="D17">
+        <v>0.0</v>
+      </c>
+      <c r="E17">
+        <v>7.819947773804995e-15</v>
+      </c>
+      <c r="F17">
+        <v>0.023933932510013023</v>
+      </c>
+      <c r="G17">
+        <v>-0.4002656212734492</v>
+      </c>
+      <c r="H17">
+        <v>-0.24243423152081936</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>-0.2185292523873888</v>
+      </c>
+      <c r="C18">
+        <v>-2.41044308264451e-8</v>
+      </c>
+      <c r="D18">
+        <v>0.0</v>
+      </c>
+      <c r="E18">
+        <v>7.744977345828397e-15</v>
+      </c>
+      <c r="F18">
+        <v>0.017683096658247664</v>
+      </c>
+      <c r="G18">
+        <v>-0.36984428209583076</v>
+      </c>
+      <c r="H18">
+        <v>-0.23047147775077065</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>-0.2122767128374673</v>
+      </c>
+      <c r="C19">
+        <v>-5.14629588454877e-9</v>
+      </c>
+      <c r="D19">
+        <v>0.0</v>
+      </c>
+      <c r="E19">
+        <v>7.664675995318849e-15</v>
+      </c>
+      <c r="F19">
+        <v>0.012364980141239663</v>
+      </c>
+      <c r="G19">
+        <v>-0.34060187362750627</v>
+      </c>
+      <c r="H19">
+        <v>-0.21989224309555344</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>-0.2060797172707516</v>
+      </c>
+      <c r="C20">
+        <v>-1.0987340110261482e-9</v>
+      </c>
+      <c r="D20">
+        <v>0.0</v>
+      </c>
+      <c r="E20">
+        <v>7.580398602510176e-15</v>
+      </c>
+      <c r="F20">
+        <v>0.007885120029216744</v>
+      </c>
+      <c r="G20">
+        <v>-0.3124890191979479</v>
+      </c>
+      <c r="H20">
+        <v>-0.21009142183176638</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>-0.19961054127215333</v>
+      </c>
+      <c r="C21">
+        <v>-2.345794959814191e-10</v>
+      </c>
+      <c r="D21">
+        <v>0.0</v>
+      </c>
+      <c r="E21">
+        <v>7.49331555098882e-15</v>
+      </c>
+      <c r="F21">
+        <v>0.0041537189024692745</v>
+      </c>
+      <c r="G21">
+        <v>-0.28548627615138966</v>
+      </c>
+      <c r="H21">
+        <v>-0.20065974270056278</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>8.102500031716207</v>
+      </c>
+      <c r="C2">
+        <v>0.0</v>
+      </c>
+      <c r="D2">
+        <v>-0.9999999999999997</v>
+      </c>
+      <c r="E2">
+        <v>-1.329654503413945</v>
+      </c>
+      <c r="F2">
+        <v>1.1945048918812522e-14</v>
+      </c>
+      <c r="G2">
+        <v>-3.200818256209439</v>
+      </c>
+      <c r="H2">
+        <v>0.30026943656535576</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3.792490064412832</v>
+      </c>
+      <c r="C3">
+        <v>0.0</v>
+      </c>
+      <c r="D3">
+        <v>-0.9999999999999998</v>
+      </c>
+      <c r="E3">
+        <v>-1.315085512368188</v>
+      </c>
+      <c r="F3">
+        <v>1.236786245210933e-14</v>
+      </c>
+      <c r="G3">
+        <v>-0.8007358613175596</v>
+      </c>
+      <c r="H3">
+        <v>0.341324272834796</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1.5356822530888818</v>
+      </c>
+      <c r="C4">
+        <v>0.0</v>
+      </c>
+      <c r="D4">
+        <v>-0.9999999999999999</v>
+      </c>
+      <c r="E4">
+        <v>-1.2870123987247313</v>
+      </c>
+      <c r="F4">
+        <v>1.2712130219558677e-14</v>
+      </c>
+      <c r="G4">
+        <v>-0.6225725146161963</v>
+      </c>
+      <c r="H4">
+        <v>0.3262395395060162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>0.31441751547674085</v>
+      </c>
+      <c r="C5">
+        <v>0.0</v>
+      </c>
+      <c r="D5">
+        <v>-0.9999999999999998</v>
+      </c>
+      <c r="E5">
+        <v>-1.2554591177135284</v>
+      </c>
+      <c r="F5">
+        <v>1.2984205210219286e-14</v>
+      </c>
+      <c r="G5">
+        <v>-0.4304117562920385</v>
+      </c>
+      <c r="H5">
+        <v>0.29717263763957846</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>-0.37145665129207356</v>
+      </c>
+      <c r="C6">
+        <v>0.0</v>
+      </c>
+      <c r="D6">
+        <v>-1.0</v>
+      </c>
+      <c r="E6">
+        <v>-1.2237625435542734</v>
+      </c>
+      <c r="F6">
+        <v>1.3190713735165675e-14</v>
+      </c>
+      <c r="G6">
+        <v>-0.3107196037060323</v>
+      </c>
+      <c r="H6">
+        <v>0.26450237048057795</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>-0.7682647916323522</v>
+      </c>
+      <c r="C7">
+        <v>0.0</v>
+      </c>
+      <c r="D7">
+        <v>-0.9999999999999999</v>
+      </c>
+      <c r="E7">
+        <v>-1.1934427321679302</v>
+      </c>
+      <c r="F7">
+        <v>1.3338330603505361e-14</v>
+      </c>
+      <c r="G7">
+        <v>-0.231532170537758</v>
+      </c>
+      <c r="H7">
+        <v>0.23168373759608402</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>-0.9983762771240431</v>
+      </c>
+      <c r="C8">
+        <v>0.0</v>
+      </c>
+      <c r="D8">
+        <v>-0.8228559440075245</v>
+      </c>
+      <c r="E8">
+        <v>-0.9881766315918266</v>
+      </c>
+      <c r="F8">
+        <v>1.3433608185646603e-14</v>
+      </c>
+      <c r="G8">
+        <v>0.0</v>
+      </c>
+      <c r="H8">
+        <v>0.20029060488666367</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>-1.0615234494165058</v>
+      </c>
+      <c r="C9">
+        <v>0.0</v>
+      </c>
+      <c r="D9">
+        <v>-0.6802281125838165</v>
+      </c>
+      <c r="E9">
+        <v>-0.8199746353671349</v>
+      </c>
+      <c r="F9">
+        <v>1.3482850291698822e-14</v>
+      </c>
+      <c r="G9">
+        <v>0.0</v>
+      </c>
+      <c r="H9">
+        <v>0.17117303992477478</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>-1.0428589933721049</v>
+      </c>
+      <c r="C10">
+        <v>0.0</v>
+      </c>
+      <c r="D10">
+        <v>-0.5839658177105909</v>
+      </c>
+      <c r="E10">
+        <v>-0.7007626576002115</v>
+      </c>
+      <c r="F10">
+        <v>1.3492022862886328e-14</v>
+      </c>
+      <c r="G10">
+        <v>0.0</v>
+      </c>
+      <c r="H10">
+        <v>0.1446935496898365</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>-0.9921377386601338</v>
+      </c>
+      <c r="C11">
+        <v>0.0</v>
+      </c>
+      <c r="D11">
+        <v>-0.5204572812941508</v>
+      </c>
+      <c r="E11">
+        <v>-0.6168642282878078</v>
+      </c>
+      <c r="F11">
+        <v>1.3466694517385076e-14</v>
+      </c>
+      <c r="G11">
+        <v>0.0</v>
+      </c>
+      <c r="H11">
+        <v>0.12093144802170196</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>-0.931317131703341</v>
+      </c>
+      <c r="C12">
+        <v>0.0</v>
+      </c>
+      <c r="D12">
+        <v>-0.4780823352039434</v>
+      </c>
+      <c r="E12">
+        <v>-0.55652563000766</v>
+      </c>
+      <c r="F12">
+        <v>1.3412000973304146e-14</v>
+      </c>
+      <c r="G12">
+        <v>0.0</v>
+      </c>
+      <c r="H12">
+        <v>0.0998197529172211</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>-0.8688979012157383</v>
+      </c>
+      <c r="C13">
+        <v>0.0</v>
+      </c>
+      <c r="D13">
+        <v>-0.4491432070574239</v>
+      </c>
+      <c r="E13">
+        <v>-0.5118835184227113</v>
+      </c>
+      <c r="F13">
+        <v>1.3332628271158423e-14</v>
+      </c>
+      <c r="G13">
+        <v>0.0</v>
+      </c>
+      <c r="H13">
+        <v>0.08122018743975679</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>-0.8077995380727567</v>
+      </c>
+      <c r="C14">
+        <v>0.0</v>
+      </c>
+      <c r="D14">
+        <v>-0.42862347099201664</v>
+      </c>
+      <c r="E14">
+        <v>-0.4777426740355558</v>
+      </c>
+      <c r="F14">
+        <v>1.323281052728338e-14</v>
+      </c>
+      <c r="G14">
+        <v>0.0</v>
+      </c>
+      <c r="H14">
+        <v>0.06496131838760731</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>-0.748840312416389</v>
+      </c>
+      <c r="C15">
+        <v>0.0</v>
+      </c>
+      <c r="D15">
+        <v>-0.4131736946282153</v>
+      </c>
+      <c r="E15">
+        <v>-0.45057174710644904</v>
+      </c>
+      <c r="F15">
+        <v>1.3116338666312405e-14</v>
+      </c>
+      <c r="G15">
+        <v>0.0</v>
+      </c>
+      <c r="H15">
+        <v>0.05085802283126942</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>-0.6921339810602142</v>
+      </c>
+      <c r="C16">
+        <v>0.0</v>
+      </c>
+      <c r="D16">
+        <v>-0.40051669219830294</v>
+      </c>
+      <c r="E16">
+        <v>-0.427914314394589</v>
+      </c>
+      <c r="F16">
+        <v>1.2986577207574162e-14</v>
+      </c>
+      <c r="G16">
+        <v>0.0</v>
+      </c>
+      <c r="H16">
+        <v>0.038721943535952465</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>-0.6376112097334126</v>
+      </c>
+      <c r="C17">
+        <v>0.0</v>
+      </c>
+      <c r="D17">
+        <v>-0.38910425750697364</v>
+      </c>
+      <c r="E17">
+        <v>-0.40804913786530783</v>
+      </c>
+      <c r="F17">
+        <v>1.2846486722289322e-14</v>
+      </c>
+      <c r="G17">
+        <v>0.0</v>
+      </c>
+      <c r="H17">
+        <v>0.028367498022024082</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>-0.5851956049270015</v>
+      </c>
+      <c r="C18">
+        <v>0.0</v>
+      </c>
+      <c r="D18">
+        <v>-0.37790515148182624</v>
+      </c>
+      <c r="E18">
+        <v>-0.38978034641269066</v>
+      </c>
+      <c r="F18">
+        <v>1.2698650042513726e-14</v>
+      </c>
+      <c r="G18">
+        <v>0.0</v>
+      </c>
+      <c r="H18">
+        <v>0.01961552912300906</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>-0.5348503251242726</v>
+      </c>
+      <c r="C19">
+        <v>0.0</v>
+      </c>
+      <c r="D19">
+        <v>-0.3662630979125017</v>
+      </c>
+      <c r="E19">
+        <v>-0.3722967723993606</v>
+      </c>
+      <c r="F19">
+        <v>1.2545300696393843e-14</v>
+      </c>
+      <c r="G19">
+        <v>0.0</v>
+      </c>
+      <c r="H19">
+        <v>0.012295576831407232</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>-0.48657969434858706</v>
+      </c>
+      <c r="C20">
+        <v>0.0</v>
+      </c>
+      <c r="D20">
+        <v>-0.35379549635818497</v>
+      </c>
+      <c r="E20">
+        <v>-0.3550714206232398</v>
+      </c>
+      <c r="F20">
+        <v>1.2388352375174012e-14</v>
+      </c>
+      <c r="G20">
+        <v>0.0</v>
+      </c>
+      <c r="H20">
+        <v>0.00624726656368428</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>-0.44041765856436416</v>
+      </c>
+      <c r="C21">
+        <v>0.0</v>
+      </c>
+      <c r="D21">
+        <v>-0.3403183431064198</v>
+      </c>
+      <c r="E21">
+        <v>-0.3377867288833952</v>
+      </c>
+      <c r="F21">
+        <v>1.2229428513066768e-14</v>
+      </c>
+      <c r="G21">
+        <v>0.0</v>
+      </c>
+      <c r="H21">
+        <v>0.0013210919840288618</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>-3.452818634558829</v>
+      </c>
+      <c r="C2">
+        <v>0.0</v>
+      </c>
+      <c r="D2">
+        <v>-1.0</v>
+      </c>
+      <c r="E2">
+        <v>-0.6724381448767068</v>
+      </c>
+      <c r="F2">
+        <v>-8.622736026215812e-15</v>
+      </c>
+      <c r="G2">
+        <v>0.4586028719414287</v>
+      </c>
+      <c r="H2">
+        <v>-0.29161085716791146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>-2.247026625155925</v>
+      </c>
+      <c r="C3">
+        <v>0.0</v>
+      </c>
+      <c r="D3">
+        <v>-1.0</v>
+      </c>
+      <c r="E3">
+        <v>-0.6754920439440939</v>
+      </c>
+      <c r="F3">
+        <v>-9.136479065758198e-15</v>
+      </c>
+      <c r="G3">
+        <v>0.2231931345543115</v>
+      </c>
+      <c r="H3">
+        <v>-0.33915754479466115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>-1.6205323788595911</v>
+      </c>
+      <c r="C4">
+        <v>0.0</v>
+      </c>
+      <c r="D4">
+        <v>-1.0</v>
+      </c>
+      <c r="E4">
+        <v>-0.691426733217315</v>
+      </c>
+      <c r="F4">
+        <v>-9.571849997976843e-15</v>
+      </c>
+      <c r="G4">
+        <v>0.17337718670339702</v>
+      </c>
+      <c r="H4">
+        <v>-0.335995537700286</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>-1.2672896844330854</v>
+      </c>
+      <c r="C5">
+        <v>0.0</v>
+      </c>
+      <c r="D5">
+        <v>-1.0</v>
+      </c>
+      <c r="E5">
+        <v>-0.7126190796009915</v>
+      </c>
+      <c r="F5">
+        <v>-9.933327023769615e-15</v>
+      </c>
+      <c r="G5">
+        <v>0.13606624062531958</v>
+      </c>
+      <c r="H5">
+        <v>-0.3194967604267933</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>-1.0342703989673772</v>
+      </c>
+      <c r="C6">
+        <v>0.0</v>
+      </c>
+      <c r="D6">
+        <v>-0.9999999999999999</v>
+      </c>
+      <c r="E6">
+        <v>-0.7369490309361169</v>
+      </c>
+      <c r="F6">
+        <v>-1.022616636842296e-14</v>
+      </c>
+      <c r="G6">
+        <v>0.10077323633482829</v>
+      </c>
+      <c r="H6">
+        <v>-0.29755420498113316</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>-0.8446534793547625</v>
+      </c>
+      <c r="C7">
+        <v>0.0</v>
+      </c>
+      <c r="D7">
+        <v>-0.9999999999999998</v>
+      </c>
+      <c r="E7">
+        <v>-0.7634137716033644</v>
+      </c>
+      <c r="F7">
+        <v>-1.0456084872095713e-14</v>
+      </c>
+      <c r="G7">
+        <v>2.063782970431291</v>
+      </c>
+      <c r="H7">
+        <v>-0.27236297336874193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>-0.658731170928402</v>
+      </c>
+      <c r="C8">
+        <v>0.0</v>
+      </c>
+      <c r="D8">
+        <v>1.0018733440900165</v>
+      </c>
+      <c r="E8">
+        <v>1.2106152491219961</v>
+      </c>
+      <c r="F8">
+        <v>-1.062900957022899e-14</v>
+      </c>
+      <c r="G8">
+        <v>0.0</v>
+      </c>
+      <c r="H8">
+        <v>-0.2449613808818727</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>0.24680905953848012</v>
+      </c>
+      <c r="C9">
+        <v>0.0</v>
+      </c>
+      <c r="D9">
+        <v>1.0184154340611102</v>
+      </c>
+      <c r="E9">
+        <v>1.1997204343437655</v>
+      </c>
+      <c r="F9">
+        <v>-1.0750883791106619e-14</v>
+      </c>
+      <c r="G9">
+        <v>0.0</v>
+      </c>
+      <c r="H9">
+        <v>-0.2161313684701008</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>0.7263675921425261</v>
+      </c>
+      <c r="C10">
+        <v>0.0</v>
+      </c>
+      <c r="D10">
+        <v>0.81565738323619</v>
+      </c>
+      <c r="E10">
+        <v>0.9711631474977502</v>
+      </c>
+      <c r="F10">
+        <v>-1.0827520518668891e-14</v>
+      </c>
+      <c r="G10">
+        <v>0.0</v>
+      </c>
+      <c r="H10">
+        <v>-0.18772319729265108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>0.8982855718353072</v>
+      </c>
+      <c r="C11">
+        <v>0.0</v>
+      </c>
+      <c r="D11">
+        <v>0.6586264335291755</v>
+      </c>
+      <c r="E11">
+        <v>0.7905470542901599</v>
+      </c>
+      <c r="F11">
+        <v>-1.0864494887789338e-14</v>
+      </c>
+      <c r="G11">
+        <v>0.0</v>
+      </c>
+      <c r="H11">
+        <v>-0.1610106683164092</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>0.925522701303046</v>
+      </c>
+      <c r="C12">
+        <v>0.0</v>
+      </c>
+      <c r="D12">
+        <v>0.55700364670584</v>
+      </c>
+      <c r="E12">
+        <v>0.6677310999777977</v>
+      </c>
+      <c r="F12">
+        <v>-1.0867068720641567e-14</v>
+      </c>
+      <c r="G12">
+        <v>0.0</v>
+      </c>
+      <c r="H12">
+        <v>-0.1365906107359131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>0.89464697633588</v>
+      </c>
+      <c r="C13">
+        <v>0.0</v>
+      </c>
+      <c r="D13">
+        <v>0.49186589094681055</v>
+      </c>
+      <c r="E13">
+        <v>0.5837699848463282</v>
+      </c>
+      <c r="F13">
+        <v>-1.0840140977964427e-14</v>
+      </c>
+      <c r="G13">
+        <v>0.0</v>
+      </c>
+      <c r="H13">
+        <v>-0.11464720511777458</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>0.8432769678272422</v>
+      </c>
+      <c r="C14">
+        <v>0.0</v>
+      </c>
+      <c r="D14">
+        <v>0.44886422568029916</v>
+      </c>
+      <c r="E14">
+        <v>0.524200293667064</v>
+      </c>
+      <c r="F14">
+        <v>-1.0788218883580525e-14</v>
+      </c>
+      <c r="G14">
+        <v>0.0</v>
+      </c>
+      <c r="H14">
+        <v>-0.09515749882355043</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>0.78628418943233</v>
+      </c>
+      <c r="C15">
+        <v>0.0</v>
+      </c>
+      <c r="D15">
+        <v>0.41930366274779857</v>
+      </c>
+      <c r="E15">
+        <v>0.4801724794746719</v>
+      </c>
+      <c r="F15">
+        <v>-1.0715405280632185e-14</v>
+      </c>
+      <c r="G15">
+        <v>0.0</v>
+      </c>
+      <c r="H15">
+        <v>-0.07800296479348615</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>0.7291287172948269</v>
+      </c>
+      <c r="C16">
+        <v>0.0</v>
+      </c>
+      <c r="D16">
+        <v>0.397940575159894</v>
+      </c>
+      <c r="E16">
+        <v>0.4462730444426526</v>
+      </c>
+      <c r="F16">
+        <v>-1.0625398492454296e-14</v>
+      </c>
+      <c r="G16">
+        <v>0.0</v>
+      </c>
+      <c r="H16">
+        <v>-0.06302357283899464</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>0.6736313551308283</v>
+      </c>
+      <c r="C17">
+        <v>0.0</v>
+      </c>
+      <c r="D17">
+        <v>0.3814757938432244</v>
+      </c>
+      <c r="E17">
+        <v>0.41902976580951823</v>
+      </c>
+      <c r="F17">
+        <v>-1.0521501591329904e-14</v>
+      </c>
+      <c r="G17">
+        <v>0.0</v>
+      </c>
+      <c r="H17">
+        <v>-0.05004343869535837</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>0.6202949310831299</v>
+      </c>
+      <c r="C18">
+        <v>0.0</v>
+      </c>
+      <c r="D18">
+        <v>0.36775375988496617</v>
+      </c>
+      <c r="E18">
+        <v>0.39611715994926344</v>
+      </c>
+      <c r="F18">
+        <v>-1.0406638528335869e-14</v>
+      </c>
+      <c r="G18">
+        <v>0.0</v>
+      </c>
+      <c r="H18">
+        <v>-0.03888338257389103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>0.5691926844693456</v>
+      </c>
+      <c r="C19">
+        <v>0.0</v>
+      </c>
+      <c r="D19">
+        <v>0.3553437873111153</v>
+      </c>
+      <c r="E19">
+        <v>0.37594124158524256</v>
+      </c>
+      <c r="F19">
+        <v>-1.0283375052422972e-14</v>
+      </c>
+      <c r="G19">
+        <v>0.0</v>
+      </c>
+      <c r="H19">
+        <v>-0.029367464426564148</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>0.5202897774842203</v>
+      </c>
+      <c r="C20">
+        <v>0.0</v>
+      </c>
+      <c r="D20">
+        <v>0.3433055700353689</v>
+      </c>
+      <c r="E20">
+        <v>0.3574070387942728</v>
+      </c>
+      <c r="F20">
+        <v>-1.0153942753091595e-14</v>
+      </c>
+      <c r="G20">
+        <v>0.0</v>
+      </c>
+      <c r="H20">
+        <v>-0.021326604155422448</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>0.4735483412482155</v>
+      </c>
+      <c r="C21">
+        <v>0.0</v>
+      </c>
+      <c r="D21">
+        <v>0.33104442188153804</v>
+      </c>
+      <c r="E21">
+        <v>0.3397749693612522</v>
+      </c>
+      <c r="F21">
+        <v>-1.0020264905286315e-14</v>
+      </c>
+      <c r="G21">
+        <v>0.0</v>
+      </c>
+      <c r="H21">
+        <v>-0.014600660752960591</v>
       </c>
     </row>
   </sheetData>

--- a/irf/irf/Paper IRFs.xlsx
+++ b/irf/irf/Paper IRFs.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="101">
   <si>
     <t>t</t>
   </si>
@@ -316,6 +316,24 @@
   </si>
   <si>
     <t>2026-03-02T18:56:18.708</t>
+  </si>
+  <si>
+    <t>2026-03-05T15:15:56.318</t>
+  </si>
+  <si>
+    <t>2026-03-06T12:20:08.04</t>
+  </si>
+  <si>
+    <t>2026-03-06T12:20:10.938</t>
+  </si>
+  <si>
+    <t>2026-03-06T12:20:14.589</t>
+  </si>
+  <si>
+    <t>2026-03-06T12:20:15.539</t>
+  </si>
+  <si>
+    <t>2026-03-06T12:22:17.882</t>
   </si>
 </sst>
 </file>
@@ -699,7 +717,7 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1066,7 +1084,7 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1328,7 +1346,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1336,22 +1354,22 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>8.102500031716207</v>
+        <v>8.10250003171621</v>
       </c>
       <c r="C2">
         <v>0.0</v>
       </c>
       <c r="D2">
-        <v>-0.9999999999999997</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="E2">
-        <v>-1.329654503413945</v>
+        <v>-1.3296545034139453</v>
       </c>
       <c r="F2">
-        <v>1.1945048918812522e-14</v>
+        <v>1.1945048918812519e-14</v>
       </c>
       <c r="G2">
-        <v>-3.200818256209439</v>
+        <v>-3.20081825620944e16</v>
       </c>
       <c r="H2">
         <v>0.30026943656535576</v>
@@ -1362,25 +1380,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.792490064412832</v>
+        <v>3.7924900644128283</v>
       </c>
       <c r="C3">
         <v>0.0</v>
       </c>
       <c r="D3">
-        <v>-0.9999999999999998</v>
+        <v>-1.0</v>
       </c>
       <c r="E3">
-        <v>-1.315085512368188</v>
+        <v>-1.3150855123681888</v>
       </c>
       <c r="F3">
-        <v>1.236786245210933e-14</v>
+        <v>1.2367862452109334e-14</v>
       </c>
       <c r="G3">
-        <v>-0.8007358613175596</v>
+        <v>-8.007358613175597e15</v>
       </c>
       <c r="H3">
-        <v>0.341324272834796</v>
+        <v>0.3413242728347961</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1388,25 +1406,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.5356822530888818</v>
+        <v>1.535682253088888</v>
       </c>
       <c r="C4">
         <v>0.0</v>
       </c>
       <c r="D4">
-        <v>-0.9999999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="E4">
-        <v>-1.2870123987247313</v>
+        <v>-1.2870123987247315</v>
       </c>
       <c r="F4">
-        <v>1.2712130219558677e-14</v>
+        <v>1.2712130219558681e-14</v>
       </c>
       <c r="G4">
-        <v>-0.6225725146161963</v>
+        <v>-6.225725146161975e15</v>
       </c>
       <c r="H4">
-        <v>0.3262395395060162</v>
+        <v>0.32623953950601636</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1414,25 +1432,25 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.31441751547674085</v>
+        <v>0.3144175154767359</v>
       </c>
       <c r="C5">
         <v>0.0</v>
       </c>
       <c r="D5">
-        <v>-0.9999999999999998</v>
+        <v>-1.0</v>
       </c>
       <c r="E5">
-        <v>-1.2554591177135284</v>
+        <v>-1.2554591177135286</v>
       </c>
       <c r="F5">
-        <v>1.2984205210219286e-14</v>
+        <v>1.2984205210219291e-14</v>
       </c>
       <c r="G5">
-        <v>-0.4304117562920385</v>
+        <v>-4.3041175629203765e15</v>
       </c>
       <c r="H5">
-        <v>0.29717263763957846</v>
+        <v>0.2971726376395785</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1440,25 +1458,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>-0.37145665129207356</v>
+        <v>-0.3714566512920711</v>
       </c>
       <c r="C6">
         <v>0.0</v>
       </c>
       <c r="D6">
-        <v>-1.0</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="E6">
         <v>-1.2237625435542734</v>
       </c>
       <c r="F6">
-        <v>1.3190713735165675e-14</v>
+        <v>1.3190713735165678e-14</v>
       </c>
       <c r="G6">
-        <v>-0.3107196037060323</v>
+        <v>-3.1071960370603305e15</v>
       </c>
       <c r="H6">
-        <v>0.26450237048057795</v>
+        <v>0.2645023704805781</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1466,25 +1484,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>-0.7682647916323522</v>
+        <v>-0.7682647916323554</v>
       </c>
       <c r="C7">
         <v>0.0</v>
       </c>
       <c r="D7">
-        <v>-0.9999999999999999</v>
+        <v>-1.0</v>
       </c>
       <c r="E7">
-        <v>-1.1934427321679302</v>
+        <v>-1.1934427321679304</v>
       </c>
       <c r="F7">
-        <v>1.3338330603505361e-14</v>
+        <v>1.3338330603505364e-14</v>
       </c>
       <c r="G7">
-        <v>-0.231532170537758</v>
+        <v>-2.315321705377577e15</v>
       </c>
       <c r="H7">
-        <v>0.23168373759608402</v>
+        <v>0.23168373759608413</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1492,25 +1510,25 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>-0.9983762771240431</v>
+        <v>-0.9983762771240439</v>
       </c>
       <c r="C8">
         <v>0.0</v>
       </c>
       <c r="D8">
-        <v>-0.8228559440075245</v>
+        <v>-0.8228559440075246</v>
       </c>
       <c r="E8">
         <v>-0.9881766315918266</v>
       </c>
       <c r="F8">
-        <v>1.3433608185646603e-14</v>
+        <v>1.3433608185646608e-14</v>
       </c>
       <c r="G8">
         <v>0.0</v>
       </c>
       <c r="H8">
-        <v>0.20029060488666367</v>
+        <v>0.20029060488666384</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1518,25 +1536,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>-1.0615234494165058</v>
+        <v>-1.061523449416503</v>
       </c>
       <c r="C9">
         <v>0.0</v>
       </c>
       <c r="D9">
-        <v>-0.6802281125838165</v>
+        <v>-0.6802281125838158</v>
       </c>
       <c r="E9">
-        <v>-0.8199746353671349</v>
+        <v>-0.8199746353671341</v>
       </c>
       <c r="F9">
-        <v>1.3482850291698822e-14</v>
+        <v>1.3482850291698827e-14</v>
       </c>
       <c r="G9">
         <v>0.0</v>
       </c>
       <c r="H9">
-        <v>0.17117303992477478</v>
+        <v>0.1711730399247749</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1544,25 +1562,25 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>-1.0428589933721049</v>
+        <v>-1.0428589933721073</v>
       </c>
       <c r="C10">
         <v>0.0</v>
       </c>
       <c r="D10">
-        <v>-0.5839658177105909</v>
+        <v>-0.5839658177105906</v>
       </c>
       <c r="E10">
-        <v>-0.7007626576002115</v>
+        <v>-0.7007626576002113</v>
       </c>
       <c r="F10">
-        <v>1.3492022862886328e-14</v>
+        <v>1.349202286288633e-14</v>
       </c>
       <c r="G10">
         <v>0.0</v>
       </c>
       <c r="H10">
-        <v>0.1446935496898365</v>
+        <v>0.14469354968983653</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1570,25 +1588,25 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>-0.9921377386601338</v>
+        <v>-0.9921377386601307</v>
       </c>
       <c r="C11">
         <v>0.0</v>
       </c>
       <c r="D11">
-        <v>-0.5204572812941508</v>
+        <v>-0.5204572812941505</v>
       </c>
       <c r="E11">
-        <v>-0.6168642282878078</v>
+        <v>-0.6168642282878074</v>
       </c>
       <c r="F11">
-        <v>1.3466694517385076e-14</v>
+        <v>1.3466694517385083e-14</v>
       </c>
       <c r="G11">
         <v>0.0</v>
       </c>
       <c r="H11">
-        <v>0.12093144802170196</v>
+        <v>0.12093144802170194</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1596,19 +1614,19 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>-0.931317131703341</v>
+        <v>-0.9313171317033456</v>
       </c>
       <c r="C12">
         <v>0.0</v>
       </c>
       <c r="D12">
-        <v>-0.4780823352039434</v>
+        <v>-0.478082335203944</v>
       </c>
       <c r="E12">
-        <v>-0.55652563000766</v>
+        <v>-0.5565256300076604</v>
       </c>
       <c r="F12">
-        <v>1.3412000973304146e-14</v>
+        <v>1.3412000973304154e-14</v>
       </c>
       <c r="G12">
         <v>0.0</v>
@@ -1622,25 +1640,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>-0.8688979012157383</v>
+        <v>-0.8688979012157352</v>
       </c>
       <c r="C13">
         <v>0.0</v>
       </c>
       <c r="D13">
-        <v>-0.4491432070574239</v>
+        <v>-0.4491432070574237</v>
       </c>
       <c r="E13">
-        <v>-0.5118835184227113</v>
+        <v>-0.5118835184227111</v>
       </c>
       <c r="F13">
-        <v>1.3332628271158423e-14</v>
+        <v>1.3332628271158425e-14</v>
       </c>
       <c r="G13">
         <v>0.0</v>
       </c>
       <c r="H13">
-        <v>0.08122018743975679</v>
+        <v>0.0812201874397568</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1648,7 +1666,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>-0.8077995380727567</v>
+        <v>-0.8077995380727581</v>
       </c>
       <c r="C14">
         <v>0.0</v>
@@ -1660,13 +1678,13 @@
         <v>-0.4777426740355558</v>
       </c>
       <c r="F14">
-        <v>1.323281052728338e-14</v>
+        <v>1.3232810527283388e-14</v>
       </c>
       <c r="G14">
         <v>0.0</v>
       </c>
       <c r="H14">
-        <v>0.06496131838760731</v>
+        <v>0.06496131838760733</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1674,25 +1692,25 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>-0.748840312416389</v>
+        <v>-0.7488403124163898</v>
       </c>
       <c r="C15">
         <v>0.0</v>
       </c>
       <c r="D15">
-        <v>-0.4131736946282153</v>
+        <v>-0.4131736946282152</v>
       </c>
       <c r="E15">
-        <v>-0.45057174710644904</v>
+        <v>-0.4505717471064489</v>
       </c>
       <c r="F15">
-        <v>1.3116338666312405e-14</v>
+        <v>1.3116338666312411e-14</v>
       </c>
       <c r="G15">
         <v>0.0</v>
       </c>
       <c r="H15">
-        <v>0.05085802283126942</v>
+        <v>0.05085802283126939</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1700,25 +1718,25 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>-0.6921339810602142</v>
+        <v>-0.6921339810602125</v>
       </c>
       <c r="C16">
         <v>0.0</v>
       </c>
       <c r="D16">
-        <v>-0.40051669219830294</v>
+        <v>-0.4005166921983027</v>
       </c>
       <c r="E16">
-        <v>-0.427914314394589</v>
+        <v>-0.42791431439458877</v>
       </c>
       <c r="F16">
-        <v>1.2986577207574162e-14</v>
+        <v>1.2986577207574167e-14</v>
       </c>
       <c r="G16">
         <v>0.0</v>
       </c>
       <c r="H16">
-        <v>0.038721943535952465</v>
+        <v>0.03872194353595246</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1726,25 +1744,25 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>-0.6376112097334126</v>
+        <v>-0.6376112097334125</v>
       </c>
       <c r="C17">
         <v>0.0</v>
       </c>
       <c r="D17">
-        <v>-0.38910425750697364</v>
+        <v>-0.38910425750697375</v>
       </c>
       <c r="E17">
-        <v>-0.40804913786530783</v>
+        <v>-0.408049137865308</v>
       </c>
       <c r="F17">
-        <v>1.2846486722289322e-14</v>
+        <v>1.284648672228933e-14</v>
       </c>
       <c r="G17">
         <v>0.0</v>
       </c>
       <c r="H17">
-        <v>0.028367498022024082</v>
+        <v>0.028367498022024113</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1752,25 +1770,25 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>-0.5851956049270015</v>
+        <v>-0.5851956049270024</v>
       </c>
       <c r="C18">
         <v>0.0</v>
       </c>
       <c r="D18">
-        <v>-0.37790515148182624</v>
+        <v>-0.3779051514818267</v>
       </c>
       <c r="E18">
-        <v>-0.38978034641269066</v>
+        <v>-0.38978034641269116</v>
       </c>
       <c r="F18">
-        <v>1.2698650042513726e-14</v>
+        <v>1.2698650042513736e-14</v>
       </c>
       <c r="G18">
         <v>0.0</v>
       </c>
       <c r="H18">
-        <v>0.01961552912300906</v>
+        <v>0.019615529123009106</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1778,25 +1796,25 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>-0.5348503251242726</v>
+        <v>-0.5348503251242709</v>
       </c>
       <c r="C19">
         <v>0.0</v>
       </c>
       <c r="D19">
-        <v>-0.3662630979125017</v>
+        <v>-0.3662630979125019</v>
       </c>
       <c r="E19">
-        <v>-0.3722967723993606</v>
+        <v>-0.37229677239936076</v>
       </c>
       <c r="F19">
-        <v>1.2545300696393843e-14</v>
+        <v>1.254530069639385e-14</v>
       </c>
       <c r="G19">
         <v>0.0</v>
       </c>
       <c r="H19">
-        <v>0.012295576831407232</v>
+        <v>0.012295576831407242</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1804,25 +1822,25 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>-0.48657969434858706</v>
+        <v>-0.4865796943485886</v>
       </c>
       <c r="C20">
         <v>0.0</v>
       </c>
       <c r="D20">
-        <v>-0.35379549635818497</v>
+        <v>-0.3537954963581855</v>
       </c>
       <c r="E20">
-        <v>-0.3550714206232398</v>
+        <v>-0.3550714206232403</v>
       </c>
       <c r="F20">
-        <v>1.2388352375174012e-14</v>
+        <v>1.2388352375174015e-14</v>
       </c>
       <c r="G20">
         <v>0.0</v>
       </c>
       <c r="H20">
-        <v>0.00624726656368428</v>
+        <v>0.006247266563684284</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1830,25 +1848,25 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>-0.44041765856436416</v>
+        <v>-0.44041765856436393</v>
       </c>
       <c r="C21">
         <v>0.0</v>
       </c>
       <c r="D21">
-        <v>-0.3403183431064198</v>
+        <v>-0.3403183431064202</v>
       </c>
       <c r="E21">
-        <v>-0.3377867288833952</v>
+        <v>-0.33778672888339567</v>
       </c>
       <c r="F21">
-        <v>1.2229428513066768e-14</v>
+        <v>1.2229428513066773e-14</v>
       </c>
       <c r="G21">
         <v>0.0</v>
       </c>
       <c r="H21">
-        <v>0.0013210919840288618</v>
+        <v>0.0013210919840288976</v>
       </c>
     </row>
   </sheetData>
@@ -3014,7 +3032,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:11">

--- a/irf/irf/Paper IRFs.xlsx
+++ b/irf/irf/Paper IRFs.xlsx
@@ -20,6 +20,7 @@
     <sheet name="interest_rate_peg_with_only_FG_" r:id="rId8" sheetId="5"/>
     <sheet name="IRF_rate_peg_with_permanent_liq" r:id="rId9" sheetId="6"/>
     <sheet name="Interest_rate_peg_IRF_Policy_ra" r:id="rId10" sheetId="7"/>
+    <sheet name="interest_rate_peg_with_contempo" r:id="rId11" sheetId="8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="135">
   <si>
     <t>t</t>
   </si>
@@ -334,6 +335,108 @@
   </si>
   <si>
     <t>2026-03-06T12:22:17.882</t>
+  </si>
+  <si>
+    <t>2026-03-07T11:56:55.99</t>
+  </si>
+  <si>
+    <t>2026-03-07T11:58:32.214</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:02:41.312</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:05:50.853</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:12:42.23</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:16:33.496</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:17:22.722</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:19:31.92</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:23:42.977</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:23:57.312</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:36:34.811</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:36:38.972</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:36:42.408</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:36:45.871</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:36:49.381</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:37:38.808</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:37:42.813</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:37:46.476</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:37:49.892</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:37:53.234</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:37:56.683</t>
+  </si>
+  <si>
+    <t>Inflation (obs_corepce)</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:47:44.336</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:47:48.58</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:47:51.984</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:47:55.415</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:47:58.966</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:48:02.715</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:50:22.615</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:50:26.67</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:50:30.115</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:50:33.469</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:50:36.951</t>
+  </si>
+  <si>
+    <t>2026-03-07T12:50:40.745</t>
   </si>
 </sst>
 </file>
@@ -717,7 +820,7 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -725,16 +828,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.0256250079290514</v>
+        <v>1.5232200986747049</v>
       </c>
       <c r="C2">
         <v>0.0</v>
       </c>
       <c r="D2">
-        <v>-0.9999999999999997</v>
+        <v>-1.0</v>
       </c>
       <c r="E2">
-        <v>0.30026943656535576</v>
+        <v>0.06041691720689047</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -742,16 +845,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.9737475240322597</v>
+        <v>2.3275213113536504</v>
       </c>
       <c r="C3">
         <v>0.0</v>
       </c>
       <c r="D3">
-        <v>-0.9999999999999998</v>
+        <v>-0.9999999999999999</v>
       </c>
       <c r="E3">
-        <v>0.341324272834796</v>
+        <v>0.0693641485259583</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -759,16 +862,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.3576680873044795</v>
+        <v>2.7075610215628734</v>
       </c>
       <c r="C4">
         <v>0.0</v>
       </c>
       <c r="D4">
-        <v>-0.9999999999999999</v>
+        <v>-1.0</v>
       </c>
       <c r="E4">
-        <v>0.3262395395060162</v>
+        <v>0.06660856356307546</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -776,16 +879,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3.436272466173665</v>
+        <v>2.831397136820782</v>
       </c>
       <c r="C5">
         <v>0.0</v>
       </c>
       <c r="D5">
-        <v>-0.9999999999999998</v>
+        <v>-0.9999999999999997</v>
       </c>
       <c r="E5">
-        <v>0.29717263763957846</v>
+        <v>0.06087128567327553</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -793,7 +896,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>3.343408303350647</v>
+        <v>2.7970924109183697</v>
       </c>
       <c r="C6">
         <v>0.0</v>
@@ -802,7 +905,7 @@
         <v>-1.0</v>
       </c>
       <c r="E6">
-        <v>0.26450237048057795</v>
+        <v>0.054429968855103955</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -810,7 +913,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>3.1513421054425583</v>
+        <v>2.663931788752943</v>
       </c>
       <c r="C7">
         <v>0.0</v>
@@ -819,7 +922,7 @@
         <v>-0.9999999999999999</v>
       </c>
       <c r="E7">
-        <v>0.23168373759608402</v>
+        <v>0.04808325260956113</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -827,16 +930,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2.9017480361615475</v>
+        <v>2.469605702041349</v>
       </c>
       <c r="C8">
         <v>0.0</v>
       </c>
       <c r="D8">
-        <v>-0.8228559440075245</v>
+        <v>-0.8228127749890541</v>
       </c>
       <c r="E8">
-        <v>0.20029060488666367</v>
+        <v>0.042202449635029365</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -844,16 +947,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2.636367173807421</v>
+        <v>2.2524750766126327</v>
       </c>
       <c r="C9">
         <v>0.0</v>
       </c>
       <c r="D9">
-        <v>-0.6802281125838165</v>
+        <v>-0.6707001770180403</v>
       </c>
       <c r="E9">
-        <v>0.17117303992477478</v>
+        <v>0.03698335598536416</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -861,16 +964,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2.375652425464394</v>
+        <v>2.0340427981566163</v>
       </c>
       <c r="C10">
         <v>0.0</v>
       </c>
       <c r="D10">
-        <v>-0.5839658177105909</v>
+        <v>-0.5587090606627749</v>
       </c>
       <c r="E10">
-        <v>0.1446935496898365</v>
+        <v>0.0324996672427466</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -878,16 +981,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2.12761799079936</v>
+        <v>1.8246676750584552</v>
       </c>
       <c r="C11">
         <v>0.0</v>
       </c>
       <c r="D11">
-        <v>-0.5204572812941508</v>
+        <v>-0.4769893176013968</v>
       </c>
       <c r="E11">
-        <v>0.12093144802170196</v>
+        <v>0.028749943697603413</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -895,16 +998,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1.8947887078735237</v>
+        <v>1.628862652853758</v>
       </c>
       <c r="C12">
         <v>0.0</v>
       </c>
       <c r="D12">
-        <v>-0.4780823352039434</v>
+        <v>-0.41632872260205844</v>
       </c>
       <c r="E12">
-        <v>0.0998197529172211</v>
+        <v>0.025691668894171554</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -912,16 +1015,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.6775642325695883</v>
+        <v>1.448266074981068</v>
       </c>
       <c r="C13">
         <v>0.0</v>
       </c>
       <c r="D13">
-        <v>-0.4491432070574239</v>
+        <v>-0.37042230167751666</v>
       </c>
       <c r="E13">
-        <v>0.08122018743975679</v>
+        <v>0.023261957401227804</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -929,16 +1032,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1.4756143480513981</v>
+        <v>1.2831281565729924</v>
       </c>
       <c r="C14">
         <v>0.0</v>
       </c>
       <c r="D14">
-        <v>-0.42862347099201664</v>
+        <v>-0.335047453903922</v>
       </c>
       <c r="E14">
-        <v>0.06496131838760731</v>
+        <v>0.021389325778774195</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -946,16 +1049,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1.2884042699473002</v>
+        <v>1.13303129833586</v>
       </c>
       <c r="C15">
         <v>0.0</v>
       </c>
       <c r="D15">
-        <v>-0.4131736946282153</v>
+        <v>-0.3072821349529822</v>
       </c>
       <c r="E15">
-        <v>0.05085802283126942</v>
+        <v>0.020000313874025705</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -963,16 +1066,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>1.1153707746822454</v>
+        <v>0.9972391461047327</v>
       </c>
       <c r="C16">
         <v>0.0</v>
       </c>
       <c r="D16">
-        <v>-0.40051669219830294</v>
+        <v>-0.28503110616386534</v>
       </c>
       <c r="E16">
-        <v>0.038721943535952465</v>
+        <v>0.019023255314255645</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -980,16 +1083,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.9559679722488909</v>
+        <v>0.874868958448911</v>
       </c>
       <c r="C17">
         <v>0.0</v>
       </c>
       <c r="D17">
-        <v>-0.38910425750697364</v>
+        <v>-0.2667552267164717</v>
       </c>
       <c r="E17">
-        <v>0.028367498022024082</v>
+        <v>0.018390444769442068</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -997,16 +1100,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.8096690710171393</v>
+        <v>0.7649796730044779</v>
       </c>
       <c r="C18">
         <v>0.0</v>
       </c>
       <c r="D18">
-        <v>-0.37790515148182624</v>
+        <v>-0.2513110442691379</v>
       </c>
       <c r="E18">
-        <v>0.01961552912300906</v>
+        <v>0.018039361618583903</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1014,16 +1117,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.6759564897360697</v>
+        <v>0.6666190517958762</v>
       </c>
       <c r="C19">
         <v>0.0</v>
       </c>
       <c r="D19">
-        <v>-0.3662630979125017</v>
+        <v>-0.23784872058975948</v>
       </c>
       <c r="E19">
-        <v>0.012295576831407232</v>
+        <v>0.017913306517494103</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1031,16 +1134,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.5543115661489215</v>
+        <v>0.5788502958563876</v>
       </c>
       <c r="C20">
         <v>0.0</v>
       </c>
       <c r="D20">
-        <v>-0.35379549635818497</v>
+        <v>-0.2257419438903663</v>
       </c>
       <c r="E20">
-        <v>0.00624726656368428</v>
+        <v>0.01796165415152384</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1048,16 +1151,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.44420715150782886</v>
+        <v>0.5007678159601359</v>
       </c>
       <c r="C21">
         <v>0.0</v>
       </c>
       <c r="D21">
-        <v>-0.3403183431064198</v>
+        <v>-0.21453667352964648</v>
       </c>
       <c r="E21">
-        <v>0.0013210919840288618</v>
+        <v>0.01813984665888384</v>
       </c>
     </row>
   </sheetData>
@@ -1908,7 +2011,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1916,7 +2019,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>-3.452818634558829</v>
+        <v>0.010611389448048958</v>
       </c>
       <c r="C2">
         <v>0.0</v>
@@ -1925,16 +2028,16 @@
         <v>-1.0</v>
       </c>
       <c r="E2">
-        <v>-0.6724381448767068</v>
+        <v>0.01691563407698074</v>
       </c>
       <c r="F2">
-        <v>-8.622736026215812e-15</v>
+        <v>4.5087075869680536e-17</v>
       </c>
       <c r="G2">
-        <v>0.4586028719414287</v>
+        <v>-0.1644474583019147</v>
       </c>
       <c r="H2">
-        <v>-0.29161085716791146</v>
+        <v>-0.014925831077689883</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1942,7 +2045,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>-2.247026625155925</v>
+        <v>-0.03186432239033837</v>
       </c>
       <c r="C3">
         <v>0.0</v>
@@ -1951,16 +2054,16 @@
         <v>-1.0</v>
       </c>
       <c r="E3">
-        <v>-0.6754920439440939</v>
+        <v>-0.16045476866356317</v>
       </c>
       <c r="F3">
-        <v>-9.136479065758198e-15</v>
+        <v>-1.2006389061474226e-16</v>
       </c>
       <c r="G3">
-        <v>0.2231931345543115</v>
+        <v>-0.1817890425383521</v>
       </c>
       <c r="H3">
-        <v>-0.33915754479466115</v>
+        <v>-0.017866904525598144</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1968,7 +2071,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>-1.6205323788595911</v>
+        <v>-0.1307158788307793</v>
       </c>
       <c r="C4">
         <v>0.0</v>
@@ -1977,16 +2080,16 @@
         <v>-1.0</v>
       </c>
       <c r="E4">
-        <v>-0.691426733217315</v>
+        <v>-0.3962673948995753</v>
       </c>
       <c r="F4">
-        <v>-9.571849997976843e-15</v>
+        <v>-2.4823694109419566e-16</v>
       </c>
       <c r="G4">
-        <v>0.17337718670339702</v>
+        <v>-0.08260789907318522</v>
       </c>
       <c r="H4">
-        <v>-0.335995537700286</v>
+        <v>-0.018396958001933562</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1994,25 +2097,25 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>-1.2672896844330854</v>
+        <v>-0.2691110903402725</v>
       </c>
       <c r="C5">
         <v>0.0</v>
       </c>
       <c r="D5">
-        <v>-1.0</v>
+        <v>-1.0000000000000002</v>
       </c>
       <c r="E5">
-        <v>-0.7126190796009915</v>
+        <v>-0.5594916702932204</v>
       </c>
       <c r="F5">
-        <v>-9.933327023769615e-15</v>
+        <v>-3.4343469768482743e-16</v>
       </c>
       <c r="G5">
-        <v>0.13606624062531958</v>
+        <v>-0.015638695049281635</v>
       </c>
       <c r="H5">
-        <v>-0.3194967604267933</v>
+        <v>-0.01835118011039349</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2020,25 +2123,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>-1.0342703989673772</v>
+        <v>-0.3930452374105372</v>
       </c>
       <c r="C6">
         <v>0.0</v>
       </c>
       <c r="D6">
-        <v>-0.9999999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="E6">
-        <v>-0.7369490309361169</v>
+        <v>-0.6649870094715363</v>
       </c>
       <c r="F6">
-        <v>-1.022616636842296e-14</v>
+        <v>-4.096415612004622e-16</v>
       </c>
       <c r="G6">
-        <v>0.10077323633482829</v>
+        <v>0.02876402916085786</v>
       </c>
       <c r="H6">
-        <v>-0.29755420498113316</v>
+        <v>-0.01803263309496081</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2046,25 +2149,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>-0.8446534793547625</v>
+        <v>-0.4759843533789608</v>
       </c>
       <c r="C7">
         <v>0.0</v>
       </c>
       <c r="D7">
-        <v>-0.9999999999999998</v>
+        <v>-1.0</v>
       </c>
       <c r="E7">
-        <v>-0.7634137716033644</v>
+        <v>-0.7350899114635326</v>
       </c>
       <c r="F7">
-        <v>-1.0456084872095713e-14</v>
+        <v>-4.50718655276338e-16</v>
       </c>
       <c r="G7">
-        <v>2.063782970431291</v>
+        <v>1.091729446652716</v>
       </c>
       <c r="H7">
-        <v>-0.27236297336874193</v>
+        <v>-0.0174553977329448</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2072,25 +2175,25 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>-0.658731170928402</v>
+        <v>-0.509228971285405</v>
       </c>
       <c r="C8">
         <v>0.0</v>
       </c>
       <c r="D8">
-        <v>1.0018733440900165</v>
+        <v>0.03635145783199292</v>
       </c>
       <c r="E8">
-        <v>1.2106152491219961</v>
+        <v>0.25242038313511095</v>
       </c>
       <c r="F8">
-        <v>-1.062900957022899e-14</v>
+        <v>-4.703276363848557e-16</v>
       </c>
       <c r="G8">
         <v>0.0</v>
       </c>
       <c r="H8">
-        <v>-0.2449613808818727</v>
+        <v>-0.016599407800643395</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2098,25 +2201,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.24680905953848012</v>
+        <v>-0.1920202389789131</v>
       </c>
       <c r="C9">
         <v>0.0</v>
       </c>
       <c r="D9">
-        <v>1.0184154340611102</v>
+        <v>0.12921754417741121</v>
       </c>
       <c r="E9">
-        <v>1.1997204343437655</v>
+        <v>0.30989248609914577</v>
       </c>
       <c r="F9">
-        <v>-1.0750883791106619e-14</v>
+        <v>-4.718786361864179e-16</v>
       </c>
       <c r="G9">
         <v>0.0</v>
       </c>
       <c r="H9">
-        <v>-0.2161313684701008</v>
+        <v>-0.015462145456922913</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2124,25 +2227,25 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.7263675921425261</v>
+        <v>0.011473420303155235</v>
       </c>
       <c r="C10">
         <v>0.0</v>
       </c>
       <c r="D10">
-        <v>0.81565738323619</v>
+        <v>0.09281887756465035</v>
       </c>
       <c r="E10">
-        <v>0.9711631474977502</v>
+        <v>0.24713842664744773</v>
       </c>
       <c r="F10">
-        <v>-1.0827520518668891e-14</v>
+        <v>-4.584979772835131e-16</v>
       </c>
       <c r="G10">
         <v>0.0</v>
       </c>
       <c r="H10">
-        <v>-0.18772319729265108</v>
+        <v>-0.014205334884728235</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2150,25 +2253,25 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.8982855718353072</v>
+        <v>0.10976997965989511</v>
       </c>
       <c r="C11">
         <v>0.0</v>
       </c>
       <c r="D11">
-        <v>0.6586264335291755</v>
+        <v>0.0564656832109975</v>
       </c>
       <c r="E11">
-        <v>0.7905470542901599</v>
+        <v>0.1908110132772078</v>
       </c>
       <c r="F11">
-        <v>-1.0864494887789338e-14</v>
+        <v>-4.3301173041301315e-16</v>
       </c>
       <c r="G11">
         <v>0.0</v>
       </c>
       <c r="H11">
-        <v>-0.1610106683164092</v>
+        <v>-0.01296421643052165</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2176,25 +2279,25 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.925522701303046</v>
+        <v>0.1495199508970184</v>
       </c>
       <c r="C12">
         <v>0.0</v>
       </c>
       <c r="D12">
-        <v>0.55700364670584</v>
+        <v>0.03246778428510973</v>
       </c>
       <c r="E12">
-        <v>0.6677310999777977</v>
+        <v>0.15149212646966237</v>
       </c>
       <c r="F12">
-        <v>-1.0867068720641567e-14</v>
+        <v>-3.979416485401561e-16</v>
       </c>
       <c r="G12">
         <v>0.0</v>
       </c>
       <c r="H12">
-        <v>-0.1365906107359131</v>
+        <v>-0.011814951213846158</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2202,25 +2305,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.89464697633588</v>
+        <v>0.16049780056471308</v>
       </c>
       <c r="C13">
         <v>0.0</v>
       </c>
       <c r="D13">
-        <v>0.49186589094681055</v>
+        <v>0.01729056859543368</v>
       </c>
       <c r="E13">
-        <v>0.5837699848463282</v>
+        <v>0.12444684763273535</v>
       </c>
       <c r="F13">
-        <v>-1.0840140977964427e-14</v>
+        <v>-3.5551049288211273e-16</v>
       </c>
       <c r="G13">
         <v>0.0</v>
       </c>
       <c r="H13">
-        <v>-0.11464720511777458</v>
+        <v>-0.010791245297977883</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2228,25 +2331,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.8432769678272422</v>
+        <v>0.15807983378839663</v>
       </c>
       <c r="C14">
         <v>0.0</v>
       </c>
       <c r="D14">
-        <v>0.44886422568029916</v>
+        <v>0.007412129983506349</v>
       </c>
       <c r="E14">
-        <v>0.524200293667064</v>
+        <v>0.10527842914313104</v>
       </c>
       <c r="F14">
-        <v>-1.0788218883580525e-14</v>
+        <v>-3.076542318857994e-16</v>
       </c>
       <c r="G14">
         <v>0.0</v>
       </c>
       <c r="H14">
-        <v>-0.09515749882355043</v>
+        <v>-0.00990258054668697</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2254,25 +2357,25 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.78628418943233</v>
+        <v>0.1497205073739659</v>
       </c>
       <c r="C15">
         <v>0.0</v>
       </c>
       <c r="D15">
-        <v>0.41930366274779857</v>
+        <v>0.0007360314313030469</v>
       </c>
       <c r="E15">
-        <v>0.4801724794746719</v>
+        <v>0.09123351500585693</v>
       </c>
       <c r="F15">
-        <v>-1.0715405280632185e-14</v>
+        <v>-2.560390285301014e-16</v>
       </c>
       <c r="G15">
         <v>0.0</v>
       </c>
       <c r="H15">
-        <v>-0.07800296479348615</v>
+        <v>-0.00914581341270332</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2280,25 +2383,25 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.7291287172948269</v>
+        <v>0.1389619919126751</v>
       </c>
       <c r="C16">
         <v>0.0</v>
       </c>
       <c r="D16">
-        <v>0.397940575159894</v>
+        <v>-0.003889122939751438</v>
       </c>
       <c r="E16">
-        <v>0.4462730444426526</v>
+        <v>0.08065991723176327</v>
       </c>
       <c r="F16">
-        <v>-1.0625398492454296e-14</v>
+        <v>-2.0208132342173716e-16</v>
       </c>
       <c r="G16">
         <v>0.0</v>
       </c>
       <c r="H16">
-        <v>-0.06302357283899464</v>
+        <v>-0.008511579201670188</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2306,25 +2409,25 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.6736313551308283</v>
+        <v>0.1274809751644383</v>
       </c>
       <c r="C17">
         <v>0.0</v>
       </c>
       <c r="D17">
-        <v>0.3814757938432244</v>
+        <v>-0.007109862531682359</v>
       </c>
       <c r="E17">
-        <v>0.41902976580951823</v>
+        <v>0.07252762679352115</v>
       </c>
       <c r="F17">
-        <v>-1.0521501591329904e-14</v>
+        <v>-1.4696966627184697e-16</v>
       </c>
       <c r="G17">
         <v>0.0</v>
       </c>
       <c r="H17">
-        <v>-0.05004343869535837</v>
+        <v>-0.007987692683893904</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2332,25 +2435,25 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.6202949310831299</v>
+        <v>0.11607232508361541</v>
       </c>
       <c r="C18">
         <v>0.0</v>
       </c>
       <c r="D18">
-        <v>0.36775375988496617</v>
+        <v>-0.00931441898106726</v>
       </c>
       <c r="E18">
-        <v>0.39611715994926344</v>
+        <v>0.0661556808140292</v>
       </c>
       <c r="F18">
-        <v>-1.0406638528335869e-14</v>
+        <v>-9.168724583972224e-17</v>
       </c>
       <c r="G18">
         <v>0.0</v>
       </c>
       <c r="H18">
-        <v>-0.03888338257389103</v>
+        <v>-0.007560961958782004</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2358,25 +2461,25 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.5691926844693456</v>
+        <v>0.10511209411254013</v>
       </c>
       <c r="C19">
         <v>0.0</v>
       </c>
       <c r="D19">
-        <v>0.3553437873111153</v>
+        <v>-0.010756344511751635</v>
       </c>
       <c r="E19">
-        <v>0.37594124158524256</v>
+        <v>0.06106905665507224</v>
       </c>
       <c r="F19">
-        <v>-1.0283375052422972e-14</v>
+        <v>-3.7034320309053016e-17</v>
       </c>
       <c r="G19">
         <v>0.0</v>
       </c>
       <c r="H19">
-        <v>-0.029367464426564148</v>
+        <v>-0.007218178453961775</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2384,25 +2487,25 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.5202897774842203</v>
+        <v>0.09477441002674511</v>
       </c>
       <c r="C20">
         <v>0.0</v>
       </c>
       <c r="D20">
-        <v>0.3433055700353689</v>
+        <v>-0.011614831036960739</v>
       </c>
       <c r="E20">
-        <v>0.3574070387942728</v>
+        <v>0.05692335170514526</v>
       </c>
       <c r="F20">
-        <v>-1.0153942753091595e-14</v>
+        <v>1.6350040134988204e-17</v>
       </c>
       <c r="G20">
         <v>0.0</v>
       </c>
       <c r="H20">
-        <v>-0.021326604155422448</v>
+        <v>-0.006946669788790951</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2410,25 +2513,25 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.4735483412482155</v>
+        <v>0.08513351486885028</v>
       </c>
       <c r="C21">
         <v>0.0</v>
       </c>
       <c r="D21">
-        <v>0.33104442188153804</v>
+        <v>-0.012024424659352481</v>
       </c>
       <c r="E21">
-        <v>0.3397749693612522</v>
+        <v>0.05346317943625842</v>
       </c>
       <c r="F21">
-        <v>-1.0020264905286315e-14</v>
+        <v>6.796731470489094e-17</v>
       </c>
       <c r="G21">
         <v>0.0</v>
       </c>
       <c r="H21">
-        <v>-0.014600660752960591</v>
+        <v>-0.006734609725728418</v>
       </c>
     </row>
   </sheetData>
@@ -2458,10 +2561,10 @@
         <v>17</v>
       </c>
       <c r="F1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G1" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="H1" t="s">
         <v>20</v>
@@ -2470,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -3020,10 +3123,10 @@
         <v>17</v>
       </c>
       <c r="F1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G1" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="H1" t="s">
         <v>20</v>
@@ -3032,7 +3135,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -3043,22 +3146,22 @@
         <v>-0.25</v>
       </c>
       <c r="C2">
-        <v>-0.4228834211071525</v>
+        <v>-0.42720639011477957</v>
       </c>
       <c r="D2">
         <v>0.0</v>
       </c>
       <c r="E2">
-        <v>7.778458640898065e-16</v>
+        <v>5.527891081887739e-16</v>
       </c>
       <c r="F2">
-        <v>0.01791681807043027</v>
+        <v>0.5707903061494471</v>
       </c>
       <c r="G2">
-        <v>0.6448448953792352</v>
+        <v>0.0037335837146633944</v>
       </c>
       <c r="H2">
-        <v>-0.269407189282181</v>
+        <v>-0.25420819389122395</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -3069,22 +3172,22 @@
         <v>-0.25</v>
       </c>
       <c r="C3">
-        <v>-0.18446705442960543</v>
+        <v>-0.1578241874397343</v>
       </c>
       <c r="D3">
         <v>0.0</v>
       </c>
       <c r="E3">
-        <v>9.746163015895408e-16</v>
+        <v>6.652083664330567e-16</v>
       </c>
       <c r="F3">
-        <v>0.024084503978877184</v>
+        <v>0.34439031998447733</v>
       </c>
       <c r="G3">
-        <v>0.373834858204526</v>
+        <v>0.0048722947714438785</v>
       </c>
       <c r="H3">
-        <v>-0.27254496309782256</v>
+        <v>-0.2546798114840862</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3095,22 +3198,22 @@
         <v>-0.25</v>
       </c>
       <c r="C4">
-        <v>-0.16784967284091193</v>
+        <v>-0.1444712686887158</v>
       </c>
       <c r="D4">
         <v>0.0</v>
       </c>
       <c r="E4">
-        <v>1.2351232281478535e-15</v>
+        <v>8.206659638099165e-16</v>
       </c>
       <c r="F4">
-        <v>0.028785928784447804</v>
+        <v>0.2644610026980745</v>
       </c>
       <c r="G4">
-        <v>0.28619727181059673</v>
+        <v>0.005678200957309296</v>
       </c>
       <c r="H4">
-        <v>-0.276268055271903</v>
+        <v>-0.25530577661322607</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3121,22 +3224,22 @@
         <v>-0.25</v>
       </c>
       <c r="C5">
-        <v>-0.15699224848525198</v>
+        <v>-0.13551215690666263</v>
       </c>
       <c r="D5">
         <v>0.0</v>
       </c>
       <c r="E5">
-        <v>1.484138260114435e-15</v>
+        <v>9.624394433497537e-16</v>
       </c>
       <c r="F5">
-        <v>0.032331123109085605</v>
+        <v>0.20730999837501063</v>
       </c>
       <c r="G5">
-        <v>0.22642299838332658</v>
+        <v>0.006248222466875985</v>
       </c>
       <c r="H5">
-        <v>-0.2790389645349226</v>
+        <v>-0.25574640488017836</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3147,22 +3250,22 @@
         <v>-0.25</v>
       </c>
       <c r="C6">
-        <v>-0.1493363956401974</v>
+        <v>-0.12928895390767903</v>
       </c>
       <c r="D6">
         <v>0.0</v>
       </c>
       <c r="E6">
-        <v>1.7239794099577973e-15</v>
+        <v>1.091895218875208e-15</v>
       </c>
       <c r="F6">
-        <v>0.034973969779512906</v>
+        <v>0.16513266434240137</v>
       </c>
       <c r="G6">
-        <v>0.18299785587830786</v>
+        <v>0.006649461773059561</v>
       </c>
       <c r="H6">
-        <v>-0.28106879286942077</v>
+        <v>-0.2560556699045665</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3173,22 +3276,22 @@
         <v>-0.25</v>
       </c>
       <c r="C7">
-        <v>-0.14343667747747924</v>
+        <v>-0.12476002269804416</v>
       </c>
       <c r="D7">
         <v>0.0</v>
       </c>
       <c r="E7">
-        <v>1.9556180753792003e-15</v>
+        <v>1.2098923557096455e-15</v>
       </c>
       <c r="F7">
-        <v>0.03689494537457178</v>
+        <v>0.13295188727357443</v>
       </c>
       <c r="G7">
-        <v>0.14933568112969398</v>
+        <v>0.006929564650280192</v>
       </c>
       <c r="H7">
-        <v>-0.2825031328027614</v>
+        <v>-0.2562720879633056</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3196,25 +3299,25 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>-0.1862317353507367</v>
+        <v>-0.19301519936625736</v>
       </c>
       <c r="C8">
-        <v>-0.030623730641442155</v>
+        <v>-0.023899139723412812</v>
       </c>
       <c r="D8">
         <v>0.0</v>
       </c>
       <c r="E8">
-        <v>1.9809291828382377e-15</v>
+        <v>1.1910174002230136e-15</v>
       </c>
       <c r="F8">
-        <v>0.033653743703977536</v>
+        <v>-0.02251291308733272</v>
       </c>
       <c r="G8">
-        <v>-0.042778721926597374</v>
+        <v>0.006272087963311239</v>
       </c>
       <c r="H8">
-        <v>-0.21472906151904128</v>
+        <v>-0.1984796740402066</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3222,25 +3325,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>-0.1386581511828697</v>
+        <v>-0.14743702473772546</v>
       </c>
       <c r="C9">
-        <v>-0.006538166491948191</v>
+        <v>-0.004578140234084342</v>
       </c>
       <c r="D9">
         <v>0.0</v>
       </c>
       <c r="E9">
-        <v>1.9984862509788736e-15</v>
+        <v>1.1613304507574725e-15</v>
       </c>
       <c r="F9">
-        <v>0.02950613151466097</v>
+        <v>-0.09553656104211461</v>
       </c>
       <c r="G9">
-        <v>-0.12005034893773403</v>
+        <v>0.005464474673954477</v>
       </c>
       <c r="H9">
-        <v>-0.16319794644528976</v>
+        <v>-0.15213433331396287</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3248,25 +3351,25 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>-0.1087313450337156</v>
+        <v>-0.11617537678407175</v>
       </c>
       <c r="C10">
-        <v>-0.0013958985460312246</v>
+        <v>-0.0008769925715110662</v>
       </c>
       <c r="D10">
         <v>0.0</v>
       </c>
       <c r="E10">
-        <v>2.0091621834842827e-15</v>
+        <v>1.1229996308443263e-15</v>
       </c>
       <c r="F10">
-        <v>0.025408504014708126</v>
+        <v>-0.12449326593762322</v>
       </c>
       <c r="G10">
-        <v>-0.14420811712030046</v>
+        <v>0.0046973085762421745</v>
       </c>
       <c r="H10">
-        <v>-0.1295949076803918</v>
+        <v>-0.1201968898147598</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -3274,25 +3377,25 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>-0.09002701706853554</v>
+        <v>-0.09470210733107613</v>
       </c>
       <c r="C11">
-        <v>-0.0002980243395779045</v>
+        <v>-0.0001679974686573985</v>
       </c>
       <c r="D11">
         <v>0.0</v>
       </c>
       <c r="E11">
-        <v>2.013794382059501e-15</v>
+        <v>1.0779465400727461e-15</v>
       </c>
       <c r="F11">
-        <v>0.02160213276436692</v>
+        <v>-0.13203757619379708</v>
       </c>
       <c r="G11">
-        <v>-0.14679421560029593</v>
+        <v>0.004021513030692352</v>
       </c>
       <c r="H11">
-        <v>-0.10755577378502677</v>
+        <v>-0.09815111971258768</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -3300,25 +3403,25 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>-0.0780194620940418</v>
+        <v>-0.07948954115007843</v>
       </c>
       <c r="C12">
-        <v>-6.362819650006602e-5</v>
+        <v>-3.2181742915448854e-5</v>
       </c>
       <c r="D12">
         <v>0.0</v>
       </c>
       <c r="E12">
-        <v>2.013173557762138e-15</v>
+        <v>1.0278542225871129e-15</v>
       </c>
       <c r="F12">
-        <v>0.018149274704253426</v>
+        <v>-0.1296263356099685</v>
       </c>
       <c r="G12">
-        <v>-0.14138790338755425</v>
+        <v>0.0034490123815153905</v>
       </c>
       <c r="H12">
-        <v>-0.09256275497121799</v>
+        <v>-0.08246779796266873</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3326,25 +3429,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>-0.07009915739816781</v>
+        <v>-0.06837981465006429</v>
       </c>
       <c r="C13">
-        <v>-1.3584619952892549e-5</v>
+        <v>-6.16476298911314e-6</v>
       </c>
       <c r="D13">
         <v>0.0</v>
       </c>
       <c r="E13">
-        <v>2.00803636619998e-15</v>
+        <v>9.741796631609592e-16</v>
       </c>
       <c r="F13">
-        <v>0.015058125445026637</v>
+        <v>-0.12278283032448467</v>
       </c>
       <c r="G13">
-        <v>-0.13337396178231442</v>
+        <v>0.002978256812593709</v>
       </c>
       <c r="H13">
-        <v>-0.08199525321080006</v>
+        <v>-0.07098202926880079</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3352,25 +3455,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>-0.06475321904412136</v>
+        <v>-0.06007073009404042</v>
       </c>
       <c r="C14">
-        <v>-2.9003163600202158e-6</v>
+        <v>-1.1809274222898644e-6</v>
       </c>
       <c r="D14">
         <v>0.0</v>
       </c>
       <c r="E14">
-        <v>1.999061100556816e-15</v>
+        <v>9.181693020234994e-16</v>
       </c>
       <c r="F14">
-        <v>0.012317217604397836</v>
+        <v>-0.11413462504137417</v>
       </c>
       <c r="G14">
-        <v>-0.1247573486401663</v>
+        <v>0.0026022146187394987</v>
       </c>
       <c r="H14">
-        <v>-0.07432139306562652</v>
+        <v>-0.062382244088892196</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -3378,25 +3481,25 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>-0.06105073578668803</v>
+        <v>-0.053739089110484695</v>
       </c>
       <c r="C15">
-        <v>-6.192175429204243e-7</v>
+        <v>-2.2621949588083419e-7</v>
       </c>
       <c r="D15">
         <v>0.0</v>
       </c>
       <c r="E15">
-        <v>1.986865789633479e-15</v>
+        <v>8.608763627873177e-16</v>
       </c>
       <c r="F15">
-        <v>0.009906887381864867</v>
+        <v>-0.10493301190703386</v>
       </c>
       <c r="G15">
-        <v>-0.11622678224477256</v>
+        <v>0.002311513994854394</v>
       </c>
       <c r="H15">
-        <v>-0.06858779640263282</v>
+        <v>-0.05583500998307157</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -3404,25 +3507,25 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>-0.058383600841612426</v>
+        <v>-0.04883302521911019</v>
       </c>
       <c r="C16">
-        <v>-1.3220294544783711e-7</v>
+        <v>-4.333480547154132e-8</v>
       </c>
       <c r="D16">
         <v>0.0</v>
       </c>
       <c r="E16">
-        <v>1.9720081512597105e-15</v>
+        <v>8.031790488303114e-16</v>
       </c>
       <c r="F16">
-        <v>0.007803872561747671</v>
+        <v>-0.09577806619976337</v>
       </c>
       <c r="G16">
-        <v>-0.10798446581007692</v>
+        <v>0.002095920872589131</v>
       </c>
       <c r="H16">
-        <v>-0.06416251056491241</v>
+        <v>-0.05077814459974558</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -3430,25 +3533,25 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>-0.056338928592428686</v>
+        <v>-0.044963588275177435</v>
       </c>
       <c r="C17">
-        <v>-2.822532886639698e-8</v>
+        <v>-8.301253273956648e-9</v>
       </c>
       <c r="D17">
         <v>0.0</v>
       </c>
       <c r="E17">
-        <v>1.9549869434512487e-15</v>
+        <v>7.457988845358226e-16</v>
       </c>
       <c r="F17">
-        <v>0.005983483127503256</v>
+        <v>-0.08695920253178047</v>
       </c>
       <c r="G17">
-        <v>-0.1000664053183623</v>
+        <v>0.0019451193806373239</v>
       </c>
       <c r="H17">
-        <v>-0.06060855788020484</v>
+        <v>-0.04681274030292732</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -3456,25 +3559,25 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>-0.0546323130968472</v>
+        <v>-0.041847138287867854</v>
       </c>
       <c r="C18">
-        <v>-6.026107706611275e-9</v>
+        <v>-1.590195206514258e-9</v>
       </c>
       <c r="D18">
         <v>0.0</v>
       </c>
       <c r="E18">
-        <v>1.936244336457099e-15</v>
+        <v>6.893186622015589e-16</v>
       </c>
       <c r="F18">
-        <v>0.004420774164561916</v>
+        <v>-0.07861477151704166</v>
       </c>
       <c r="G18">
-        <v>-0.09246107052395769</v>
+        <v>0.0018491520277515256</v>
       </c>
       <c r="H18">
-        <v>-0.05761786943769266</v>
+        <v>-0.04364581237615551</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -3482,25 +3585,25 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>-0.053069178209366824</v>
+        <v>-0.0392729649057663</v>
       </c>
       <c r="C19">
-        <v>-1.2865739711371925e-9</v>
+        <v>-3.046190358322549e-10</v>
       </c>
       <c r="D19">
         <v>0.0</v>
       </c>
       <c r="E19">
-        <v>1.916168998829712e-15</v>
+        <v>6.341996070417149e-16</v>
       </c>
       <c r="F19">
-        <v>0.003091245035309916</v>
+        <v>-0.07080733196772027</v>
       </c>
       <c r="G19">
-        <v>-0.08515046840687657</v>
+        <v>0.0017986740882890322</v>
       </c>
       <c r="H19">
-        <v>-0.05497306077388836</v>
+        <v>-0.04105806207702938</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3508,25 +3611,25 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>-0.0515199293176879</v>
+        <v>-0.037083598512260264</v>
       </c>
       <c r="C20">
-        <v>-2.7468350275653706e-10</v>
+        <v>-5.835295100199053e-11</v>
       </c>
       <c r="D20">
         <v>0.0</v>
       </c>
       <c r="E20">
-        <v>1.895099650627544e-15</v>
+        <v>5.807974955422541e-16</v>
       </c>
       <c r="F20">
-        <v>0.001971280007304186</v>
+        <v>-0.06355970087713314</v>
       </c>
       <c r="G20">
-        <v>-0.07812225479948698</v>
+        <v>0.0017850971712642175</v>
       </c>
       <c r="H20">
-        <v>-0.052522855457941595</v>
+        <v>-0.038884260483906356</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -3534,25 +3637,587 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>-0.04990263531803833</v>
+        <v>-0.03516178968903228</v>
       </c>
       <c r="C21">
-        <v>-5.864487399535477e-11</v>
+        <v>-1.1178020148688154e-11</v>
       </c>
       <c r="D21">
         <v>0.0</v>
       </c>
       <c r="E21">
-        <v>1.873328887747205e-15</v>
+        <v>5.293775604191032e-16</v>
       </c>
       <c r="F21">
-        <v>0.0010384297256173186</v>
+        <v>-0.05687269770598974</v>
       </c>
       <c r="G21">
-        <v>-0.07137156903784742</v>
+        <v>0.001800661971647017</v>
       </c>
       <c r="H21">
-        <v>-0.050164935675140694</v>
+        <v>-0.0370002532243192</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>-3.176493858019506</v>
+      </c>
+      <c r="C2">
+        <v>0.0</v>
+      </c>
+      <c r="D2">
+        <v>-1.0000000000000002</v>
+      </c>
+      <c r="E2">
+        <v>-0.9052392657323787</v>
+      </c>
+      <c r="F2">
+        <v>-4.7483479158732125e-15</v>
+      </c>
+      <c r="G2">
+        <v>0.7205053288041088</v>
+      </c>
+      <c r="H2">
+        <v>-0.08040185016545284</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>-2.339916203195548</v>
+      </c>
+      <c r="C3">
+        <v>0.0</v>
+      </c>
+      <c r="D3">
+        <v>-1.0</v>
+      </c>
+      <c r="E3">
+        <v>-0.9050688766126487</v>
+      </c>
+      <c r="F3">
+        <v>-5.3791489454505824e-15</v>
+      </c>
+      <c r="G3">
+        <v>0.5032421639873857</v>
+      </c>
+      <c r="H3">
+        <v>-0.09476073426764203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>-1.8379967551838212</v>
+      </c>
+      <c r="C4">
+        <v>0.0</v>
+      </c>
+      <c r="D4">
+        <v>-1.0</v>
+      </c>
+      <c r="E4">
+        <v>-0.9086031713999635</v>
+      </c>
+      <c r="F4">
+        <v>-5.8183056492119395e-15</v>
+      </c>
+      <c r="G4">
+        <v>0.47446958701465264</v>
+      </c>
+      <c r="H4">
+        <v>-0.09493112338737886</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>-1.5057052460874383</v>
+      </c>
+      <c r="C5">
+        <v>0.0</v>
+      </c>
+      <c r="D5">
+        <v>-1.0</v>
+      </c>
+      <c r="E5">
+        <v>-0.9135571947895866</v>
+      </c>
+      <c r="F5">
+        <v>-6.090418604880368e-15</v>
+      </c>
+      <c r="G5">
+        <v>0.4516365720817424</v>
+      </c>
+      <c r="H5">
+        <v>-0.09139682860006812</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>-1.2504215444989588</v>
+      </c>
+      <c r="C6">
+        <v>0.0</v>
+      </c>
+      <c r="D6">
+        <v>-0.9999999999999997</v>
+      </c>
+      <c r="E6">
+        <v>-0.9192954503986278</v>
+      </c>
+      <c r="F6">
+        <v>-6.219020891789063e-15</v>
+      </c>
+      <c r="G6">
+        <v>0.4255368850428102</v>
+      </c>
+      <c r="H6">
+        <v>-0.08644280521045197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>-1.0197889743676405</v>
+      </c>
+      <c r="C7">
+        <v>0.0</v>
+      </c>
+      <c r="D7">
+        <v>-0.9999999999999999</v>
+      </c>
+      <c r="E7">
+        <v>-0.9255267684593391</v>
+      </c>
+      <c r="F7">
+        <v>-6.2261913106385064e-15</v>
+      </c>
+      <c r="G7">
+        <v>2.6636909000770084</v>
+      </c>
+      <c r="H7">
+        <v>-0.08070454960141284</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>-0.7834310456132147</v>
+      </c>
+      <c r="C8">
+        <v>0.0</v>
+      </c>
+      <c r="D8">
+        <v>1.2734464728070378</v>
+      </c>
+      <c r="E8">
+        <v>1.3414080441414482</v>
+      </c>
+      <c r="F8">
+        <v>-6.132302703677179e-15</v>
+      </c>
+      <c r="G8">
+        <v>0.0</v>
+      </c>
+      <c r="H8">
+        <v>-0.07447323154070248</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>0.13386627111547522</v>
+      </c>
+      <c r="C9">
+        <v>0.0</v>
+      </c>
+      <c r="D9">
+        <v>1.281004580320485</v>
+      </c>
+      <c r="E9">
+        <v>1.3426532754608267</v>
+      </c>
+      <c r="F9">
+        <v>-5.9558794758840135e-15</v>
+      </c>
+      <c r="G9">
+        <v>0.0</v>
+      </c>
+      <c r="H9">
+        <v>-0.06796157133445066</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>0.6708481598313354</v>
+      </c>
+      <c r="C10">
+        <v>0.0</v>
+      </c>
+      <c r="D10">
+        <v>1.0309421533109264</v>
+      </c>
+      <c r="E10">
+        <v>1.0868180927178592</v>
+      </c>
+      <c r="F10">
+        <v>-5.713541401188097e-15</v>
+      </c>
+      <c r="G10">
+        <v>0.0</v>
+      </c>
+      <c r="H10">
+        <v>-0.06164869514037902</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>0.9002406758186732</v>
+      </c>
+      <c r="C11">
+        <v>0.0</v>
+      </c>
+      <c r="D11">
+        <v>0.8245778752789108</v>
+      </c>
+      <c r="E11">
+        <v>0.8753826214960255</v>
+      </c>
+      <c r="F11">
+        <v>-5.4200138113656535e-15</v>
+      </c>
+      <c r="G11">
+        <v>0.0</v>
+      </c>
+      <c r="H11">
+        <v>-0.05587593940696686</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>0.963668795374451</v>
+      </c>
+      <c r="C12">
+        <v>0.0</v>
+      </c>
+      <c r="D12">
+        <v>0.6786817445489455</v>
+      </c>
+      <c r="E12">
+        <v>0.7251580193976526</v>
+      </c>
+      <c r="F12">
+        <v>-5.088187219966319e-15</v>
+      </c>
+      <c r="G12">
+        <v>0.0</v>
+      </c>
+      <c r="H12">
+        <v>-0.05080474621714512</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>0.9474779594753344</v>
+      </c>
+      <c r="C13">
+        <v>0.0</v>
+      </c>
+      <c r="D13">
+        <v>0.5755513070359215</v>
+      </c>
+      <c r="E13">
+        <v>0.6184168634141053</v>
+      </c>
+      <c r="F13">
+        <v>-4.72921222665598e-15</v>
+      </c>
+      <c r="G13">
+        <v>0.0</v>
+      </c>
+      <c r="H13">
+        <v>-0.04647627484873401</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>0.8957636284726331</v>
+      </c>
+      <c r="C14">
+        <v>0.0</v>
+      </c>
+      <c r="D14">
+        <v>0.5005134811262366</v>
+      </c>
+      <c r="E14">
+        <v>0.5404283904458612</v>
+      </c>
+      <c r="F14">
+        <v>-4.352618103283e-15</v>
+      </c>
+      <c r="G14">
+        <v>0.0</v>
+      </c>
+      <c r="H14">
+        <v>-0.042865556378207624</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>0.8298521301499691</v>
+      </c>
+      <c r="C15">
+        <v>0.0</v>
+      </c>
+      <c r="D15">
+        <v>0.44424580942170105</v>
+      </c>
+      <c r="E15">
+        <v>0.4817982033686396</v>
+      </c>
+      <c r="F15">
+        <v>-3.966445739574199e-15</v>
+      </c>
+      <c r="G15">
+        <v>0.0</v>
+      </c>
+      <c r="H15">
+        <v>-0.039914909319645364</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>0.7598752475964843</v>
+      </c>
+      <c r="C16">
+        <v>0.0</v>
+      </c>
+      <c r="D16">
+        <v>0.4009221257836244</v>
+      </c>
+      <c r="E16">
+        <v>0.43662384428718026</v>
+      </c>
+      <c r="F16">
+        <v>-3.5773876090182515e-15</v>
+      </c>
+      <c r="G16">
+        <v>0.0</v>
+      </c>
+      <c r="H16">
+        <v>-0.0375523939469565</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>0.6906149433032076</v>
+      </c>
+      <c r="C17">
+        <v>0.0</v>
+      </c>
+      <c r="D17">
+        <v>0.3667487938508236</v>
+      </c>
+      <c r="E17">
+        <v>0.40103636978371493</v>
+      </c>
+      <c r="F17">
+        <v>-3.1909291091707843e-15</v>
+      </c>
+      <c r="G17">
+        <v>0.0</v>
+      </c>
+      <c r="H17">
+        <v>-0.03570171850357123</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>0.624305901237475</v>
+      </c>
+      <c r="C18">
+        <v>0.0</v>
+      </c>
+      <c r="D18">
+        <v>0.3391321379730927</v>
+      </c>
+      <c r="E18">
+        <v>0.37237068033761667</v>
+      </c>
+      <c r="F18">
+        <v>-2.811487052786615e-15</v>
+      </c>
+      <c r="G18">
+        <v>0.0</v>
+      </c>
+      <c r="H18">
+        <v>-0.03428757593290447</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>0.5619574797877032</v>
+      </c>
+      <c r="C19">
+        <v>0.0</v>
+      </c>
+      <c r="D19">
+        <v>0.3162298539971158</v>
+      </c>
+      <c r="E19">
+        <v>0.3487184850955368</v>
+      </c>
+      <c r="F19">
+        <v>-2.442542261379695e-15</v>
+      </c>
+      <c r="G19">
+        <v>0.0</v>
+      </c>
+      <c r="H19">
+        <v>-0.03323854236453497</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>0.5039768198912434</v>
+      </c>
+      <c r="C20">
+        <v>0.0</v>
+      </c>
+      <c r="D20">
+        <v>0.2967029198221134</v>
+      </c>
+      <c r="E20">
+        <v>0.3286809863978688</v>
+      </c>
+      <c r="F20">
+        <v>-2.086764168779213e-15</v>
+      </c>
+      <c r="G20">
+        <v>0.0</v>
+      </c>
+      <c r="H20">
+        <v>-0.03248863109843009</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>0.4504654531108913</v>
+      </c>
+      <c r="C21">
+        <v>0.0</v>
+      </c>
+      <c r="D21">
+        <v>0.27956929395510494</v>
+      </c>
+      <c r="E21">
+        <v>0.3112228747784289</v>
+      </c>
+      <c r="F21">
+        <v>-1.7461261073911667e-15</v>
+      </c>
+      <c r="G21">
+        <v>0.0</v>
+      </c>
+      <c r="H21">
+        <v>-0.031978066575762916</v>
       </c>
     </row>
   </sheetData>

--- a/irf/irf/Paper IRFs.xlsx
+++ b/irf/irf/Paper IRFs.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="143">
   <si>
     <t>t</t>
   </si>
@@ -437,6 +437,30 @@
   </si>
   <si>
     <t>2026-03-07T12:50:40.745</t>
+  </si>
+  <si>
+    <t>2026-03-08T23:41:18.378</t>
+  </si>
+  <si>
+    <t>2026-03-08T23:41:45.068</t>
+  </si>
+  <si>
+    <t>2026-03-08T23:41:51.843</t>
+  </si>
+  <si>
+    <t>2026-03-08T23:41:55.452</t>
+  </si>
+  <si>
+    <t>2026-03-08T23:41:59.378</t>
+  </si>
+  <si>
+    <t>2026-03-08T23:42:03.115</t>
+  </si>
+  <si>
+    <t>2026-03-08T23:42:07.443</t>
+  </si>
+  <si>
+    <t>2026-03-09T09:21:01.743</t>
   </si>
 </sst>
 </file>
@@ -2573,7 +2597,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -3135,7 +3159,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -3697,7 +3721,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:11">

--- a/irf/irf/Paper IRFs.xlsx
+++ b/irf/irf/Paper IRFs.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="144">
   <si>
     <t>t</t>
   </si>
@@ -461,6 +461,9 @@
   </si>
   <si>
     <t>2026-03-09T09:21:01.743</t>
+  </si>
+  <si>
+    <t>2026-03-13T15:57:09.957</t>
   </si>
 </sst>
 </file>
@@ -3721,7 +3724,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -3729,25 +3732,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>-3.176493858019506</v>
+        <v>0.24568080506695344</v>
       </c>
       <c r="C2">
         <v>0.0</v>
       </c>
       <c r="D2">
-        <v>-1.0000000000000002</v>
+        <v>-1.0</v>
       </c>
       <c r="E2">
-        <v>-0.9052392657323787</v>
+        <v>0.08493046150715088</v>
       </c>
       <c r="F2">
-        <v>-4.7483479158732125e-15</v>
+        <v>3.986335937361826e-16</v>
       </c>
       <c r="G2">
-        <v>0.7205053288041088</v>
+        <v>-0.22971839175496833</v>
       </c>
       <c r="H2">
-        <v>-0.08040185016545284</v>
+        <v>-0.009243260936556393</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -3755,7 +3758,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>-2.339916203195548</v>
+        <v>0.13836927980089797</v>
       </c>
       <c r="C3">
         <v>0.0</v>
@@ -3764,16 +3767,16 @@
         <v>-1.0</v>
       </c>
       <c r="E3">
-        <v>-0.9050688766126487</v>
+        <v>-0.1055347112364461</v>
       </c>
       <c r="F3">
-        <v>-5.3791489454505824e-15</v>
+        <v>2.678273004630199e-16</v>
       </c>
       <c r="G3">
-        <v>0.5032421639873857</v>
+        <v>-0.23231447954005477</v>
       </c>
       <c r="H3">
-        <v>-0.09476073426764203</v>
+        <v>-0.011174059579196038</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3781,7 +3784,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>-1.8379967551838212</v>
+        <v>-0.00479298431057662</v>
       </c>
       <c r="C4">
         <v>0.0</v>
@@ -3790,16 +3793,16 @@
         <v>-1.0</v>
       </c>
       <c r="E4">
-        <v>-0.9086031713999635</v>
+        <v>-0.3584793514459424</v>
       </c>
       <c r="F4">
-        <v>-5.8183056492119395e-15</v>
+        <v>1.625912853080499e-16</v>
       </c>
       <c r="G4">
-        <v>0.47446958701465264</v>
+        <v>-0.12369593004209355</v>
       </c>
       <c r="H4">
-        <v>-0.09493112338737886</v>
+        <v>-0.011700337986996764</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3807,7 +3810,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>-1.5057052460874383</v>
+        <v>-0.17790435476722674</v>
       </c>
       <c r="C5">
         <v>0.0</v>
@@ -3816,16 +3819,16 @@
         <v>-1.0</v>
       </c>
       <c r="E5">
-        <v>-0.9135571947895866</v>
+        <v>-0.5333770711596347</v>
       </c>
       <c r="F5">
-        <v>-6.090418604880368e-15</v>
+        <v>8.044215724776388e-17</v>
       </c>
       <c r="G5">
-        <v>0.4516365720817424</v>
+        <v>-0.05010323746278902</v>
       </c>
       <c r="H5">
-        <v>-0.09139682860006812</v>
+        <v>-0.011914477625187872</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3833,25 +3836,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>-1.2504215444989588</v>
+        <v>-0.3298082459014194</v>
       </c>
       <c r="C6">
         <v>0.0</v>
       </c>
       <c r="D6">
-        <v>-0.9999999999999997</v>
+        <v>-1.0</v>
       </c>
       <c r="E6">
-        <v>-0.9192954503986278</v>
+        <v>-0.6462301338888465</v>
       </c>
       <c r="F6">
-        <v>-6.219020891789063e-15</v>
+        <v>1.8837355658372474e-17</v>
       </c>
       <c r="G6">
-        <v>0.4255368850428102</v>
+        <v>-0.000500509071672816</v>
       </c>
       <c r="H6">
-        <v>-0.08644280521045197</v>
+        <v>-0.011956037676767046</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3859,25 +3862,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>-1.0197889743676405</v>
+        <v>-0.4358752811830413</v>
       </c>
       <c r="C7">
         <v>0.0</v>
       </c>
       <c r="D7">
-        <v>-0.9999999999999999</v>
+        <v>-1.0</v>
       </c>
       <c r="E7">
-        <v>-0.9255267684593391</v>
+        <v>-0.7210439740970532</v>
       </c>
       <c r="F7">
-        <v>-6.2261913106385064e-15</v>
+        <v>-2.474057278354479e-17</v>
       </c>
       <c r="G7">
-        <v>2.6636909000770084</v>
+        <v>0.9757872258787043</v>
       </c>
       <c r="H7">
-        <v>-0.08070454960141284</v>
+        <v>-0.011792460556177211</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3885,25 +3888,25 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>-0.7834310456132147</v>
+        <v>-0.4890048128818044</v>
       </c>
       <c r="C8">
         <v>0.0</v>
       </c>
       <c r="D8">
-        <v>1.2734464728070378</v>
+        <v>-0.05489221931557406</v>
       </c>
       <c r="E8">
-        <v>1.3414080441414482</v>
+        <v>0.17210057151534616</v>
       </c>
       <c r="F8">
-        <v>-6.132302703677179e-15</v>
+        <v>-5.272072761559501e-17</v>
       </c>
       <c r="G8">
         <v>0.0</v>
       </c>
       <c r="H8">
-        <v>-0.07447323154070248</v>
+        <v>-0.011381871558407643</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3911,25 +3914,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.13386627111547522</v>
+        <v>-0.21605645540033253</v>
       </c>
       <c r="C9">
         <v>0.0</v>
       </c>
       <c r="D9">
-        <v>1.281004580320485</v>
+        <v>0.04426587660423642</v>
       </c>
       <c r="E9">
-        <v>1.3426532754608267</v>
+        <v>0.23371976622355564</v>
       </c>
       <c r="F9">
-        <v>-5.9558794758840135e-15</v>
+        <v>-6.739846608045116e-17</v>
       </c>
       <c r="G9">
         <v>0.0</v>
       </c>
       <c r="H9">
-        <v>-0.06796157133445066</v>
+        <v>-0.010706021593438059</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3937,25 +3940,25 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.6708481598313354</v>
+        <v>-0.03715968800662442</v>
       </c>
       <c r="C10">
         <v>0.0</v>
       </c>
       <c r="D10">
-        <v>1.0309421533109264</v>
+        <v>0.023626280180739645</v>
       </c>
       <c r="E10">
-        <v>1.0868180927178592</v>
+        <v>0.1852066757060291</v>
       </c>
       <c r="F10">
-        <v>-5.713541401188097e-15</v>
+        <v>-7.090488236116101e-17</v>
       </c>
       <c r="G10">
         <v>0.0</v>
       </c>
       <c r="H10">
-        <v>-0.06164869514037902</v>
+        <v>-0.009893978809767157</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -3963,25 +3966,25 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.9002406758186732</v>
+        <v>0.05146770528173952</v>
       </c>
       <c r="C11">
         <v>0.0</v>
       </c>
       <c r="D11">
-        <v>0.8245778752789108</v>
+        <v>-0.0001875083529248034</v>
       </c>
       <c r="E11">
-        <v>0.8753826214960255</v>
+        <v>0.14031947459295552</v>
       </c>
       <c r="F11">
-        <v>-5.4200138113656535e-15</v>
+        <v>-6.51884005147327e-17</v>
       </c>
       <c r="G11">
         <v>0.0</v>
       </c>
       <c r="H11">
-        <v>-0.05587593940696686</v>
+        <v>-0.00905805109405701</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -3989,25 +3992,25 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.963668795374451</v>
+        <v>0.08947126149456243</v>
       </c>
       <c r="C12">
         <v>0.0</v>
       </c>
       <c r="D12">
-        <v>0.6786817445489455</v>
+        <v>-0.015194632299564359</v>
       </c>
       <c r="E12">
-        <v>0.7251580193976526</v>
+        <v>0.10918059429850749</v>
       </c>
       <c r="F12">
-        <v>-5.088187219966319e-15</v>
+        <v>-5.200601103324721e-17</v>
       </c>
       <c r="G12">
         <v>0.0</v>
       </c>
       <c r="H12">
-        <v>-0.05080474621714512</v>
+        <v>-0.008263755495204507</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -4015,25 +4018,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.9474779594753344</v>
+        <v>0.102452975654777</v>
       </c>
       <c r="C13">
         <v>0.0</v>
       </c>
       <c r="D13">
-        <v>0.5755513070359215</v>
+        <v>-0.02388473480957891</v>
       </c>
       <c r="E13">
-        <v>0.6184168634141053</v>
+        <v>0.08801339660840735</v>
       </c>
       <c r="F13">
-        <v>-4.72921222665598e-15</v>
+        <v>-3.2921989892903245e-17</v>
       </c>
       <c r="G13">
         <v>0.0</v>
       </c>
       <c r="H13">
-        <v>-0.04647627484873401</v>
+        <v>-0.0075423214128905545</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4041,25 +4044,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.8957636284726331</v>
+        <v>0.10367093133192853</v>
       </c>
       <c r="C14">
         <v>0.0</v>
       </c>
       <c r="D14">
-        <v>0.5005134811262366</v>
+        <v>-0.02895725146259366</v>
       </c>
       <c r="E14">
-        <v>0.5404283904458612</v>
+        <v>0.0731833336983537</v>
       </c>
       <c r="F14">
-        <v>-4.352618103283e-15</v>
+        <v>-9.312250802979382e-18</v>
       </c>
       <c r="G14">
         <v>0.0</v>
       </c>
       <c r="H14">
-        <v>-0.042865556378207624</v>
+        <v>-0.0069052296085054445</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4067,25 +4070,25 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.8298521301499691</v>
+        <v>0.09955644604058812</v>
       </c>
       <c r="C15">
         <v>0.0</v>
       </c>
       <c r="D15">
-        <v>0.44424580942170105</v>
+        <v>-0.031975654013133986</v>
       </c>
       <c r="E15">
-        <v>0.4817982033686396</v>
+        <v>0.06242686887210582</v>
       </c>
       <c r="F15">
-        <v>-3.966445739574199e-15</v>
+        <v>1.7627220165840808e-17</v>
       </c>
       <c r="G15">
         <v>0.0</v>
       </c>
       <c r="H15">
-        <v>-0.039914909319645364</v>
+        <v>-0.0063535387702982095</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -4093,25 +4096,25 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.7598752475964843</v>
+        <v>0.09316566426406624</v>
       </c>
       <c r="C16">
         <v>0.0</v>
       </c>
       <c r="D16">
-        <v>0.4009221257836244</v>
+        <v>-0.033746544105549066</v>
       </c>
       <c r="E16">
-        <v>0.43662384428718026</v>
+        <v>0.05440529875601142</v>
       </c>
       <c r="F16">
-        <v>-3.5773876090182515e-15</v>
+        <v>4.686912360866499e-17</v>
       </c>
       <c r="G16">
         <v>0.0</v>
       </c>
       <c r="H16">
-        <v>-0.0375523939469565</v>
+        <v>-0.005883034883141703</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -4119,25 +4122,25 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.6906149433032076</v>
+        <v>0.08594623987111218</v>
       </c>
       <c r="C17">
         <v>0.0</v>
       </c>
       <c r="D17">
-        <v>0.3667487938508236</v>
+        <v>-0.034684331856074974</v>
       </c>
       <c r="E17">
-        <v>0.40103636978371493</v>
+        <v>0.04829800390868981</v>
       </c>
       <c r="F17">
-        <v>-3.1909291091707843e-15</v>
+        <v>7.754182985099447e-17</v>
       </c>
       <c r="G17">
         <v>0.0</v>
       </c>
       <c r="H17">
-        <v>-0.03570171850357123</v>
+        <v>-0.005486957601275591</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -4145,25 +4148,25 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.624305901237475</v>
+        <v>0.07858684516753045</v>
       </c>
       <c r="C18">
         <v>0.0</v>
       </c>
       <c r="D18">
-        <v>0.3391321379730927</v>
+        <v>-0.03501458328618973</v>
       </c>
       <c r="E18">
-        <v>0.37237068033761667</v>
+        <v>0.04357036423279956</v>
       </c>
       <c r="F18">
-        <v>-2.811487052786615e-15</v>
+        <v>1.0891540188502129e-16</v>
       </c>
       <c r="G18">
         <v>0.0</v>
       </c>
       <c r="H18">
-        <v>-0.03428757593290447</v>
+        <v>-0.005157450582039444</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -4171,25 +4174,25 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.5619574797877032</v>
+        <v>0.07141682222775211</v>
       </c>
       <c r="C19">
         <v>0.0</v>
       </c>
       <c r="D19">
-        <v>0.3162298539971158</v>
+        <v>-0.034873669993865056</v>
       </c>
       <c r="E19">
-        <v>0.3487184850955368</v>
+        <v>0.039853069796671414</v>
       </c>
       <c r="F19">
-        <v>-2.442542261379695e-15</v>
+        <v>1.4038729023343552e-16</v>
       </c>
       <c r="G19">
         <v>0.0</v>
       </c>
       <c r="H19">
-        <v>-0.03323854236453497</v>
+        <v>-0.00488635412461131</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -4197,25 +4200,25 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.5039768198912434</v>
+        <v>0.06459311261489223</v>
       </c>
       <c r="C20">
         <v>0.0</v>
       </c>
       <c r="D20">
-        <v>0.2967029198221134</v>
+        <v>-0.034355238990845194</v>
       </c>
       <c r="E20">
-        <v>0.3286809863978688</v>
+        <v>0.03687948637375892</v>
       </c>
       <c r="F20">
-        <v>-2.086764168779213e-15</v>
+        <v>1.714681770280525e-16</v>
       </c>
       <c r="G20">
         <v>0.0</v>
       </c>
       <c r="H20">
-        <v>-0.03248863109843009</v>
+        <v>-0.0046656525878128055</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4223,25 +4226,25 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.4504654531108913</v>
+        <v>0.0581879455947522</v>
       </c>
       <c r="C21">
         <v>0.0</v>
       </c>
       <c r="D21">
-        <v>0.27956929395510494</v>
+        <v>-0.03353132816914686</v>
       </c>
       <c r="E21">
-        <v>0.3112228747784289</v>
+        <v>0.03445175174577457</v>
       </c>
       <c r="F21">
-        <v>-1.7461261073911667e-15</v>
+        <v>2.0176831827986297e-16</v>
       </c>
       <c r="G21">
         <v>0.0</v>
       </c>
       <c r="H21">
-        <v>-0.031978066575762916</v>
+        <v>-0.004487732397470871</v>
       </c>
     </row>
   </sheetData>

--- a/irf/irf/Paper IRFs.xlsx
+++ b/irf/irf/Paper IRFs.xlsx
@@ -21,6 +21,9 @@
     <sheet name="IRF_rate_peg_with_permanent_liq" r:id="rId9" sheetId="6"/>
     <sheet name="Interest_rate_peg_IRF_Policy_ra" r:id="rId10" sheetId="7"/>
     <sheet name="interest_rate_peg_with_contempo" r:id="rId11" sheetId="8"/>
+    <sheet name="interest_rate_peg_combined_thre" r:id="rId12" sheetId="9"/>
+    <sheet name="interest_rate_peg_combined_four" r:id="rId13" sheetId="10"/>
+    <sheet name="interest_rate_peg_combined_mit_" r:id="rId14" sheetId="11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="282">
   <si>
     <t>t</t>
   </si>
@@ -464,6 +467,420 @@
   </si>
   <si>
     <t>2026-03-13T15:57:09.957</t>
+  </si>
+  <si>
+    <t>2026-03-17T18:01:13.444</t>
+  </si>
+  <si>
+    <t>2026-03-17T18:13:15.612</t>
+  </si>
+  <si>
+    <t>2026-03-17T18:13:22.261</t>
+  </si>
+  <si>
+    <t>2026-03-17T18:13:25.416</t>
+  </si>
+  <si>
+    <t>2026-03-17T18:13:28.516</t>
+  </si>
+  <si>
+    <t>2026-03-17T18:13:31.622</t>
+  </si>
+  <si>
+    <t>2026-03-17T18:13:34.796</t>
+  </si>
+  <si>
+    <t>2026-03-17T18:16:48.375</t>
+  </si>
+  <si>
+    <t>Monetary policy shock (rm_sh)</t>
+  </si>
+  <si>
+    <t>2026-03-23T13:13:20.991</t>
+  </si>
+  <si>
+    <t>Shock q3 rm_shl2</t>
+  </si>
+  <si>
+    <t>Shock q1 rm_sh</t>
+  </si>
+  <si>
+    <t>Shock q4 rm_shl3</t>
+  </si>
+  <si>
+    <t>Shock q5 rm_shl4</t>
+  </si>
+  <si>
+    <t>Forward5YearRealNaturalRate</t>
+  </si>
+  <si>
+    <t>Shock q6 rm_shl5</t>
+  </si>
+  <si>
+    <t>obs_nominalrate</t>
+  </si>
+  <si>
+    <t>obs_corepce</t>
+  </si>
+  <si>
+    <t>Shock q2 rm_shl1</t>
+  </si>
+  <si>
+    <t>ExAnteRealRate</t>
+  </si>
+  <si>
+    <t>obs_gdp</t>
+  </si>
+  <si>
+    <t>2026-03-23T13:13:29.954</t>
+  </si>
+  <si>
+    <t>2026-03-23T13:13:32.853</t>
+  </si>
+  <si>
+    <t>2026-03-23T13:13:35.795</t>
+  </si>
+  <si>
+    <t>Permanent liquidity shock (b_liqp_sh)</t>
+  </si>
+  <si>
+    <t>2026-03-23T13:13:38.917</t>
+  </si>
+  <si>
+    <t>2026-03-23T13:15:51.764</t>
+  </si>
+  <si>
+    <t>2026-03-24T18:19:02.328</t>
+  </si>
+  <si>
+    <t>2026-03-24T18:19:09.47</t>
+  </si>
+  <si>
+    <t>2026-03-24T18:19:12.287</t>
+  </si>
+  <si>
+    <t>2026-03-24T18:19:15.177</t>
+  </si>
+  <si>
+    <t>2026-03-24T18:19:18.187</t>
+  </si>
+  <si>
+    <t>2026-03-24T18:24:50.037</t>
+  </si>
+  <si>
+    <t>2026-03-24T18:26:49.343</t>
+  </si>
+  <si>
+    <t>Permanent liquidity shock (b_liqtil_sh)</t>
+  </si>
+  <si>
+    <t>2026-03-24T18:28:18.24</t>
+  </si>
+  <si>
+    <t>2026-03-24T18:32:39.427</t>
+  </si>
+  <si>
+    <t>2026-03-25T12:35:53.324</t>
+  </si>
+  <si>
+    <t>2026-03-25T12:35:58.363</t>
+  </si>
+  <si>
+    <t>2026-03-25T12:36:01.464</t>
+  </si>
+  <si>
+    <t>2026-03-25T12:36:04.584</t>
+  </si>
+  <si>
+    <t>2026-03-25T12:36:07.606</t>
+  </si>
+  <si>
+    <t>2026-03-25T12:36:10.939</t>
+  </si>
+  <si>
+    <t>2026-03-25T12:37:32.306</t>
+  </si>
+  <si>
+    <t>2026-03-25T17:42:10.144</t>
+  </si>
+  <si>
+    <t>2026-03-25T17:42:17.041</t>
+  </si>
+  <si>
+    <t>2026-03-25T17:42:20.087</t>
+  </si>
+  <si>
+    <t>2026-03-25T17:42:23.188</t>
+  </si>
+  <si>
+    <t>Scenario 2 stars</t>
+  </si>
+  <si>
+    <t>Scenario 2 ex ante real</t>
+  </si>
+  <si>
+    <t>Scenario 1 output</t>
+  </si>
+  <si>
+    <t>Scenario 1 policy rate</t>
+  </si>
+  <si>
+    <t>Scenario 3 inflation</t>
+  </si>
+  <si>
+    <t>Scenario 3 output</t>
+  </si>
+  <si>
+    <t>Scenario 2 r*</t>
+  </si>
+  <si>
+    <t>Scenario 1 ex ante real</t>
+  </si>
+  <si>
+    <t>Scenario 1 r*</t>
+  </si>
+  <si>
+    <t>Scenario 2 inflation</t>
+  </si>
+  <si>
+    <t>Scenario 1 inflation</t>
+  </si>
+  <si>
+    <t>Scenario 3 policy rate</t>
+  </si>
+  <si>
+    <t>Scenario 1 stars</t>
+  </si>
+  <si>
+    <t>Scenario 3 ex ante real</t>
+  </si>
+  <si>
+    <t>Scenario 2 output</t>
+  </si>
+  <si>
+    <t>Scenario 3 stars</t>
+  </si>
+  <si>
+    <t>Scenario 2 policy rate</t>
+  </si>
+  <si>
+    <t>Scenario 3 r*</t>
+  </si>
+  <si>
+    <t>2026-03-25T17:42:27.314</t>
+  </si>
+  <si>
+    <t>2026-03-25T17:42:30.525</t>
+  </si>
+  <si>
+    <t>2026-03-25T17:42:34.077</t>
+  </si>
+  <si>
+    <t>2026-03-25T17:50:40.751</t>
+  </si>
+  <si>
+    <t>2026-03-25T17:50:44.41</t>
+  </si>
+  <si>
+    <t>2026-03-25T17:50:47.693</t>
+  </si>
+  <si>
+    <t>2026-03-25T17:50:50.759</t>
+  </si>
+  <si>
+    <t>2026-03-25T17:50:53.807</t>
+  </si>
+  <si>
+    <t>Scenario 4 inflation</t>
+  </si>
+  <si>
+    <t>Scenario 4 ex ante real</t>
+  </si>
+  <si>
+    <t>Scenario 4 stars</t>
+  </si>
+  <si>
+    <t>Scenario 4 r*</t>
+  </si>
+  <si>
+    <t>Scenario 4 policy rate</t>
+  </si>
+  <si>
+    <t>Scenario 4 output</t>
+  </si>
+  <si>
+    <t>2026-03-25T17:50:57.186</t>
+  </si>
+  <si>
+    <t>2026-03-25T17:51:00.332</t>
+  </si>
+  <si>
+    <t>2026-03-25T17:51:03.358</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:07:57.313</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:08:01.4</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:08:04.605</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:08:07.767</t>
+  </si>
+  <si>
+    <t>MP-plus-FG r*</t>
+  </si>
+  <si>
+    <t>MP-plus-FG stars</t>
+  </si>
+  <si>
+    <t>MP-plus-FG policy rate</t>
+  </si>
+  <si>
+    <t>MIT sequence output</t>
+  </si>
+  <si>
+    <t>Anticipated-only r*</t>
+  </si>
+  <si>
+    <t>MP-plus-FG output</t>
+  </si>
+  <si>
+    <t>MP-plus-FG ex ante real</t>
+  </si>
+  <si>
+    <t>Anticipated-only inflation</t>
+  </si>
+  <si>
+    <t>Anticipated-only policy rate</t>
+  </si>
+  <si>
+    <t>MIT sequence stars</t>
+  </si>
+  <si>
+    <t>Anticipated-only output</t>
+  </si>
+  <si>
+    <t>Anticipated-only ex ante real</t>
+  </si>
+  <si>
+    <t>MIT sequence inflation</t>
+  </si>
+  <si>
+    <t>Anticipated-only stars</t>
+  </si>
+  <si>
+    <t>MIT sequence ex ante real</t>
+  </si>
+  <si>
+    <t>MIT sequence policy rate</t>
+  </si>
+  <si>
+    <t>MIT sequence r*</t>
+  </si>
+  <si>
+    <t>MP-plus-FG inflation</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:08:10.812</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:12:38.928</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:12:42.805</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:12:46.073</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:12:49.41</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:12:52.635</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:17:07.428</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:17:11.108</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:17:14.313</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:17:17.506</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:17:20.459</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:19:44.681</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:19:48.413</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:19:51.513</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:19:54.658</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:19:57.657</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:21:37.055</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:21:40.795</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:21:43.93</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:21:47.123</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:21:50.118</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:54:46.378</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:54:50.86</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:54:54.164</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:54:57.271</t>
+  </si>
+  <si>
+    <t>2026-03-25T18:55:00.283</t>
+  </si>
+  <si>
+    <t>Output (y_t)</t>
+  </si>
+  <si>
+    <t>Permanent liquidity innovations</t>
+  </si>
+  <si>
+    <t>2026-03-30T11:19:07.302</t>
+  </si>
+  <si>
+    <t>2026-03-30T11:20:02.981</t>
+  </si>
+  <si>
+    <t>2026-03-30T11:21:21.11</t>
+  </si>
+  <si>
+    <t>2026-03-30T11:34:30.372</t>
+  </si>
+  <si>
+    <t>2026-03-30T11:36:06.554</t>
   </si>
 </sst>
 </file>
@@ -822,6 +1239,3082 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
+  <dimension ref="A1:AC21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:29">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K1" t="s">
+        <v>220</v>
+      </c>
+      <c r="L1" t="s">
+        <v>199</v>
+      </c>
+      <c r="M1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N1" t="s">
+        <v>200</v>
+      </c>
+      <c r="O1" t="s">
+        <v>201</v>
+      </c>
+      <c r="P1" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>203</v>
+      </c>
+      <c r="R1" t="s">
+        <v>221</v>
+      </c>
+      <c r="S1" t="s">
+        <v>204</v>
+      </c>
+      <c r="T1" t="s">
+        <v>205</v>
+      </c>
+      <c r="U1" t="s">
+        <v>206</v>
+      </c>
+      <c r="V1" t="s">
+        <v>207</v>
+      </c>
+      <c r="W1" t="s">
+        <v>208</v>
+      </c>
+      <c r="X1" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>223</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.0</v>
+      </c>
+      <c r="C2">
+        <v>0.014934334858653578</v>
+      </c>
+      <c r="D2">
+        <v>-0.9052392657323787</v>
+      </c>
+      <c r="E2">
+        <v>-1.0168327755648958</v>
+      </c>
+      <c r="F2">
+        <v>0.9681399006074287</v>
+      </c>
+      <c r="G2">
+        <v>-1.0</v>
+      </c>
+      <c r="H2">
+        <v>-0.01413114937975354</v>
+      </c>
+      <c r="I2">
+        <v>0.010611389448048958</v>
+      </c>
+      <c r="J2">
+        <v>-4.748347915873213e-15</v>
+      </c>
+      <c r="K2">
+        <v>-1.7088255604591185</v>
+      </c>
+      <c r="L2">
+        <v>0.293966292813274</v>
+      </c>
+      <c r="M2">
+        <v>0.0</v>
+      </c>
+      <c r="N2">
+        <v>1.485218579098167e-15</v>
+      </c>
+      <c r="O2">
+        <v>-0.08040185016545286</v>
+      </c>
+      <c r="P2">
+        <v>0.00577910790065508</v>
+      </c>
+      <c r="Q2">
+        <v>-1.0</v>
+      </c>
+      <c r="R2">
+        <v>2.2111564327550956e-15</v>
+      </c>
+      <c r="S2">
+        <v>-1.300438309001632</v>
+      </c>
+      <c r="T2">
+        <v>0.01691563407698074</v>
+      </c>
+      <c r="U2">
+        <v>-3.1764938580195055</v>
+      </c>
+      <c r="V2">
+        <v>-1.0</v>
+      </c>
+      <c r="W2">
+        <v>-1.0</v>
+      </c>
+      <c r="X2">
+        <v>-1.0</v>
+      </c>
+      <c r="Y2">
+        <v>0.5707903061494471</v>
+      </c>
+      <c r="Z2">
+        <v>4.5087075869680536e-17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>-0.25661611979210086</v>
+      </c>
+      <c r="C3">
+        <v>0.019489179085775514</v>
+      </c>
+      <c r="D3">
+        <v>-0.9050688766126486</v>
+      </c>
+      <c r="E3">
+        <v>-1.0187192459363448</v>
+      </c>
+      <c r="F3">
+        <v>0.661562881766815</v>
+      </c>
+      <c r="G3">
+        <v>-1.0</v>
+      </c>
+      <c r="H3">
+        <v>-0.016915634076980258</v>
+      </c>
+      <c r="I3">
+        <v>-0.03186432239033837</v>
+      </c>
+      <c r="J3">
+        <v>-5.3791489454505824e-15</v>
+      </c>
+      <c r="K3">
+        <v>-0.30395262181504173</v>
+      </c>
+      <c r="L3">
+        <v>0.06325583478741865</v>
+      </c>
+      <c r="M3">
+        <v>0.0</v>
+      </c>
+      <c r="N3">
+        <v>1.459966730155892e-15</v>
+      </c>
+      <c r="O3">
+        <v>-0.09476073426764205</v>
+      </c>
+      <c r="P3">
+        <v>0.0064720161883647775</v>
+      </c>
+      <c r="Q3">
+        <v>-1.0</v>
+      </c>
+      <c r="R3">
+        <v>2.6608334657322267e-15</v>
+      </c>
+      <c r="S3">
+        <v>-0.4303211772063297</v>
+      </c>
+      <c r="T3">
+        <v>-0.16045476866356317</v>
+      </c>
+      <c r="U3">
+        <v>-2.3399162031955485</v>
+      </c>
+      <c r="V3">
+        <v>-0.1644474583019147</v>
+      </c>
+      <c r="W3">
+        <v>-0.9999999999999999</v>
+      </c>
+      <c r="X3">
+        <v>-1.0</v>
+      </c>
+      <c r="Y3">
+        <v>0.34439031998447733</v>
+      </c>
+      <c r="Z3">
+        <v>-1.2006389061474226e-16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>-0.15033445389395944</v>
+      </c>
+      <c r="C4">
+        <v>0.022712803829237183</v>
+      </c>
+      <c r="D4">
+        <v>-0.9086031713999636</v>
+      </c>
+      <c r="E4">
+        <v>-1.0212231064529043</v>
+      </c>
+      <c r="F4">
+        <v>0.38221670065155294</v>
+      </c>
+      <c r="G4">
+        <v>-1.0</v>
+      </c>
+      <c r="H4">
+        <v>-0.01741746642483185</v>
+      </c>
+      <c r="I4">
+        <v>-0.1307158788307793</v>
+      </c>
+      <c r="J4">
+        <v>-5.818305649211937e-15</v>
+      </c>
+      <c r="K4">
+        <v>-0.4569533138979312</v>
+      </c>
+      <c r="L4">
+        <v>-0.24234210056676064</v>
+      </c>
+      <c r="M4">
+        <v>0.0</v>
+      </c>
+      <c r="N4">
+        <v>1.4252250825956042e-15</v>
+      </c>
+      <c r="O4">
+        <v>-0.09493112338737889</v>
+      </c>
+      <c r="P4">
+        <v>0.005870605597528342</v>
+      </c>
+      <c r="Q4">
+        <v>-1.0</v>
+      </c>
+      <c r="R4">
+        <v>3.282663855239666e-15</v>
+      </c>
+      <c r="S4">
+        <v>-0.3875986598402924</v>
+      </c>
+      <c r="T4">
+        <v>-0.3962673948995753</v>
+      </c>
+      <c r="U4">
+        <v>-1.8379967551838206</v>
+      </c>
+      <c r="V4">
+        <v>-0.1817890425383521</v>
+      </c>
+      <c r="W4">
+        <v>-1.0</v>
+      </c>
+      <c r="X4">
+        <v>-1.0</v>
+      </c>
+      <c r="Y4">
+        <v>0.2644610026980745</v>
+      </c>
+      <c r="Z4">
+        <v>-2.4823694109419566e-16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>-0.11633708234053922</v>
+      </c>
+      <c r="C5">
+        <v>0.02499288986750394</v>
+      </c>
+      <c r="D5">
+        <v>-0.9135571947895866</v>
+      </c>
+      <c r="E5">
+        <v>-1.0229856195207134</v>
+      </c>
+      <c r="F5">
+        <v>0.10240916673370665</v>
+      </c>
+      <c r="G5">
+        <v>-1.0</v>
+      </c>
+      <c r="H5">
+        <v>-0.017374125841632445</v>
+      </c>
+      <c r="I5">
+        <v>-0.2691110903402725</v>
+      </c>
+      <c r="J5">
+        <v>-6.090418604880365e-15</v>
+      </c>
+      <c r="K5">
+        <v>-0.4313484542300172</v>
+      </c>
+      <c r="L5">
+        <v>-0.45311682283775634</v>
+      </c>
+      <c r="M5">
+        <v>0.0</v>
+      </c>
+      <c r="N5">
+        <v>1.3831794292525924e-15</v>
+      </c>
+      <c r="O5">
+        <v>-0.09139682860006812</v>
+      </c>
+      <c r="P5">
+        <v>0.0048651298028423995</v>
+      </c>
+      <c r="Q5">
+        <v>-1.0000000000000002</v>
+      </c>
+      <c r="R5">
+        <v>3.849757773399015e-15</v>
+      </c>
+      <c r="S5">
+        <v>-0.24997531697629544</v>
+      </c>
+      <c r="T5">
+        <v>-0.5594916702932204</v>
+      </c>
+      <c r="U5">
+        <v>-1.505705246087438</v>
+      </c>
+      <c r="V5">
+        <v>-0.08260789907318522</v>
+      </c>
+      <c r="W5">
+        <v>-1.0000000000000002</v>
+      </c>
+      <c r="X5">
+        <v>-1.0</v>
+      </c>
+      <c r="Y5">
+        <v>0.20730999837501063</v>
+      </c>
+      <c r="Z5">
+        <v>-3.4343469768482743e-16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>-0.08906487405434146</v>
+      </c>
+      <c r="C6">
+        <v>0.026597847092238246</v>
+      </c>
+      <c r="D6">
+        <v>-0.9192954503986281</v>
+      </c>
+      <c r="E6">
+        <v>-1.024222679618266</v>
+      </c>
+      <c r="F6">
+        <v>-0.135456549530828</v>
+      </c>
+      <c r="G6">
+        <v>-1.0</v>
+      </c>
+      <c r="H6">
+        <v>-0.01707253891919418</v>
+      </c>
+      <c r="I6">
+        <v>-0.3930452374105372</v>
+      </c>
+      <c r="J6">
+        <v>-6.2190208917890676e-15</v>
+      </c>
+      <c r="K6">
+        <v>-0.413320503578175</v>
+      </c>
+      <c r="L6">
+        <v>-0.58858301151456</v>
+      </c>
+      <c r="M6">
+        <v>0.0</v>
+      </c>
+      <c r="N6">
+        <v>1.3357185412306094e-15</v>
+      </c>
+      <c r="O6">
+        <v>-0.08644280521045197</v>
+      </c>
+      <c r="P6">
+        <v>0.0037689465803442124</v>
+      </c>
+      <c r="Q6">
+        <v>-0.9999999999999998</v>
+      </c>
+      <c r="R6">
+        <v>4.367580875500832e-15</v>
+      </c>
+      <c r="S6">
+        <v>-0.15602608614441268</v>
+      </c>
+      <c r="T6">
+        <v>-0.6649870094715363</v>
+      </c>
+      <c r="U6">
+        <v>-1.2504215444989601</v>
+      </c>
+      <c r="V6">
+        <v>-0.015638695049281635</v>
+      </c>
+      <c r="W6">
+        <v>-1.0</v>
+      </c>
+      <c r="X6">
+        <v>-1.0</v>
+      </c>
+      <c r="Y6">
+        <v>0.16513266434240137</v>
+      </c>
+      <c r="Z6">
+        <v>-4.096415612004622e-16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>-0.0662202549382754</v>
+      </c>
+      <c r="C7">
+        <v>0.027718258601120767</v>
+      </c>
+      <c r="D7">
+        <v>-0.9255267684593391</v>
+      </c>
+      <c r="E7">
+        <v>-1.0250883518532223</v>
+      </c>
+      <c r="F7">
+        <v>-0.31260461262184863</v>
+      </c>
+      <c r="G7">
+        <v>-1.0</v>
+      </c>
+      <c r="H7">
+        <v>-0.016526036745515102</v>
+      </c>
+      <c r="I7">
+        <v>-0.4759843533789608</v>
+      </c>
+      <c r="J7">
+        <v>-6.2261913106385175e-15</v>
+      </c>
+      <c r="K7">
+        <v>-0.399973267708569</v>
+      </c>
+      <c r="L7">
+        <v>-0.6778753841761269</v>
+      </c>
+      <c r="M7">
+        <v>0.0</v>
+      </c>
+      <c r="N7">
+        <v>1.2844545829858365e-15</v>
+      </c>
+      <c r="O7">
+        <v>-0.08070454960141288</v>
+      </c>
+      <c r="P7">
+        <v>0.002755647131150306</v>
+      </c>
+      <c r="Q7">
+        <v>-1.0</v>
+      </c>
+      <c r="R7">
+        <v>4.839569422838582e-15</v>
+      </c>
+      <c r="S7">
+        <v>-0.0904417367180636</v>
+      </c>
+      <c r="T7">
+        <v>-0.7350899114635326</v>
+      </c>
+      <c r="U7">
+        <v>-1.01978897436764</v>
+      </c>
+      <c r="V7">
+        <v>0.02876402916085786</v>
+      </c>
+      <c r="W7">
+        <v>-0.9999999999999999</v>
+      </c>
+      <c r="X7">
+        <v>-1.0</v>
+      </c>
+      <c r="Y7">
+        <v>0.13295188727357443</v>
+      </c>
+      <c r="Z7">
+        <v>-4.50718655276338e-16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>-0.32142721498078364</v>
+      </c>
+      <c r="C8">
+        <v>0.025088351853244956</v>
+      </c>
+      <c r="D8">
+        <v>1.3414080441414482</v>
+      </c>
+      <c r="E8">
+        <v>-0.7939186961608264</v>
+      </c>
+      <c r="F8">
+        <v>-0.4268481637496183</v>
+      </c>
+      <c r="G8">
+        <v>-0.33531927654145866</v>
+      </c>
+      <c r="H8">
+        <v>-0.015715621463581707</v>
+      </c>
+      <c r="I8">
+        <v>-0.509228971285405</v>
+      </c>
+      <c r="J8">
+        <v>-6.132302703677181e-15</v>
+      </c>
+      <c r="K8">
+        <v>0.0</v>
+      </c>
+      <c r="L8">
+        <v>-0.07475322826127526</v>
+      </c>
+      <c r="M8">
+        <v>0.0</v>
+      </c>
+      <c r="N8">
+        <v>1.2307465784418506e-15</v>
+      </c>
+      <c r="O8">
+        <v>-0.07447323154070251</v>
+      </c>
+      <c r="P8">
+        <v>0.0019374155489657041</v>
+      </c>
+      <c r="Q8">
+        <v>0.03635145783199292</v>
+      </c>
+      <c r="R8">
+        <v>4.764069600892054e-15</v>
+      </c>
+      <c r="S8">
+        <v>0.6194520057701742</v>
+      </c>
+      <c r="T8">
+        <v>0.25242038313511095</v>
+      </c>
+      <c r="U8">
+        <v>-0.7834310456132124</v>
+      </c>
+      <c r="V8">
+        <v>1.091729446652716</v>
+      </c>
+      <c r="W8">
+        <v>1.2734464728070378</v>
+      </c>
+      <c r="X8">
+        <v>-0.7720607974650294</v>
+      </c>
+      <c r="Y8">
+        <v>-0.02251291308733272</v>
+      </c>
+      <c r="Z8">
+        <v>-4.703276363848557e-16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.0</v>
+      </c>
+      <c r="C9">
+        <v>0.021857898695817907</v>
+      </c>
+      <c r="D9">
+        <v>1.342653275460827</v>
+      </c>
+      <c r="E9">
+        <v>-0.6085373332558515</v>
+      </c>
+      <c r="F9">
+        <v>-0.2899290309981144</v>
+      </c>
+      <c r="G9">
+        <v>-0.21682340529141533</v>
+      </c>
+      <c r="H9">
+        <v>-0.014638909287259121</v>
+      </c>
+      <c r="I9">
+        <v>-0.1920202389789131</v>
+      </c>
+      <c r="J9">
+        <v>-5.95587947588401e-15</v>
+      </c>
+      <c r="K9">
+        <v>0.0</v>
+      </c>
+      <c r="L9">
+        <v>-0.0003884190598680559</v>
+      </c>
+      <c r="M9">
+        <v>0.0</v>
+      </c>
+      <c r="N9">
+        <v>1.1757253026558572e-15</v>
+      </c>
+      <c r="O9">
+        <v>-0.06796157133445065</v>
+      </c>
+      <c r="P9">
+        <v>0.0013812611296645967</v>
+      </c>
+      <c r="Q9">
+        <v>0.12921754417741121</v>
+      </c>
+      <c r="R9">
+        <v>4.64532180302989e-15</v>
+      </c>
+      <c r="S9">
+        <v>0.0</v>
+      </c>
+      <c r="T9">
+        <v>0.30989248609914577</v>
+      </c>
+      <c r="U9">
+        <v>0.1338662711154739</v>
+      </c>
+      <c r="V9">
+        <v>0.0</v>
+      </c>
+      <c r="W9">
+        <v>1.2810045803204857</v>
+      </c>
+      <c r="X9">
+        <v>-0.5897480989509019</v>
+      </c>
+      <c r="Y9">
+        <v>-0.09553656104211461</v>
+      </c>
+      <c r="Z9">
+        <v>-4.718786361864179e-16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.0</v>
+      </c>
+      <c r="C10">
+        <v>0.018789234304968698</v>
+      </c>
+      <c r="D10">
+        <v>1.086818092717859</v>
+      </c>
+      <c r="E10">
+        <v>-0.4807875592590392</v>
+      </c>
+      <c r="F10">
+        <v>-0.1866280114390827</v>
+      </c>
+      <c r="G10">
+        <v>-0.18902929303563276</v>
+      </c>
+      <c r="H10">
+        <v>-0.013449013874046038</v>
+      </c>
+      <c r="I10">
+        <v>0.011473420303155235</v>
+      </c>
+      <c r="J10">
+        <v>-5.713541401188098e-15</v>
+      </c>
+      <c r="K10">
+        <v>0.0</v>
+      </c>
+      <c r="L10">
+        <v>-0.005133512329801582</v>
+      </c>
+      <c r="M10">
+        <v>0.0</v>
+      </c>
+      <c r="N10">
+        <v>1.1203183827245261e-15</v>
+      </c>
+      <c r="O10">
+        <v>-0.06164869514037899</v>
+      </c>
+      <c r="P10">
+        <v>0.0010320168600286752</v>
+      </c>
+      <c r="Q10">
+        <v>0.09281887756465035</v>
+      </c>
+      <c r="R10">
+        <v>4.491998523377305e-15</v>
+      </c>
+      <c r="S10">
+        <v>0.0</v>
+      </c>
+      <c r="T10">
+        <v>0.24713842664744773</v>
+      </c>
+      <c r="U10">
+        <v>0.6708481598313336</v>
+      </c>
+      <c r="V10">
+        <v>0.0</v>
+      </c>
+      <c r="W10">
+        <v>1.030942153310926</v>
+      </c>
+      <c r="X10">
+        <v>-0.464701507136287</v>
+      </c>
+      <c r="Y10">
+        <v>-0.12449326593762322</v>
+      </c>
+      <c r="Z10">
+        <v>-4.584979772835131e-16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.0</v>
+      </c>
+      <c r="C11">
+        <v>0.01608605212276941</v>
+      </c>
+      <c r="D11">
+        <v>0.8753826214960259</v>
+      </c>
+      <c r="E11">
+        <v>-0.3926044788503507</v>
+      </c>
+      <c r="F11">
+        <v>-0.12771769960939094</v>
+      </c>
+      <c r="G11">
+        <v>-0.17430464489742342</v>
+      </c>
+      <c r="H11">
+        <v>-0.012273975098444636</v>
+      </c>
+      <c r="I11">
+        <v>0.10976997965989511</v>
+      </c>
+      <c r="J11">
+        <v>-5.420013811365651e-15</v>
+      </c>
+      <c r="K11">
+        <v>0.0</v>
+      </c>
+      <c r="L11">
+        <v>-0.01486052308658145</v>
+      </c>
+      <c r="M11">
+        <v>0.0</v>
+      </c>
+      <c r="N11">
+        <v>1.065274741776018e-15</v>
+      </c>
+      <c r="O11">
+        <v>-0.055875939406966856</v>
+      </c>
+      <c r="P11">
+        <v>0.0008257253275572897</v>
+      </c>
+      <c r="Q11">
+        <v>0.0564656832109975</v>
+      </c>
+      <c r="R11">
+        <v>4.3117861602909845e-15</v>
+      </c>
+      <c r="S11">
+        <v>0.0</v>
+      </c>
+      <c r="T11">
+        <v>0.1908110132772078</v>
+      </c>
+      <c r="U11">
+        <v>0.900240675818676</v>
+      </c>
+      <c r="V11">
+        <v>0.0</v>
+      </c>
+      <c r="W11">
+        <v>0.8245778752789112</v>
+      </c>
+      <c r="X11">
+        <v>-0.37880842932430453</v>
+      </c>
+      <c r="Y11">
+        <v>-0.13203757619379708</v>
+      </c>
+      <c r="Z11">
+        <v>-4.3301173041301315e-16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.0</v>
+      </c>
+      <c r="C12">
+        <v>0.013796049526061562</v>
+      </c>
+      <c r="D12">
+        <v>0.7251580193976521</v>
+      </c>
+      <c r="E12">
+        <v>-0.3298711918506749</v>
+      </c>
+      <c r="F12">
+        <v>-0.09508155121341409</v>
+      </c>
+      <c r="G12">
+        <v>-0.16167964518980515</v>
+      </c>
+      <c r="H12">
+        <v>-0.01118589910661117</v>
+      </c>
+      <c r="I12">
+        <v>0.1495199508970184</v>
+      </c>
+      <c r="J12">
+        <v>-5.0881872199663204e-15</v>
+      </c>
+      <c r="K12">
+        <v>0.0</v>
+      </c>
+      <c r="L12">
+        <v>-0.020859084333534228</v>
+      </c>
+      <c r="M12">
+        <v>0.0</v>
+      </c>
+      <c r="N12">
+        <v>1.0111877997415131e-15</v>
+      </c>
+      <c r="O12">
+        <v>-0.05080474621714511</v>
+      </c>
+      <c r="P12">
+        <v>0.0007171203238718381</v>
+      </c>
+      <c r="Q12">
+        <v>0.03246778428510973</v>
+      </c>
+      <c r="R12">
+        <v>4.1114168903484515e-15</v>
+      </c>
+      <c r="S12">
+        <v>0.0</v>
+      </c>
+      <c r="T12">
+        <v>0.15149212646966237</v>
+      </c>
+      <c r="U12">
+        <v>0.9636687953744474</v>
+      </c>
+      <c r="V12">
+        <v>0.0</v>
+      </c>
+      <c r="W12">
+        <v>0.6786817445489453</v>
+      </c>
+      <c r="X12">
+        <v>-0.31795816460031373</v>
+      </c>
+      <c r="Y12">
+        <v>-0.1296263356099685</v>
+      </c>
+      <c r="Z12">
+        <v>-3.979416485401561e-16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.0</v>
+      </c>
+      <c r="C13">
+        <v>0.011913027250374837</v>
+      </c>
+      <c r="D13">
+        <v>0.6184168634141056</v>
+      </c>
+      <c r="E13">
+        <v>-0.28392811707520316</v>
+      </c>
+      <c r="F13">
+        <v>-0.07594118759622955</v>
+      </c>
+      <c r="G13">
+        <v>-0.15043234364362912</v>
+      </c>
+      <c r="H13">
+        <v>-0.01021669738224655</v>
+      </c>
+      <c r="I13">
+        <v>0.16049780056471308</v>
+      </c>
+      <c r="J13">
+        <v>-4.72921222665598e-15</v>
+      </c>
+      <c r="K13">
+        <v>0.0</v>
+      </c>
+      <c r="L13">
+        <v>-0.023960668606128846</v>
+      </c>
+      <c r="M13">
+        <v>0.0</v>
+      </c>
+      <c r="N13">
+        <v>9.585170600904135e-16</v>
+      </c>
+      <c r="O13">
+        <v>-0.04647627484873401</v>
+      </c>
+      <c r="P13">
+        <v>0.0006770687568986135</v>
+      </c>
+      <c r="Q13">
+        <v>0.01729056859543368</v>
+      </c>
+      <c r="R13">
+        <v>3.896718652643837e-15</v>
+      </c>
+      <c r="S13">
+        <v>0.0</v>
+      </c>
+      <c r="T13">
+        <v>0.12444684763273535</v>
+      </c>
+      <c r="U13">
+        <v>0.947477959475338</v>
+      </c>
+      <c r="V13">
+        <v>0.0</v>
+      </c>
+      <c r="W13">
+        <v>0.5755513070359216</v>
+      </c>
+      <c r="X13">
+        <v>-0.27351925860025716</v>
+      </c>
+      <c r="Y13">
+        <v>-0.12278283032448467</v>
+      </c>
+      <c r="Z13">
+        <v>-3.5551049288211273e-16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>0.0</v>
+      </c>
+      <c r="C14">
+        <v>0.010408858474957995</v>
+      </c>
+      <c r="D14">
+        <v>0.5404283904458609</v>
+      </c>
+      <c r="E14">
+        <v>-0.24952897635556878</v>
+      </c>
+      <c r="F14">
+        <v>-0.0635486380644424</v>
+      </c>
+      <c r="G14">
+        <v>-0.14073440612023572</v>
+      </c>
+      <c r="H14">
+        <v>-0.009375346955349115</v>
+      </c>
+      <c r="I14">
+        <v>0.15807983378839663</v>
+      </c>
+      <c r="J14">
+        <v>-4.352618103282998e-15</v>
+      </c>
+      <c r="K14">
+        <v>0.0</v>
+      </c>
+      <c r="L14">
+        <v>-0.025457289392786728</v>
+      </c>
+      <c r="M14">
+        <v>0.0</v>
+      </c>
+      <c r="N14">
+        <v>9.0760787360947e-16</v>
+      </c>
+      <c r="O14">
+        <v>-0.04286555637820762</v>
+      </c>
+      <c r="P14">
+        <v>0.000686394931765014</v>
+      </c>
+      <c r="Q14">
+        <v>0.007412129983506349</v>
+      </c>
+      <c r="R14">
+        <v>3.672677208093998e-15</v>
+      </c>
+      <c r="S14">
+        <v>0.0</v>
+      </c>
+      <c r="T14">
+        <v>0.10527842914313104</v>
+      </c>
+      <c r="U14">
+        <v>0.8957636284726316</v>
+      </c>
+      <c r="V14">
+        <v>0.0</v>
+      </c>
+      <c r="W14">
+        <v>0.5005134811262363</v>
+      </c>
+      <c r="X14">
+        <v>-0.24028292037616167</v>
+      </c>
+      <c r="Y14">
+        <v>-0.11413462504137417</v>
+      </c>
+      <c r="Z14">
+        <v>-3.076542318857994e-16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>0.0</v>
+      </c>
+      <c r="C15">
+        <v>0.009246055979417576</v>
+      </c>
+      <c r="D15">
+        <v>0.4817982033686391</v>
+      </c>
+      <c r="E15">
+        <v>-0.22334003993228627</v>
+      </c>
+      <c r="F15">
+        <v>-0.054617087271392264</v>
+      </c>
+      <c r="G15">
+        <v>-0.13251129629382138</v>
+      </c>
+      <c r="H15">
+        <v>-0.008658871647518815</v>
+      </c>
+      <c r="I15">
+        <v>0.1497205073739659</v>
+      </c>
+      <c r="J15">
+        <v>-3.966445739574202e-15</v>
+      </c>
+      <c r="K15">
+        <v>0.0</v>
+      </c>
+      <c r="L15">
+        <v>-0.026107079521606846</v>
+      </c>
+      <c r="M15">
+        <v>0.0</v>
+      </c>
+      <c r="N15">
+        <v>8.58709289444294e-16</v>
+      </c>
+      <c r="O15">
+        <v>-0.03991490931964535</v>
+      </c>
+      <c r="P15">
+        <v>0.0007316394567861879</v>
+      </c>
+      <c r="Q15">
+        <v>0.0007360314313030469</v>
+      </c>
+      <c r="R15">
+        <v>3.4435054511492708e-15</v>
+      </c>
+      <c r="S15">
+        <v>0.0</v>
+      </c>
+      <c r="T15">
+        <v>0.09123351500585693</v>
+      </c>
+      <c r="U15">
+        <v>0.8298521301499666</v>
+      </c>
+      <c r="V15">
+        <v>0.0</v>
+      </c>
+      <c r="W15">
+        <v>0.44424580942170055</v>
+      </c>
+      <c r="X15">
+        <v>-0.21495635644193878</v>
+      </c>
+      <c r="Y15">
+        <v>-0.10493301190703386</v>
+      </c>
+      <c r="Z15">
+        <v>-2.560390285301014e-16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.0</v>
+      </c>
+      <c r="C16">
+        <v>0.008383683490356524</v>
+      </c>
+      <c r="D16">
+        <v>0.4366238442871805</v>
+      </c>
+      <c r="E16">
+        <v>-0.2031125783989823</v>
+      </c>
+      <c r="F16">
+        <v>-0.04758413666166646</v>
+      </c>
+      <c r="G16">
+        <v>-0.12550992997104138</v>
+      </c>
+      <c r="H16">
+        <v>-0.008058405359832108</v>
+      </c>
+      <c r="I16">
+        <v>0.1389619919126751</v>
+      </c>
+      <c r="J16">
+        <v>-3.577387609018251e-15</v>
+      </c>
+      <c r="K16">
+        <v>0.0</v>
+      </c>
+      <c r="L16">
+        <v>-0.026285283078346433</v>
+      </c>
+      <c r="M16">
+        <v>0.0</v>
+      </c>
+      <c r="N16">
+        <v>8.119899893854588e-16</v>
+      </c>
+      <c r="O16">
+        <v>-0.0375523939469565</v>
+      </c>
+      <c r="P16">
+        <v>0.000802718696996974</v>
+      </c>
+      <c r="Q16">
+        <v>-0.003889122939751438</v>
+      </c>
+      <c r="R16">
+        <v>3.2127161953212456e-15</v>
+      </c>
+      <c r="S16">
+        <v>0.0</v>
+      </c>
+      <c r="T16">
+        <v>0.08065991723176327</v>
+      </c>
+      <c r="U16">
+        <v>0.7598752475964856</v>
+      </c>
+      <c r="V16">
+        <v>0.0</v>
+      </c>
+      <c r="W16">
+        <v>0.4009221257836246</v>
+      </c>
+      <c r="X16">
+        <v>-0.19533210087644076</v>
+      </c>
+      <c r="Y16">
+        <v>-0.09577806619976337</v>
+      </c>
+      <c r="Z16">
+        <v>-2.0208132342173716e-16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>0.0</v>
+      </c>
+      <c r="C17">
+        <v>0.0077804775225492956</v>
+      </c>
+      <c r="D17">
+        <v>0.40103636978371526</v>
+      </c>
+      <c r="E17">
+        <v>-0.18725096121170928</v>
+      </c>
+      <c r="F17">
+        <v>-0.041706041964552354</v>
+      </c>
+      <c r="G17">
+        <v>-0.11943132506086479</v>
+      </c>
+      <c r="H17">
+        <v>-0.007562411629084261</v>
+      </c>
+      <c r="I17">
+        <v>0.1274809751644383</v>
+      </c>
+      <c r="J17">
+        <v>-3.1909291091707866e-15</v>
+      </c>
+      <c r="K17">
+        <v>0.0</v>
+      </c>
+      <c r="L17">
+        <v>-0.02616898444270438</v>
+      </c>
+      <c r="M17">
+        <v>0.0</v>
+      </c>
+      <c r="N17">
+        <v>7.675523614222594e-16</v>
+      </c>
+      <c r="O17">
+        <v>-0.03570171850357122</v>
+      </c>
+      <c r="P17">
+        <v>0.0008917141447645979</v>
+      </c>
+      <c r="Q17">
+        <v>-0.007109862531682359</v>
+      </c>
+      <c r="R17">
+        <v>2.9831955381432905e-15</v>
+      </c>
+      <c r="S17">
+        <v>0.0</v>
+      </c>
+      <c r="T17">
+        <v>0.07252762679352115</v>
+      </c>
+      <c r="U17">
+        <v>0.6906149433032079</v>
+      </c>
+      <c r="V17">
+        <v>0.0</v>
+      </c>
+      <c r="W17">
+        <v>0.36674879385082393</v>
+      </c>
+      <c r="X17">
+        <v>-0.17985435310070974</v>
+      </c>
+      <c r="Y17">
+        <v>-0.08695920253178047</v>
+      </c>
+      <c r="Z17">
+        <v>-1.4696966627184697e-16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.0</v>
+      </c>
+      <c r="C18">
+        <v>0.007396608111006103</v>
+      </c>
+      <c r="D18">
+        <v>0.3723706803376171</v>
+      </c>
+      <c r="E18">
+        <v>-0.17458324950462203</v>
+      </c>
+      <c r="F18">
+        <v>-0.03662051111390226</v>
+      </c>
+      <c r="G18">
+        <v>-0.11400111332981608</v>
+      </c>
+      <c r="H18">
+        <v>-0.007158400918384182</v>
+      </c>
+      <c r="I18">
+        <v>0.11607232508361541</v>
+      </c>
+      <c r="J18">
+        <v>-2.811487052786614e-15</v>
+      </c>
+      <c r="K18">
+        <v>0.0</v>
+      </c>
+      <c r="L18">
+        <v>-0.025843035833772954</v>
+      </c>
+      <c r="M18">
+        <v>0.0</v>
+      </c>
+      <c r="N18">
+        <v>7.254448089823672e-16</v>
+      </c>
+      <c r="O18">
+        <v>-0.03428757593290447</v>
+      </c>
+      <c r="P18">
+        <v>0.0009922425475876132</v>
+      </c>
+      <c r="Q18">
+        <v>-0.00931441898106726</v>
+      </c>
+      <c r="R18">
+        <v>2.7572746488062356e-15</v>
+      </c>
+      <c r="S18">
+        <v>0.0</v>
+      </c>
+      <c r="T18">
+        <v>0.0661556808140292</v>
+      </c>
+      <c r="U18">
+        <v>0.6243059012374765</v>
+      </c>
+      <c r="V18">
+        <v>0.0</v>
+      </c>
+      <c r="W18">
+        <v>0.33913213797309316</v>
+      </c>
+      <c r="X18">
+        <v>-0.16738855315147141</v>
+      </c>
+      <c r="Y18">
+        <v>-0.07861477151704166</v>
+      </c>
+      <c r="Z18">
+        <v>-9.168724583972224e-17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.0</v>
+      </c>
+      <c r="C19">
+        <v>0.007194696353156129</v>
+      </c>
+      <c r="D19">
+        <v>0.3487184850955369</v>
+      </c>
+      <c r="E19">
+        <v>-0.16423224830811753</v>
+      </c>
+      <c r="F19">
+        <v>-0.032141761034904154</v>
+      </c>
+      <c r="G19">
+        <v>-0.10899552505862764</v>
+      </c>
+      <c r="H19">
+        <v>-0.00683386790670013</v>
+      </c>
+      <c r="I19">
+        <v>0.10511209411254013</v>
+      </c>
+      <c r="J19">
+        <v>-2.442542261379695e-15</v>
+      </c>
+      <c r="K19">
+        <v>0.0</v>
+      </c>
+      <c r="L19">
+        <v>-0.025351851210866826</v>
+      </c>
+      <c r="M19">
+        <v>0.0</v>
+      </c>
+      <c r="N19">
+        <v>6.85672417796208e-16</v>
+      </c>
+      <c r="O19">
+        <v>-0.03323854236453495</v>
+      </c>
+      <c r="P19">
+        <v>0.0010991078371503501</v>
+      </c>
+      <c r="Q19">
+        <v>-0.010756344511751635</v>
+      </c>
+      <c r="R19">
+        <v>2.5367984281668596e-15</v>
+      </c>
+      <c r="S19">
+        <v>0.0</v>
+      </c>
+      <c r="T19">
+        <v>0.06106905665507224</v>
+      </c>
+      <c r="U19">
+        <v>0.5619574797877019</v>
+      </c>
+      <c r="V19">
+        <v>0.0</v>
+      </c>
+      <c r="W19">
+        <v>0.3162298539971159</v>
+      </c>
+      <c r="X19">
+        <v>-0.1570918596230652</v>
+      </c>
+      <c r="Y19">
+        <v>-0.07080733196772027</v>
+      </c>
+      <c r="Z19">
+        <v>-3.7034320309053016e-17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>0.0</v>
+      </c>
+      <c r="C20">
+        <v>0.00714038868505687</v>
+      </c>
+      <c r="D20">
+        <v>0.3286809863978689</v>
+      </c>
+      <c r="E20">
+        <v>-0.15553704193562543</v>
+      </c>
+      <c r="F20">
+        <v>-0.028165670032337484</v>
+      </c>
+      <c r="G20">
+        <v>-0.10424529474024744</v>
+      </c>
+      <c r="H20">
+        <v>-0.006576814916789152</v>
+      </c>
+      <c r="I20">
+        <v>0.09477441002674511</v>
+      </c>
+      <c r="J20">
+        <v>-2.0867641687792137e-15</v>
+      </c>
+      <c r="K20">
+        <v>0.0</v>
+      </c>
+      <c r="L20">
+        <v>-0.024723052520219828</v>
+      </c>
+      <c r="M20">
+        <v>0.0</v>
+      </c>
+      <c r="N20">
+        <v>6.482061166984758e-16</v>
+      </c>
+      <c r="O20">
+        <v>-0.032488631098430074</v>
+      </c>
+      <c r="P20">
+        <v>0.0012080873199841746</v>
+      </c>
+      <c r="Q20">
+        <v>-0.011614831036960739</v>
+      </c>
+      <c r="R20">
+        <v>2.3231899821690162e-15</v>
+      </c>
+      <c r="S20">
+        <v>0.0</v>
+      </c>
+      <c r="T20">
+        <v>0.05692335170514526</v>
+      </c>
+      <c r="U20">
+        <v>0.5039768198912442</v>
+      </c>
+      <c r="V20">
+        <v>0.0</v>
+      </c>
+      <c r="W20">
+        <v>0.2967029198221135</v>
+      </c>
+      <c r="X20">
+        <v>-0.14833439404904106</v>
+      </c>
+      <c r="Y20">
+        <v>-0.06355970087713314</v>
+      </c>
+      <c r="Z20">
+        <v>1.6350040134988204e-17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.0</v>
+      </c>
+      <c r="C21">
+        <v>0.007202647886588068</v>
+      </c>
+      <c r="D21">
+        <v>0.3112228747784288</v>
+      </c>
+      <c r="E21">
+        <v>-0.1480010128972768</v>
+      </c>
+      <c r="F21">
+        <v>-0.024626194880877153</v>
+      </c>
+      <c r="G21">
+        <v>-0.09963034839537782</v>
+      </c>
+      <c r="H21">
+        <v>-0.006376045364124454</v>
+      </c>
+      <c r="I21">
+        <v>0.08513351486885028</v>
+      </c>
+      <c r="J21">
+        <v>-1.7461261073911644e-15</v>
+      </c>
+      <c r="K21">
+        <v>0.0</v>
+      </c>
+      <c r="L21">
+        <v>-0.02397770756111911</v>
+      </c>
+      <c r="M21">
+        <v>0.0</v>
+      </c>
+      <c r="N21">
+        <v>6.129904748104142e-16</v>
+      </c>
+      <c r="O21">
+        <v>-0.03197806657576289</v>
+      </c>
+      <c r="P21">
+        <v>0.001315782595724113</v>
+      </c>
+      <c r="Q21">
+        <v>-0.012024424659352481</v>
+      </c>
+      <c r="R21">
+        <v>2.117510241676413e-15</v>
+      </c>
+      <c r="S21">
+        <v>0.0</v>
+      </c>
+      <c r="T21">
+        <v>0.05346317943625842</v>
+      </c>
+      <c r="U21">
+        <v>0.4504654531108905</v>
+      </c>
+      <c r="V21">
+        <v>0.0</v>
+      </c>
+      <c r="W21">
+        <v>0.2795692939551048</v>
+      </c>
+      <c r="X21">
+        <v>-0.14064715875612913</v>
+      </c>
+      <c r="Y21">
+        <v>-0.05687269770598974</v>
+      </c>
+      <c r="Z21">
+        <v>6.796731470489094e-17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
+  <dimension ref="A1:W22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:23">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" t="s">
+        <v>237</v>
+      </c>
+      <c r="J1" t="s">
+        <v>238</v>
+      </c>
+      <c r="K1" t="s">
+        <v>239</v>
+      </c>
+      <c r="L1" t="s">
+        <v>240</v>
+      </c>
+      <c r="M1" t="s">
+        <v>241</v>
+      </c>
+      <c r="N1" t="s">
+        <v>242</v>
+      </c>
+      <c r="O1" t="s">
+        <v>243</v>
+      </c>
+      <c r="P1" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>245</v>
+      </c>
+      <c r="R1" t="s">
+        <v>246</v>
+      </c>
+      <c r="S1" t="s">
+        <v>247</v>
+      </c>
+      <c r="T1" t="s">
+        <v>248</v>
+      </c>
+      <c r="V1" t="s">
+        <v>5</v>
+      </c>
+      <c r="W1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>4.5087075869680536e-17</v>
+      </c>
+      <c r="C2">
+        <v>-1.0</v>
+      </c>
+      <c r="D2">
+        <v>-1.0</v>
+      </c>
+      <c r="E2">
+        <v>0.5707903061494471</v>
+      </c>
+      <c r="F2">
+        <v>-4.748347915873213e-15</v>
+      </c>
+      <c r="G2">
+        <v>0.010611389448048958</v>
+      </c>
+      <c r="H2">
+        <v>0.0</v>
+      </c>
+      <c r="I2">
+        <v>0.01691563407698074</v>
+      </c>
+      <c r="J2">
+        <v>-0.08040185016545286</v>
+      </c>
+      <c r="K2">
+        <v>-1.0</v>
+      </c>
+      <c r="L2">
+        <v>-1.7088255604591185</v>
+      </c>
+      <c r="M2">
+        <v>-3.1764938580195055</v>
+      </c>
+      <c r="N2">
+        <v>-0.9052392657323787</v>
+      </c>
+      <c r="O2">
+        <v>0.014934334858653578</v>
+      </c>
+      <c r="P2">
+        <v>0.0</v>
+      </c>
+      <c r="Q2">
+        <v>-1.0168327755648958</v>
+      </c>
+      <c r="R2">
+        <v>-1.0</v>
+      </c>
+      <c r="S2">
+        <v>2.2111564327550956e-15</v>
+      </c>
+      <c r="T2">
+        <v>-0.01413114937975354</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>-1.2006389061474226e-16</v>
+      </c>
+      <c r="C3">
+        <v>-0.1644474583019147</v>
+      </c>
+      <c r="D3">
+        <v>-1.0</v>
+      </c>
+      <c r="E3">
+        <v>0.34439031998447733</v>
+      </c>
+      <c r="F3">
+        <v>-5.3791489454505824e-15</v>
+      </c>
+      <c r="G3">
+        <v>-0.03186432239033837</v>
+      </c>
+      <c r="H3">
+        <v>0.0</v>
+      </c>
+      <c r="I3">
+        <v>-0.16045476866356317</v>
+      </c>
+      <c r="J3">
+        <v>-0.09476073426764205</v>
+      </c>
+      <c r="K3">
+        <v>-0.9999999999999999</v>
+      </c>
+      <c r="L3">
+        <v>-0.30395262181504173</v>
+      </c>
+      <c r="M3">
+        <v>-2.3399162031955485</v>
+      </c>
+      <c r="N3">
+        <v>-0.9050688766126486</v>
+      </c>
+      <c r="O3">
+        <v>0.019489179085775514</v>
+      </c>
+      <c r="P3">
+        <v>-0.25661611979210086</v>
+      </c>
+      <c r="Q3">
+        <v>-1.0187192459363448</v>
+      </c>
+      <c r="R3">
+        <v>-1.0</v>
+      </c>
+      <c r="S3">
+        <v>2.6608334657322267e-15</v>
+      </c>
+      <c r="T3">
+        <v>-0.016915634076980258</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>-2.4823694109419566e-16</v>
+      </c>
+      <c r="C4">
+        <v>-0.1817890425383521</v>
+      </c>
+      <c r="D4">
+        <v>-1.0</v>
+      </c>
+      <c r="E4">
+        <v>0.2644610026980745</v>
+      </c>
+      <c r="F4">
+        <v>-5.818305649211937e-15</v>
+      </c>
+      <c r="G4">
+        <v>-0.1307158788307793</v>
+      </c>
+      <c r="H4">
+        <v>0.0</v>
+      </c>
+      <c r="I4">
+        <v>-0.3962673948995753</v>
+      </c>
+      <c r="J4">
+        <v>-0.09493112338737889</v>
+      </c>
+      <c r="K4">
+        <v>-1.0</v>
+      </c>
+      <c r="L4">
+        <v>-0.4569533138979312</v>
+      </c>
+      <c r="M4">
+        <v>-1.8379967551838206</v>
+      </c>
+      <c r="N4">
+        <v>-0.9086031713999636</v>
+      </c>
+      <c r="O4">
+        <v>0.022712803829237183</v>
+      </c>
+      <c r="P4">
+        <v>-0.15033445389395944</v>
+      </c>
+      <c r="Q4">
+        <v>-1.0212231064529043</v>
+      </c>
+      <c r="R4">
+        <v>-1.0</v>
+      </c>
+      <c r="S4">
+        <v>3.282663855239666e-15</v>
+      </c>
+      <c r="T4">
+        <v>-0.01741746642483185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>-3.4343469768482743e-16</v>
+      </c>
+      <c r="C5">
+        <v>-0.08260789907318522</v>
+      </c>
+      <c r="D5">
+        <v>-1.0000000000000002</v>
+      </c>
+      <c r="E5">
+        <v>0.20730999837501063</v>
+      </c>
+      <c r="F5">
+        <v>-6.090418604880365e-15</v>
+      </c>
+      <c r="G5">
+        <v>-0.2691110903402725</v>
+      </c>
+      <c r="H5">
+        <v>0.0</v>
+      </c>
+      <c r="I5">
+        <v>-0.5594916702932204</v>
+      </c>
+      <c r="J5">
+        <v>-0.09139682860006812</v>
+      </c>
+      <c r="K5">
+        <v>-1.0000000000000002</v>
+      </c>
+      <c r="L5">
+        <v>-0.4313484542300172</v>
+      </c>
+      <c r="M5">
+        <v>-1.505705246087438</v>
+      </c>
+      <c r="N5">
+        <v>-0.9135571947895866</v>
+      </c>
+      <c r="O5">
+        <v>0.02499288986750394</v>
+      </c>
+      <c r="P5">
+        <v>-0.11633708234053922</v>
+      </c>
+      <c r="Q5">
+        <v>-1.0229856195207134</v>
+      </c>
+      <c r="R5">
+        <v>-1.0</v>
+      </c>
+      <c r="S5">
+        <v>3.849757773399015e-15</v>
+      </c>
+      <c r="T5">
+        <v>-0.017374125841632445</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>-4.096415612004622e-16</v>
+      </c>
+      <c r="C6">
+        <v>-0.015638695049281635</v>
+      </c>
+      <c r="D6">
+        <v>-0.9999999999999998</v>
+      </c>
+      <c r="E6">
+        <v>0.16513266434240137</v>
+      </c>
+      <c r="F6">
+        <v>-6.2190208917890676e-15</v>
+      </c>
+      <c r="G6">
+        <v>-0.3930452374105372</v>
+      </c>
+      <c r="H6">
+        <v>0.0</v>
+      </c>
+      <c r="I6">
+        <v>-0.6649870094715363</v>
+      </c>
+      <c r="J6">
+        <v>-0.08644280521045197</v>
+      </c>
+      <c r="K6">
+        <v>-1.0</v>
+      </c>
+      <c r="L6">
+        <v>-0.413320503578175</v>
+      </c>
+      <c r="M6">
+        <v>-1.2504215444989601</v>
+      </c>
+      <c r="N6">
+        <v>-0.9192954503986281</v>
+      </c>
+      <c r="O6">
+        <v>0.026597847092238246</v>
+      </c>
+      <c r="P6">
+        <v>-0.08906487405434146</v>
+      </c>
+      <c r="Q6">
+        <v>-1.024222679618266</v>
+      </c>
+      <c r="R6">
+        <v>-1.0</v>
+      </c>
+      <c r="S6">
+        <v>4.367580875500832e-15</v>
+      </c>
+      <c r="T6">
+        <v>-0.01707253891919418</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>-4.50718655276338e-16</v>
+      </c>
+      <c r="C7">
+        <v>0.02876402916085786</v>
+      </c>
+      <c r="D7">
+        <v>-1.0</v>
+      </c>
+      <c r="E7">
+        <v>0.13295188727357443</v>
+      </c>
+      <c r="F7">
+        <v>-6.2261913106385175e-15</v>
+      </c>
+      <c r="G7">
+        <v>-0.4759843533789608</v>
+      </c>
+      <c r="H7">
+        <v>0.0</v>
+      </c>
+      <c r="I7">
+        <v>-0.7350899114635326</v>
+      </c>
+      <c r="J7">
+        <v>-0.08070454960141288</v>
+      </c>
+      <c r="K7">
+        <v>-0.9999999999999999</v>
+      </c>
+      <c r="L7">
+        <v>-0.399973267708569</v>
+      </c>
+      <c r="M7">
+        <v>-1.01978897436764</v>
+      </c>
+      <c r="N7">
+        <v>-0.9255267684593391</v>
+      </c>
+      <c r="O7">
+        <v>0.027718258601120767</v>
+      </c>
+      <c r="P7">
+        <v>-0.0662202549382754</v>
+      </c>
+      <c r="Q7">
+        <v>-1.0250883518532223</v>
+      </c>
+      <c r="R7">
+        <v>-1.0</v>
+      </c>
+      <c r="S7">
+        <v>4.839569422838582e-15</v>
+      </c>
+      <c r="T7">
+        <v>-0.016526036745515102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>-4.703276363848557e-16</v>
+      </c>
+      <c r="C8">
+        <v>1.091729446652716</v>
+      </c>
+      <c r="D8">
+        <v>0.03635145783199292</v>
+      </c>
+      <c r="E8">
+        <v>-0.02251291308733272</v>
+      </c>
+      <c r="F8">
+        <v>-6.132302703677181e-15</v>
+      </c>
+      <c r="G8">
+        <v>-0.509228971285405</v>
+      </c>
+      <c r="H8">
+        <v>0.0</v>
+      </c>
+      <c r="I8">
+        <v>0.25242038313511095</v>
+      </c>
+      <c r="J8">
+        <v>-0.07447323154070251</v>
+      </c>
+      <c r="K8">
+        <v>1.2734464728070378</v>
+      </c>
+      <c r="L8">
+        <v>0.0</v>
+      </c>
+      <c r="M8">
+        <v>-0.7834310456132124</v>
+      </c>
+      <c r="N8">
+        <v>1.3414080441414482</v>
+      </c>
+      <c r="O8">
+        <v>0.025088351853244956</v>
+      </c>
+      <c r="P8">
+        <v>-0.32142721498078364</v>
+      </c>
+      <c r="Q8">
+        <v>-0.7939186961608264</v>
+      </c>
+      <c r="R8">
+        <v>-0.7720607974650294</v>
+      </c>
+      <c r="S8">
+        <v>4.764069600892054e-15</v>
+      </c>
+      <c r="T8">
+        <v>-0.015715621463581707</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>-4.718786361864179e-16</v>
+      </c>
+      <c r="C9">
+        <v>0.0</v>
+      </c>
+      <c r="D9">
+        <v>0.12921754417741121</v>
+      </c>
+      <c r="E9">
+        <v>-0.09553656104211461</v>
+      </c>
+      <c r="F9">
+        <v>-5.95587947588401e-15</v>
+      </c>
+      <c r="G9">
+        <v>-0.1920202389789131</v>
+      </c>
+      <c r="H9">
+        <v>0.0</v>
+      </c>
+      <c r="I9">
+        <v>0.30989248609914577</v>
+      </c>
+      <c r="J9">
+        <v>-0.06796157133445065</v>
+      </c>
+      <c r="K9">
+        <v>1.2810045803204857</v>
+      </c>
+      <c r="L9">
+        <v>0.0</v>
+      </c>
+      <c r="M9">
+        <v>0.1338662711154739</v>
+      </c>
+      <c r="N9">
+        <v>1.342653275460827</v>
+      </c>
+      <c r="O9">
+        <v>0.021857898695817907</v>
+      </c>
+      <c r="P9">
+        <v>0.0</v>
+      </c>
+      <c r="Q9">
+        <v>-0.6085373332558515</v>
+      </c>
+      <c r="R9">
+        <v>-0.5897480989509019</v>
+      </c>
+      <c r="S9">
+        <v>4.64532180302989e-15</v>
+      </c>
+      <c r="T9">
+        <v>-0.014638909287259121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>-4.584979772835131e-16</v>
+      </c>
+      <c r="C10">
+        <v>0.0</v>
+      </c>
+      <c r="D10">
+        <v>0.09281887756465035</v>
+      </c>
+      <c r="E10">
+        <v>-0.12449326593762322</v>
+      </c>
+      <c r="F10">
+        <v>-5.713541401188098e-15</v>
+      </c>
+      <c r="G10">
+        <v>0.011473420303155235</v>
+      </c>
+      <c r="H10">
+        <v>0.0</v>
+      </c>
+      <c r="I10">
+        <v>0.24713842664744773</v>
+      </c>
+      <c r="J10">
+        <v>-0.06164869514037899</v>
+      </c>
+      <c r="K10">
+        <v>1.030942153310926</v>
+      </c>
+      <c r="L10">
+        <v>0.0</v>
+      </c>
+      <c r="M10">
+        <v>0.6708481598313336</v>
+      </c>
+      <c r="N10">
+        <v>1.086818092717859</v>
+      </c>
+      <c r="O10">
+        <v>0.018789234304968698</v>
+      </c>
+      <c r="P10">
+        <v>0.0</v>
+      </c>
+      <c r="Q10">
+        <v>-0.4807875592590392</v>
+      </c>
+      <c r="R10">
+        <v>-0.464701507136287</v>
+      </c>
+      <c r="S10">
+        <v>4.491998523377305e-15</v>
+      </c>
+      <c r="T10">
+        <v>-0.013449013874046038</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>-4.3301173041301315e-16</v>
+      </c>
+      <c r="C11">
+        <v>0.0</v>
+      </c>
+      <c r="D11">
+        <v>0.0564656832109975</v>
+      </c>
+      <c r="E11">
+        <v>-0.13203757619379708</v>
+      </c>
+      <c r="F11">
+        <v>-5.420013811365651e-15</v>
+      </c>
+      <c r="G11">
+        <v>0.10976997965989511</v>
+      </c>
+      <c r="H11">
+        <v>0.0</v>
+      </c>
+      <c r="I11">
+        <v>0.1908110132772078</v>
+      </c>
+      <c r="J11">
+        <v>-0.055875939406966856</v>
+      </c>
+      <c r="K11">
+        <v>0.8245778752789112</v>
+      </c>
+      <c r="L11">
+        <v>0.0</v>
+      </c>
+      <c r="M11">
+        <v>0.900240675818676</v>
+      </c>
+      <c r="N11">
+        <v>0.8753826214960259</v>
+      </c>
+      <c r="O11">
+        <v>0.01608605212276941</v>
+      </c>
+      <c r="P11">
+        <v>0.0</v>
+      </c>
+      <c r="Q11">
+        <v>-0.3926044788503507</v>
+      </c>
+      <c r="R11">
+        <v>-0.37880842932430453</v>
+      </c>
+      <c r="S11">
+        <v>4.3117861602909845e-15</v>
+      </c>
+      <c r="T11">
+        <v>-0.012273975098444636</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>-3.979416485401561e-16</v>
+      </c>
+      <c r="C12">
+        <v>0.0</v>
+      </c>
+      <c r="D12">
+        <v>0.03246778428510973</v>
+      </c>
+      <c r="E12">
+        <v>-0.1296263356099685</v>
+      </c>
+      <c r="F12">
+        <v>-5.0881872199663204e-15</v>
+      </c>
+      <c r="G12">
+        <v>0.1495199508970184</v>
+      </c>
+      <c r="H12">
+        <v>0.0</v>
+      </c>
+      <c r="I12">
+        <v>0.15149212646966237</v>
+      </c>
+      <c r="J12">
+        <v>-0.05080474621714511</v>
+      </c>
+      <c r="K12">
+        <v>0.6786817445489453</v>
+      </c>
+      <c r="L12">
+        <v>0.0</v>
+      </c>
+      <c r="M12">
+        <v>0.9636687953744474</v>
+      </c>
+      <c r="N12">
+        <v>0.7251580193976521</v>
+      </c>
+      <c r="O12">
+        <v>0.013796049526061562</v>
+      </c>
+      <c r="P12">
+        <v>0.0</v>
+      </c>
+      <c r="Q12">
+        <v>-0.3298711918506749</v>
+      </c>
+      <c r="R12">
+        <v>-0.31795816460031373</v>
+      </c>
+      <c r="S12">
+        <v>4.1114168903484515e-15</v>
+      </c>
+      <c r="T12">
+        <v>-0.01118589910661117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>-3.5551049288211273e-16</v>
+      </c>
+      <c r="C13">
+        <v>0.0</v>
+      </c>
+      <c r="D13">
+        <v>0.01729056859543368</v>
+      </c>
+      <c r="E13">
+        <v>-0.12278283032448467</v>
+      </c>
+      <c r="F13">
+        <v>-4.72921222665598e-15</v>
+      </c>
+      <c r="G13">
+        <v>0.16049780056471308</v>
+      </c>
+      <c r="H13">
+        <v>0.0</v>
+      </c>
+      <c r="I13">
+        <v>0.12444684763273535</v>
+      </c>
+      <c r="J13">
+        <v>-0.04647627484873401</v>
+      </c>
+      <c r="K13">
+        <v>0.5755513070359216</v>
+      </c>
+      <c r="L13">
+        <v>0.0</v>
+      </c>
+      <c r="M13">
+        <v>0.947477959475338</v>
+      </c>
+      <c r="N13">
+        <v>0.6184168634141056</v>
+      </c>
+      <c r="O13">
+        <v>0.011913027250374837</v>
+      </c>
+      <c r="P13">
+        <v>0.0</v>
+      </c>
+      <c r="Q13">
+        <v>-0.28392811707520316</v>
+      </c>
+      <c r="R13">
+        <v>-0.27351925860025716</v>
+      </c>
+      <c r="S13">
+        <v>3.896718652643837e-15</v>
+      </c>
+      <c r="T13">
+        <v>-0.01021669738224655</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>-3.076542318857994e-16</v>
+      </c>
+      <c r="C14">
+        <v>0.0</v>
+      </c>
+      <c r="D14">
+        <v>0.007412129983506349</v>
+      </c>
+      <c r="E14">
+        <v>-0.11413462504137417</v>
+      </c>
+      <c r="F14">
+        <v>-4.352618103282998e-15</v>
+      </c>
+      <c r="G14">
+        <v>0.15807983378839663</v>
+      </c>
+      <c r="H14">
+        <v>0.0</v>
+      </c>
+      <c r="I14">
+        <v>0.10527842914313104</v>
+      </c>
+      <c r="J14">
+        <v>-0.04286555637820762</v>
+      </c>
+      <c r="K14">
+        <v>0.5005134811262363</v>
+      </c>
+      <c r="L14">
+        <v>0.0</v>
+      </c>
+      <c r="M14">
+        <v>0.8957636284726316</v>
+      </c>
+      <c r="N14">
+        <v>0.5404283904458609</v>
+      </c>
+      <c r="O14">
+        <v>0.010408858474957995</v>
+      </c>
+      <c r="P14">
+        <v>0.0</v>
+      </c>
+      <c r="Q14">
+        <v>-0.24952897635556878</v>
+      </c>
+      <c r="R14">
+        <v>-0.24028292037616167</v>
+      </c>
+      <c r="S14">
+        <v>3.672677208093998e-15</v>
+      </c>
+      <c r="T14">
+        <v>-0.009375346955349115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>-2.560390285301014e-16</v>
+      </c>
+      <c r="C15">
+        <v>0.0</v>
+      </c>
+      <c r="D15">
+        <v>0.0007360314313030469</v>
+      </c>
+      <c r="E15">
+        <v>-0.10493301190703386</v>
+      </c>
+      <c r="F15">
+        <v>-3.966445739574202e-15</v>
+      </c>
+      <c r="G15">
+        <v>0.1497205073739659</v>
+      </c>
+      <c r="H15">
+        <v>0.0</v>
+      </c>
+      <c r="I15">
+        <v>0.09123351500585693</v>
+      </c>
+      <c r="J15">
+        <v>-0.03991490931964535</v>
+      </c>
+      <c r="K15">
+        <v>0.44424580942170055</v>
+      </c>
+      <c r="L15">
+        <v>0.0</v>
+      </c>
+      <c r="M15">
+        <v>0.8298521301499666</v>
+      </c>
+      <c r="N15">
+        <v>0.4817982033686391</v>
+      </c>
+      <c r="O15">
+        <v>0.009246055979417576</v>
+      </c>
+      <c r="P15">
+        <v>0.0</v>
+      </c>
+      <c r="Q15">
+        <v>-0.22334003993228627</v>
+      </c>
+      <c r="R15">
+        <v>-0.21495635644193878</v>
+      </c>
+      <c r="S15">
+        <v>3.4435054511492708e-15</v>
+      </c>
+      <c r="T15">
+        <v>-0.008658871647518815</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>-2.0208132342173716e-16</v>
+      </c>
+      <c r="C16">
+        <v>0.0</v>
+      </c>
+      <c r="D16">
+        <v>-0.003889122939751438</v>
+      </c>
+      <c r="E16">
+        <v>-0.09577806619976337</v>
+      </c>
+      <c r="F16">
+        <v>-3.577387609018251e-15</v>
+      </c>
+      <c r="G16">
+        <v>0.1389619919126751</v>
+      </c>
+      <c r="H16">
+        <v>0.0</v>
+      </c>
+      <c r="I16">
+        <v>0.08065991723176327</v>
+      </c>
+      <c r="J16">
+        <v>-0.0375523939469565</v>
+      </c>
+      <c r="K16">
+        <v>0.4009221257836246</v>
+      </c>
+      <c r="L16">
+        <v>0.0</v>
+      </c>
+      <c r="M16">
+        <v>0.7598752475964856</v>
+      </c>
+      <c r="N16">
+        <v>0.4366238442871805</v>
+      </c>
+      <c r="O16">
+        <v>0.008383683490356524</v>
+      </c>
+      <c r="P16">
+        <v>0.0</v>
+      </c>
+      <c r="Q16">
+        <v>-0.2031125783989823</v>
+      </c>
+      <c r="R16">
+        <v>-0.19533210087644076</v>
+      </c>
+      <c r="S16">
+        <v>3.2127161953212456e-15</v>
+      </c>
+      <c r="T16">
+        <v>-0.008058405359832108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>-1.4696966627184697e-16</v>
+      </c>
+      <c r="C17">
+        <v>0.0</v>
+      </c>
+      <c r="D17">
+        <v>-0.007109862531682359</v>
+      </c>
+      <c r="E17">
+        <v>-0.08695920253178047</v>
+      </c>
+      <c r="F17">
+        <v>-3.1909291091707866e-15</v>
+      </c>
+      <c r="G17">
+        <v>0.1274809751644383</v>
+      </c>
+      <c r="H17">
+        <v>0.0</v>
+      </c>
+      <c r="I17">
+        <v>0.07252762679352115</v>
+      </c>
+      <c r="J17">
+        <v>-0.03570171850357122</v>
+      </c>
+      <c r="K17">
+        <v>0.36674879385082393</v>
+      </c>
+      <c r="L17">
+        <v>0.0</v>
+      </c>
+      <c r="M17">
+        <v>0.6906149433032079</v>
+      </c>
+      <c r="N17">
+        <v>0.40103636978371526</v>
+      </c>
+      <c r="O17">
+        <v>0.0077804775225492956</v>
+      </c>
+      <c r="P17">
+        <v>0.0</v>
+      </c>
+      <c r="Q17">
+        <v>-0.18725096121170928</v>
+      </c>
+      <c r="R17">
+        <v>-0.17985435310070974</v>
+      </c>
+      <c r="S17">
+        <v>2.9831955381432905e-15</v>
+      </c>
+      <c r="T17">
+        <v>-0.007562411629084261</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>-9.168724583972224e-17</v>
+      </c>
+      <c r="C18">
+        <v>0.0</v>
+      </c>
+      <c r="D18">
+        <v>-0.00931441898106726</v>
+      </c>
+      <c r="E18">
+        <v>-0.07861477151704166</v>
+      </c>
+      <c r="F18">
+        <v>-2.811487052786614e-15</v>
+      </c>
+      <c r="G18">
+        <v>0.11607232508361541</v>
+      </c>
+      <c r="H18">
+        <v>0.0</v>
+      </c>
+      <c r="I18">
+        <v>0.0661556808140292</v>
+      </c>
+      <c r="J18">
+        <v>-0.03428757593290447</v>
+      </c>
+      <c r="K18">
+        <v>0.33913213797309316</v>
+      </c>
+      <c r="L18">
+        <v>0.0</v>
+      </c>
+      <c r="M18">
+        <v>0.6243059012374765</v>
+      </c>
+      <c r="N18">
+        <v>0.3723706803376171</v>
+      </c>
+      <c r="O18">
+        <v>0.007396608111006103</v>
+      </c>
+      <c r="P18">
+        <v>0.0</v>
+      </c>
+      <c r="Q18">
+        <v>-0.17458324950462203</v>
+      </c>
+      <c r="R18">
+        <v>-0.16738855315147141</v>
+      </c>
+      <c r="S18">
+        <v>2.7572746488062356e-15</v>
+      </c>
+      <c r="T18">
+        <v>-0.007158400918384182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>-3.7034320309053016e-17</v>
+      </c>
+      <c r="C19">
+        <v>0.0</v>
+      </c>
+      <c r="D19">
+        <v>-0.010756344511751635</v>
+      </c>
+      <c r="E19">
+        <v>-0.07080733196772027</v>
+      </c>
+      <c r="F19">
+        <v>-2.442542261379695e-15</v>
+      </c>
+      <c r="G19">
+        <v>0.10511209411254013</v>
+      </c>
+      <c r="H19">
+        <v>0.0</v>
+      </c>
+      <c r="I19">
+        <v>0.06106905665507224</v>
+      </c>
+      <c r="J19">
+        <v>-0.03323854236453495</v>
+      </c>
+      <c r="K19">
+        <v>0.3162298539971159</v>
+      </c>
+      <c r="L19">
+        <v>0.0</v>
+      </c>
+      <c r="M19">
+        <v>0.5619574797877019</v>
+      </c>
+      <c r="N19">
+        <v>0.3487184850955369</v>
+      </c>
+      <c r="O19">
+        <v>0.007194696353156129</v>
+      </c>
+      <c r="P19">
+        <v>0.0</v>
+      </c>
+      <c r="Q19">
+        <v>-0.16423224830811753</v>
+      </c>
+      <c r="R19">
+        <v>-0.1570918596230652</v>
+      </c>
+      <c r="S19">
+        <v>2.5367984281668596e-15</v>
+      </c>
+      <c r="T19">
+        <v>-0.00683386790670013</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>1.6350040134988204e-17</v>
+      </c>
+      <c r="C20">
+        <v>0.0</v>
+      </c>
+      <c r="D20">
+        <v>-0.011614831036960739</v>
+      </c>
+      <c r="E20">
+        <v>-0.06355970087713314</v>
+      </c>
+      <c r="F20">
+        <v>-2.0867641687792137e-15</v>
+      </c>
+      <c r="G20">
+        <v>0.09477441002674511</v>
+      </c>
+      <c r="H20">
+        <v>0.0</v>
+      </c>
+      <c r="I20">
+        <v>0.05692335170514526</v>
+      </c>
+      <c r="J20">
+        <v>-0.032488631098430074</v>
+      </c>
+      <c r="K20">
+        <v>0.2967029198221135</v>
+      </c>
+      <c r="L20">
+        <v>0.0</v>
+      </c>
+      <c r="M20">
+        <v>0.5039768198912442</v>
+      </c>
+      <c r="N20">
+        <v>0.3286809863978689</v>
+      </c>
+      <c r="O20">
+        <v>0.00714038868505687</v>
+      </c>
+      <c r="P20">
+        <v>0.0</v>
+      </c>
+      <c r="Q20">
+        <v>-0.15553704193562543</v>
+      </c>
+      <c r="R20">
+        <v>-0.14833439404904106</v>
+      </c>
+      <c r="S20">
+        <v>2.3231899821690162e-15</v>
+      </c>
+      <c r="T20">
+        <v>-0.006576814916789152</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>6.796731470489094e-17</v>
+      </c>
+      <c r="C21">
+        <v>0.0</v>
+      </c>
+      <c r="D21">
+        <v>-0.012024424659352481</v>
+      </c>
+      <c r="E21">
+        <v>-0.05687269770598974</v>
+      </c>
+      <c r="F21">
+        <v>-1.7461261073911644e-15</v>
+      </c>
+      <c r="G21">
+        <v>0.08513351486885028</v>
+      </c>
+      <c r="H21">
+        <v>0.0</v>
+      </c>
+      <c r="I21">
+        <v>0.05346317943625842</v>
+      </c>
+      <c r="J21">
+        <v>-0.03197806657576289</v>
+      </c>
+      <c r="K21">
+        <v>0.2795692939551048</v>
+      </c>
+      <c r="L21">
+        <v>0.0</v>
+      </c>
+      <c r="M21">
+        <v>0.4504654531108905</v>
+      </c>
+      <c r="N21">
+        <v>0.3112228747784288</v>
+      </c>
+      <c r="O21">
+        <v>0.007202647886588068</v>
+      </c>
+      <c r="P21">
+        <v>0.0</v>
+      </c>
+      <c r="Q21">
+        <v>-0.1480010128972768</v>
+      </c>
+      <c r="R21">
+        <v>-0.14064715875612913</v>
+      </c>
+      <c r="S21">
+        <v>2.117510241676413e-15</v>
+      </c>
+      <c r="T21">
+        <v>-0.006376045364124454</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>1.1744027465637388e-16</v>
+      </c>
+      <c r="C22">
+        <v>0.0</v>
+      </c>
+      <c r="D22">
+        <v>-0.012090214066508773</v>
+      </c>
+      <c r="E22">
+        <v>-0.05073426751940319</v>
+      </c>
+      <c r="F22">
+        <v>-1.4220105516204918e-15</v>
+      </c>
+      <c r="G22">
+        <v>0.07621238223928459</v>
+      </c>
+      <c r="H22">
+        <v>0.0</v>
+      </c>
+      <c r="I22">
+        <v>0.05049741171846571</v>
+      </c>
+      <c r="J22">
+        <v>-0.03165358082332999</v>
+      </c>
+      <c r="K22">
+        <v>0.26411047536161875</v>
+      </c>
+      <c r="L22">
+        <v>0.0</v>
+      </c>
+      <c r="M22">
+        <v>0.40136348100215885</v>
+      </c>
+      <c r="N22">
+        <v>0.2955788799398664</v>
+      </c>
+      <c r="O22">
+        <v>0.0073538541411506475</v>
+      </c>
+      <c r="P22">
+        <v>0.0</v>
+      </c>
+      <c r="Q22">
+        <v>-0.14125474690977477</v>
+      </c>
+      <c r="R22">
+        <v>-0.13368497150297537</v>
+      </c>
+      <c r="S22">
+        <v>1.9205123690881475e-15</v>
+      </c>
+      <c r="T22">
+        <v>-0.006221321657146216</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
   <dimension ref="A1:H21"/>
@@ -2579,16 +6072,16 @@
         <v>15</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>275</v>
       </c>
       <c r="E1" t="s">
         <v>17</v>
       </c>
       <c r="F1" t="s">
-        <v>19</v>
+        <v>276</v>
       </c>
       <c r="G1" t="s">
         <v>122</v>
@@ -2600,168 +6093,168 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>141</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="C2">
         <v>0.0</v>
       </c>
       <c r="D2">
-        <v>0.0</v>
+        <v>-0.6435762806683293</v>
       </c>
       <c r="E2">
-        <v>0.0</v>
+        <v>-1.2192030578654236</v>
       </c>
       <c r="F2">
-        <v>0.0</v>
+        <v>-0.1080622464366398</v>
       </c>
       <c r="G2">
-        <v>0.0</v>
+        <v>-0.36271067620171826</v>
       </c>
       <c r="H2">
-        <v>0.0</v>
+        <v>-0.5614432916327226</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="C3">
         <v>0.0</v>
       </c>
       <c r="D3">
-        <v>0.0</v>
+        <v>-0.6279220081723806</v>
       </c>
       <c r="E3">
-        <v>0.0</v>
+        <v>-0.6378687459157811</v>
       </c>
       <c r="F3">
-        <v>0.0</v>
+        <v>0.05044507809445791</v>
       </c>
       <c r="G3">
-        <v>0.0</v>
+        <v>-0.269237922296917</v>
       </c>
       <c r="H3">
-        <v>0.0</v>
+        <v>-0.7502686492477091</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="C4">
         <v>0.0</v>
       </c>
       <c r="D4">
-        <v>0.0</v>
+        <v>-0.6178660313088483</v>
       </c>
       <c r="E4">
-        <v>0.0</v>
+        <v>-0.634456502029503</v>
       </c>
       <c r="F4">
-        <v>0.0</v>
+        <v>-0.0002629263061184572</v>
       </c>
       <c r="G4">
-        <v>0.0</v>
+        <v>-0.25061386228086724</v>
       </c>
       <c r="H4">
-        <v>0.0</v>
+        <v>-0.7534061133303237</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="C5">
         <v>0.0</v>
       </c>
       <c r="D5">
-        <v>0.0</v>
+        <v>-0.6096302598513561</v>
       </c>
       <c r="E5">
-        <v>0.0</v>
+        <v>-0.6301676667741174</v>
       </c>
       <c r="F5">
-        <v>0.0</v>
+        <v>-0.00018220654470116424</v>
       </c>
       <c r="G5">
-        <v>0.0</v>
+        <v>-0.24720546250875922</v>
       </c>
       <c r="H5">
-        <v>0.0</v>
+        <v>-0.7536898503703882</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="C6">
         <v>0.0</v>
       </c>
       <c r="D6">
-        <v>0.0</v>
+        <v>-0.602299277061698</v>
       </c>
       <c r="E6">
-        <v>0.0</v>
+        <v>-0.6269800578164451</v>
       </c>
       <c r="F6">
-        <v>0.0</v>
+        <v>-0.00027601075156010547</v>
       </c>
       <c r="G6">
-        <v>0.0</v>
+        <v>-0.2472365790685624</v>
       </c>
       <c r="H6">
-        <v>0.0</v>
+        <v>-0.7529723962950038</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="C7">
         <v>0.0</v>
       </c>
       <c r="D7">
-        <v>0.0</v>
+        <v>-0.5955632684612778</v>
       </c>
       <c r="E7">
-        <v>0.0</v>
+        <v>-0.6249128390389327</v>
       </c>
       <c r="F7">
-        <v>0.0</v>
+        <v>-0.00037248957610660344</v>
       </c>
       <c r="G7">
-        <v>0.0</v>
+        <v>-0.248277864091797</v>
       </c>
       <c r="H7">
-        <v>0.0</v>
+        <v>-0.7517461913854471</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>0.0</v>
@@ -2770,24 +6263,24 @@
         <v>0.0</v>
       </c>
       <c r="D8">
-        <v>0.0</v>
+        <v>0.05430946582074303</v>
       </c>
       <c r="E8">
-        <v>0.0</v>
+        <v>0.5955077290089377</v>
       </c>
       <c r="F8">
-        <v>0.0</v>
+        <v>0.10761627645382683</v>
       </c>
       <c r="G8">
-        <v>0.0</v>
+        <v>0.11295997038794492</v>
       </c>
       <c r="H8">
-        <v>0.0</v>
+        <v>-0.18876390832992718</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9">
         <v>0.0</v>
@@ -2796,24 +6289,24 @@
         <v>0.0</v>
       </c>
       <c r="D9">
-        <v>0.0</v>
+        <v>0.04461029027889063</v>
       </c>
       <c r="E9">
-        <v>0.0</v>
+        <v>0.014798565807075535</v>
       </c>
       <c r="F9">
-        <v>0.0</v>
+        <v>-0.05094247202841195</v>
       </c>
       <c r="G9">
-        <v>0.0</v>
+        <v>0.01777562068919533</v>
       </c>
       <c r="H9">
-        <v>0.0</v>
+        <v>0.001799603566086494</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10">
         <v>0.0</v>
@@ -2822,24 +6315,24 @@
         <v>0.0</v>
       </c>
       <c r="D10">
-        <v>0.0</v>
+        <v>0.04023509098759547</v>
       </c>
       <c r="E10">
-        <v>0.0</v>
+        <v>0.011620584958082124</v>
       </c>
       <c r="F10">
-        <v>0.0</v>
+        <v>-0.00026855910909260466</v>
       </c>
       <c r="G10">
-        <v>0.0</v>
+        <v>-0.002701021584600503</v>
       </c>
       <c r="H10">
-        <v>0.0</v>
+        <v>0.006795764727261841</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11">
         <v>0.0</v>
@@ -2848,24 +6341,24 @@
         <v>0.0</v>
       </c>
       <c r="D11">
-        <v>0.0</v>
+        <v>0.0374521315957541</v>
       </c>
       <c r="E11">
-        <v>0.0</v>
+        <v>0.0073251223202478195</v>
       </c>
       <c r="F11">
-        <v>0.0</v>
+        <v>-0.0003704221983866593</v>
       </c>
       <c r="G11">
-        <v>0.0</v>
+        <v>-0.008039085965597648</v>
       </c>
       <c r="H11">
-        <v>0.0</v>
+        <v>0.009001503908673051</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12">
         <v>0.0</v>
@@ -2874,50 +6367,50 @@
         <v>0.0</v>
       </c>
       <c r="D12">
-        <v>0.0</v>
+        <v>0.03537776930919301</v>
       </c>
       <c r="E12">
-        <v>0.0</v>
+        <v>0.00399912698299723</v>
       </c>
       <c r="F12">
-        <v>0.0</v>
+        <v>-0.0002883021280007282</v>
       </c>
       <c r="G12">
-        <v>0.0</v>
+        <v>-0.009969189323753357</v>
       </c>
       <c r="H12">
-        <v>0.0</v>
+        <v>0.010227436034322045</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13">
-        <v>0.0</v>
+        <v>-2.168404344971009e-19</v>
       </c>
       <c r="C13">
         <v>0.0</v>
       </c>
       <c r="D13">
-        <v>0.0</v>
+        <v>0.033723609910747104</v>
       </c>
       <c r="E13">
-        <v>0.0</v>
+        <v>0.0017396134227807057</v>
       </c>
       <c r="F13">
-        <v>0.0</v>
+        <v>-0.0001967240511480421</v>
       </c>
       <c r="G13">
-        <v>0.0</v>
+        <v>-0.010887739849668903</v>
       </c>
       <c r="H13">
-        <v>0.0</v>
+        <v>0.010935576880075447</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>0.0</v>
@@ -2926,24 +6419,24 @@
         <v>0.0</v>
       </c>
       <c r="D14">
-        <v>0.0</v>
+        <v>0.03234838012833448</v>
       </c>
       <c r="E14">
-        <v>0.0</v>
+        <v>0.00033011483787131996</v>
       </c>
       <c r="F14">
-        <v>0.0</v>
+        <v>-0.00012338692650097345</v>
       </c>
       <c r="G14">
-        <v>0.0</v>
+        <v>-0.011349724808897944</v>
       </c>
       <c r="H14">
-        <v>0.0</v>
+        <v>0.011300181029315418</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15">
         <v>0.0</v>
@@ -2952,24 +6445,24 @@
         <v>0.0</v>
       </c>
       <c r="D15">
-        <v>0.0</v>
+        <v>0.031163015963138807</v>
       </c>
       <c r="E15">
-        <v>0.0</v>
+        <v>-0.00045021286855274765</v>
       </c>
       <c r="F15">
-        <v>0.0</v>
+        <v>-6.887059121252602e-5</v>
       </c>
       <c r="G15">
-        <v>0.0</v>
+        <v>-0.01153134500686401</v>
       </c>
       <c r="H15">
-        <v>0.0</v>
+        <v>0.011419763887938784</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16">
         <v>0.0</v>
@@ -2978,76 +6471,76 @@
         <v>0.0</v>
       </c>
       <c r="D16">
-        <v>0.0</v>
+        <v>0.030106257729127735</v>
       </c>
       <c r="E16">
-        <v>0.0</v>
+        <v>-0.0007795040050729072</v>
       </c>
       <c r="F16">
-        <v>0.0</v>
+        <v>-2.9585268713728415e-5</v>
       </c>
       <c r="G16">
-        <v>0.0</v>
+        <v>-0.01151906677284669</v>
       </c>
       <c r="H16">
-        <v>0.0</v>
+        <v>0.011362816898953416</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17">
-        <v>0.0</v>
+        <v>3.3881317890172014e-21</v>
       </c>
       <c r="C17">
         <v>0.0</v>
       </c>
       <c r="D17">
-        <v>0.0</v>
+        <v>0.029135370774065753</v>
       </c>
       <c r="E17">
-        <v>0.0</v>
+        <v>-0.0007940943470241392</v>
       </c>
       <c r="F17">
-        <v>0.0</v>
+        <v>-1.984094979805785e-6</v>
       </c>
       <c r="G17">
-        <v>0.0</v>
+        <v>-0.011369476509090388</v>
       </c>
       <c r="H17">
-        <v>0.0</v>
+        <v>0.011180182428426402</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18">
-        <v>0.0</v>
+        <v>2.710505431213761e-20</v>
       </c>
       <c r="C18">
         <v>0.0</v>
       </c>
       <c r="D18">
-        <v>0.0</v>
+        <v>0.02822089803791056</v>
       </c>
       <c r="E18">
-        <v>0.0</v>
+        <v>-0.000596486093397393</v>
       </c>
       <c r="F18">
-        <v>0.0</v>
+        <v>1.6810879433808528e-5</v>
       </c>
       <c r="G18">
-        <v>0.0</v>
+        <v>-0.011123756751115134</v>
       </c>
       <c r="H18">
-        <v>0.0</v>
+        <v>0.010910162658695524</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19">
         <v>0.0</v>
@@ -3056,24 +6549,24 @@
         <v>0.0</v>
       </c>
       <c r="D19">
-        <v>0.0</v>
+        <v>0.02734303434734894</v>
       </c>
       <c r="E19">
-        <v>0.0</v>
+        <v>-0.0002629184194522731</v>
       </c>
       <c r="F19">
-        <v>0.0</v>
+        <v>2.9036587207160657e-5</v>
       </c>
       <c r="G19">
-        <v>0.0</v>
+        <v>-0.010812701421975254</v>
       </c>
       <c r="H19">
-        <v>0.0</v>
+        <v>0.010581607058097325</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20">
         <v>0.0</v>
@@ -3082,24 +6575,24 @@
         <v>0.0</v>
       </c>
       <c r="D20">
-        <v>0.0</v>
+        <v>0.026488958211201827</v>
       </c>
       <c r="E20">
-        <v>0.0</v>
+        <v>0.00015050757965148163</v>
       </c>
       <c r="F20">
-        <v>0.0</v>
+        <v>3.641036360737823e-5</v>
       </c>
       <c r="G20">
-        <v>0.0</v>
+        <v>-0.010459395758219208</v>
       </c>
       <c r="H20">
-        <v>0.0</v>
+        <v>0.010216134446380577</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21">
         <v>0.0</v>
@@ -3108,19 +6601,19 @@
         <v>0.0</v>
       </c>
       <c r="D21">
-        <v>0.0</v>
+        <v>0.025650841016062707</v>
       </c>
       <c r="E21">
-        <v>0.0</v>
+        <v>0.000603046136270709</v>
       </c>
       <c r="F21">
-        <v>0.0</v>
+        <v>4.024348083985214e-5</v>
       </c>
       <c r="G21">
-        <v>0.0</v>
+        <v>-0.010081057297520044</v>
       </c>
       <c r="H21">
-        <v>0.0</v>
+        <v>0.009829820315255597</v>
       </c>
     </row>
   </sheetData>
@@ -3130,7 +6623,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -3162,7 +6655,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>142</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -3683,6 +7176,32 @@
       </c>
       <c r="H21">
         <v>-0.0370002532243192</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>-0.03342124287574384</v>
+      </c>
+      <c r="C22">
+        <v>-2.14116508552435e-12</v>
+      </c>
+      <c r="D22">
+        <v>0.0</v>
+      </c>
+      <c r="E22">
+        <v>4.801280922720369e-16</v>
+      </c>
+      <c r="F22">
+        <v>-0.05073426751940319</v>
+      </c>
+      <c r="G22">
+        <v>0.0018384635352876619</v>
+      </c>
+      <c r="H22">
+        <v>-0.03531368672744369</v>
       </c>
     </row>
   </sheetData>
@@ -3692,10 +7211,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3720,19 +7239,34 @@
       <c r="H1" t="s">
         <v>4</v>
       </c>
+      <c r="I1" t="s">
+        <v>160</v>
+      </c>
       <c r="J1" t="s">
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+        <v>273</v>
+      </c>
+      <c r="L1" t="s">
+        <v>163</v>
+      </c>
+      <c r="M1" t="s">
+        <v>164</v>
+      </c>
+      <c r="O1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.24568080506695344</v>
+        <v>0.010611389448048958</v>
       </c>
       <c r="C2">
         <v>0.0</v>
@@ -3741,24 +7275,39 @@
         <v>-1.0</v>
       </c>
       <c r="E2">
-        <v>0.08493046150715088</v>
+        <v>0.01691563407698074</v>
       </c>
       <c r="F2">
-        <v>3.986335937361826e-16</v>
+        <v>4.5087075869680536e-17</v>
       </c>
       <c r="G2">
-        <v>-0.22971839175496833</v>
+        <v>-0.1644474583019147</v>
       </c>
       <c r="H2">
-        <v>-0.009243260936556393</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>-0.01413114937975354</v>
+      </c>
+      <c r="I2">
+        <v>-1.0</v>
+      </c>
+      <c r="J2">
+        <v>0.005732046908926213</v>
+      </c>
+      <c r="K2">
+        <v>0.0</v>
+      </c>
+      <c r="L2">
+        <v>-1.0058184173837017</v>
+      </c>
+      <c r="M2">
+        <v>0.5725178560221338</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.13836927980089797</v>
+        <v>-0.03186432239033837</v>
       </c>
       <c r="C3">
         <v>0.0</v>
@@ -3767,24 +7316,39 @@
         <v>-1.0</v>
       </c>
       <c r="E3">
-        <v>-0.1055347112364461</v>
+        <v>-0.16045476866356317</v>
       </c>
       <c r="F3">
-        <v>2.678273004630199e-16</v>
+        <v>-1.2006389061474226e-16</v>
       </c>
       <c r="G3">
-        <v>-0.23231447954005477</v>
+        <v>-0.1817890425383521</v>
       </c>
       <c r="H3">
-        <v>-0.011174059579196038</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>-0.016915634076980258</v>
+      </c>
+      <c r="I3">
+        <v>-1.0</v>
+      </c>
+      <c r="J3">
+        <v>0.005818417383714209</v>
+      </c>
+      <c r="K3">
+        <v>-0.04160056863078614</v>
+      </c>
+      <c r="L3">
+        <v>-1.0043896746215206</v>
+      </c>
+      <c r="M3">
+        <v>0.23546751281473968</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>-0.00479298431057662</v>
+        <v>-0.1307158788307793</v>
       </c>
       <c r="C4">
         <v>0.0</v>
@@ -3793,76 +7357,121 @@
         <v>-1.0</v>
       </c>
       <c r="E4">
-        <v>-0.3584793514459424</v>
+        <v>-0.3962673948995753</v>
       </c>
       <c r="F4">
-        <v>1.625912853080499e-16</v>
+        <v>-2.4823694109419566e-16</v>
       </c>
       <c r="G4">
-        <v>-0.12369593004209355</v>
+        <v>-0.08260789907318522</v>
       </c>
       <c r="H4">
-        <v>-0.011700337986996764</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>-0.01741746642483185</v>
+      </c>
+      <c r="I4">
+        <v>-1.0</v>
+      </c>
+      <c r="J4">
+        <v>0.004389674621532381</v>
+      </c>
+      <c r="K4">
+        <v>0.0</v>
+      </c>
+      <c r="L4">
+        <v>-1.0026379432304096</v>
+      </c>
+      <c r="M4">
+        <v>0.03895381979445463</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>-0.17790435476722674</v>
+        <v>-0.2691110903402725</v>
       </c>
       <c r="C5">
         <v>0.0</v>
       </c>
       <c r="D5">
-        <v>-1.0</v>
+        <v>-1.0000000000000002</v>
       </c>
       <c r="E5">
-        <v>-0.5333770711596347</v>
+        <v>-0.5594916702932204</v>
       </c>
       <c r="F5">
-        <v>8.044215724776388e-17</v>
+        <v>-3.4343469768482743e-16</v>
       </c>
       <c r="G5">
-        <v>-0.05010323746278902</v>
+        <v>-0.015638695049281635</v>
       </c>
       <c r="H5">
-        <v>-0.011914477625187872</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>-0.017374125841632445</v>
+      </c>
+      <c r="I5">
+        <v>-1.0000000000000002</v>
+      </c>
+      <c r="J5">
+        <v>0.0026379432304188648</v>
+      </c>
+      <c r="K5">
+        <v>0.0</v>
+      </c>
+      <c r="L5">
+        <v>-1.0010155023190588</v>
+      </c>
+      <c r="M5">
+        <v>-0.07513551624625048</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>-0.3298082459014194</v>
+        <v>-0.3930452374105372</v>
       </c>
       <c r="C6">
         <v>0.0</v>
       </c>
       <c r="D6">
+        <v>-0.9999999999999998</v>
+      </c>
+      <c r="E6">
+        <v>-0.6649870094715363</v>
+      </c>
+      <c r="F6">
+        <v>-4.096415612004622e-16</v>
+      </c>
+      <c r="G6">
+        <v>0.02876402916085786</v>
+      </c>
+      <c r="H6">
+        <v>-0.01707253891919418</v>
+      </c>
+      <c r="I6">
         <v>-1.0</v>
       </c>
-      <c r="E6">
-        <v>-0.6462301338888465</v>
-      </c>
-      <c r="F6">
-        <v>1.8837355658372474e-17</v>
-      </c>
-      <c r="G6">
-        <v>-0.000500509071672816</v>
-      </c>
-      <c r="H6">
-        <v>-0.011956037676767046</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="J6">
+        <v>0.0010155023190660112</v>
+      </c>
+      <c r="K6">
+        <v>0.0</v>
+      </c>
+      <c r="L6">
+        <v>-0.9997267456449523</v>
+      </c>
+      <c r="M6">
+        <v>-0.13878901757718057</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>-0.4358752811830413</v>
+        <v>-0.4759843533789608</v>
       </c>
       <c r="C7">
         <v>0.0</v>
@@ -3871,380 +7480,1949 @@
         <v>-1.0</v>
       </c>
       <c r="E7">
-        <v>-0.7210439740970532</v>
+        <v>-0.7350899114635326</v>
       </c>
       <c r="F7">
-        <v>-2.474057278354479e-17</v>
+        <v>-4.50718655276338e-16</v>
       </c>
       <c r="G7">
-        <v>0.9757872258787043</v>
+        <v>1.091729446652716</v>
       </c>
       <c r="H7">
-        <v>-0.011792460556177211</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>-0.016526036745515102</v>
+      </c>
+      <c r="I7">
+        <v>-0.0932971365782338</v>
+      </c>
+      <c r="J7">
+        <v>-0.00027325435504208656</v>
+      </c>
+      <c r="K7">
+        <v>0.0</v>
+      </c>
+      <c r="L7">
+        <v>-0.09215724093948963</v>
+      </c>
+      <c r="M7">
+        <v>-0.1696100788728346</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>-0.4890048128818044</v>
+        <v>-0.509228971285405</v>
       </c>
       <c r="C8">
         <v>0.0</v>
       </c>
       <c r="D8">
-        <v>-0.05489221931557406</v>
+        <v>0.03635145783199292</v>
       </c>
       <c r="E8">
-        <v>0.17210057151534616</v>
+        <v>0.25242038313511095</v>
       </c>
       <c r="F8">
-        <v>-5.272072761559501e-17</v>
+        <v>-4.703276363848557e-16</v>
       </c>
       <c r="G8">
         <v>0.0</v>
       </c>
       <c r="H8">
-        <v>-0.011381871558407643</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>-0.015715621463581707</v>
+      </c>
+      <c r="I8">
+        <v>0.013964006958948116</v>
+      </c>
+      <c r="J8">
+        <v>-0.001139895638739962</v>
+      </c>
+      <c r="K8">
+        <v>0.0</v>
+      </c>
+      <c r="L8">
+        <v>0.015643545819300775</v>
+      </c>
+      <c r="M8">
+        <v>-0.11178954420434453</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>-0.21605645540033253</v>
+        <v>-0.1920202389789131</v>
       </c>
       <c r="C9">
         <v>0.0</v>
       </c>
       <c r="D9">
-        <v>0.04426587660423642</v>
+        <v>0.12921754417741121</v>
       </c>
       <c r="E9">
-        <v>0.23371976622355564</v>
+        <v>0.30989248609914577</v>
       </c>
       <c r="F9">
-        <v>-6.739846608045116e-17</v>
+        <v>-4.718786361864179e-16</v>
       </c>
       <c r="G9">
         <v>0.0</v>
       </c>
       <c r="H9">
-        <v>-0.010706021593438059</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>-0.014638909287259121</v>
+      </c>
+      <c r="I9">
+        <v>0.004008917121286593</v>
+      </c>
+      <c r="J9">
+        <v>-0.0016795388603492861</v>
+      </c>
+      <c r="K9">
+        <v>0.0</v>
+      </c>
+      <c r="L9">
+        <v>0.006003706348603366</v>
+      </c>
+      <c r="M9">
+        <v>-0.07009891266633676</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>-0.03715968800662442</v>
+        <v>0.011473420303155235</v>
       </c>
       <c r="C10">
         <v>0.0</v>
       </c>
       <c r="D10">
-        <v>0.023626280180739645</v>
+        <v>0.09281887756465035</v>
       </c>
       <c r="E10">
-        <v>0.1852066757060291</v>
+        <v>0.24713842664744773</v>
       </c>
       <c r="F10">
-        <v>-7.090488236116101e-17</v>
+        <v>-4.584979772835131e-16</v>
       </c>
       <c r="G10">
         <v>0.0</v>
       </c>
       <c r="H10">
-        <v>-0.009893978809767157</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>-0.013449013874046038</v>
+      </c>
+      <c r="I10">
+        <v>-0.011995333145062431</v>
+      </c>
+      <c r="J10">
+        <v>-0.001994789227313812</v>
+      </c>
+      <c r="K10">
+        <v>0.0</v>
+      </c>
+      <c r="L10">
+        <v>-0.009838998123310988</v>
+      </c>
+      <c r="M10">
+        <v>-0.046834972966612855</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.05146770528173952</v>
+        <v>0.10976997965989511</v>
       </c>
       <c r="C11">
         <v>0.0</v>
       </c>
       <c r="D11">
-        <v>-0.0001875083529248034</v>
+        <v>0.0564656832109975</v>
       </c>
       <c r="E11">
-        <v>0.14031947459295552</v>
+        <v>0.1908110132772078</v>
       </c>
       <c r="F11">
-        <v>-6.51884005147327e-17</v>
+        <v>-4.3301173041301315e-16</v>
       </c>
       <c r="G11">
         <v>0.0</v>
       </c>
       <c r="H11">
-        <v>-0.00905805109405701</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>-0.012273975098444636</v>
+      </c>
+      <c r="I11">
+        <v>-0.021669132469103597</v>
+      </c>
+      <c r="J11">
+        <v>-0.002156335021748862</v>
+      </c>
+      <c r="K11">
+        <v>0.0</v>
+      </c>
+      <c r="L11">
+        <v>-0.01946037486783564</v>
+      </c>
+      <c r="M11">
+        <v>-0.034248678595174845</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.08947126149456243</v>
+        <v>0.1495199508970184</v>
       </c>
       <c r="C12">
         <v>0.0</v>
       </c>
       <c r="D12">
-        <v>-0.015194632299564359</v>
+        <v>0.03246778428510973</v>
       </c>
       <c r="E12">
-        <v>0.10918059429850749</v>
+        <v>0.15149212646966237</v>
       </c>
       <c r="F12">
-        <v>-5.200601103324721e-17</v>
+        <v>-3.979416485401561e-16</v>
       </c>
       <c r="G12">
         <v>0.0</v>
       </c>
       <c r="H12">
-        <v>-0.008263755495204507</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>-0.01118589910661117</v>
+      </c>
+      <c r="I12">
+        <v>-0.026691762119215104</v>
+      </c>
+      <c r="J12">
+        <v>-0.0022087576012658813</v>
+      </c>
+      <c r="K12">
+        <v>0.0</v>
+      </c>
+      <c r="L12">
+        <v>-0.02451081846935324</v>
+      </c>
+      <c r="M12">
+        <v>-0.027081759308224672</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.102452975654777</v>
+        <v>0.16049780056471308</v>
       </c>
       <c r="C13">
         <v>0.0</v>
       </c>
       <c r="D13">
-        <v>-0.02388473480957891</v>
+        <v>0.01729056859543368</v>
       </c>
       <c r="E13">
-        <v>0.08801339660840735</v>
+        <v>0.12444684763273535</v>
       </c>
       <c r="F13">
-        <v>-3.2921989892903245e-17</v>
+        <v>-3.5551049288211273e-16</v>
       </c>
       <c r="G13">
         <v>0.0</v>
       </c>
       <c r="H13">
-        <v>-0.0075423214128905545</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>-0.01021669738224655</v>
+      </c>
+      <c r="I13">
+        <v>-0.029211273026468074</v>
+      </c>
+      <c r="J13">
+        <v>-0.0021809436498601426</v>
+      </c>
+      <c r="K13">
+        <v>0.0</v>
+      </c>
+      <c r="L13">
+        <v>-0.027118271261769883</v>
+      </c>
+      <c r="M13">
+        <v>-0.022586538762058614</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.10367093133192853</v>
+        <v>0.15807983378839663</v>
       </c>
       <c r="C14">
         <v>0.0</v>
       </c>
       <c r="D14">
-        <v>-0.02895725146259366</v>
+        <v>0.007412129983506349</v>
       </c>
       <c r="E14">
-        <v>0.0731833336983537</v>
+        <v>0.10527842914313104</v>
       </c>
       <c r="F14">
-        <v>-9.312250802979382e-18</v>
+        <v>-3.076542318857994e-16</v>
       </c>
       <c r="G14">
         <v>0.0</v>
       </c>
       <c r="H14">
-        <v>-0.0069052296085054445</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>-0.009375346955349115</v>
+      </c>
+      <c r="I14">
+        <v>-0.03045424085661229</v>
+      </c>
+      <c r="J14">
+        <v>-0.0020930017646967735</v>
+      </c>
+      <c r="K14">
+        <v>0.0</v>
+      </c>
+      <c r="L14">
+        <v>-0.028494231795550898</v>
+      </c>
+      <c r="M14">
+        <v>-0.01943241063058955</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.09955644604058812</v>
+        <v>0.1497205073739659</v>
       </c>
       <c r="C15">
         <v>0.0</v>
       </c>
       <c r="D15">
-        <v>-0.031975654013133986</v>
+        <v>0.0007360314313030469</v>
       </c>
       <c r="E15">
-        <v>0.06242686887210582</v>
+        <v>0.09123351500585693</v>
       </c>
       <c r="F15">
-        <v>1.7627220165840808e-17</v>
+        <v>-2.560390285301014e-16</v>
       </c>
       <c r="G15">
         <v>0.0</v>
       </c>
       <c r="H15">
-        <v>-0.0063535387702982095</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>-0.008658871647518815</v>
+      </c>
+      <c r="I15">
+        <v>-0.0310153761717772</v>
+      </c>
+      <c r="J15">
+        <v>-0.0019600090610602345</v>
+      </c>
+      <c r="K15">
+        <v>0.0</v>
+      </c>
+      <c r="L15">
+        <v>-0.02922146668359056</v>
+      </c>
+      <c r="M15">
+        <v>-0.01699089675987442</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.09316566426406624</v>
+        <v>0.1389619919126751</v>
       </c>
       <c r="C16">
         <v>0.0</v>
       </c>
       <c r="D16">
-        <v>-0.033746544105549066</v>
+        <v>-0.003889122939751438</v>
       </c>
       <c r="E16">
-        <v>0.05440529875601142</v>
+        <v>0.08065991723176327</v>
       </c>
       <c r="F16">
-        <v>4.686912360866499e-17</v>
+        <v>-2.0208132342173716e-16</v>
       </c>
       <c r="G16">
         <v>0.0</v>
       </c>
       <c r="H16">
-        <v>-0.005883034883141703</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>-0.008058405359832108</v>
+      </c>
+      <c r="I16">
+        <v>-0.031166639886137437</v>
+      </c>
+      <c r="J16">
+        <v>-0.0017939094881857234</v>
+      </c>
+      <c r="K16">
+        <v>0.0</v>
+      </c>
+      <c r="L16">
+        <v>-0.029562167435498554</v>
+      </c>
+      <c r="M16">
+        <v>-0.014965949886056922</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.08594623987111218</v>
+        <v>0.1274809751644383</v>
       </c>
       <c r="C17">
         <v>0.0</v>
       </c>
       <c r="D17">
-        <v>-0.034684331856074974</v>
+        <v>-0.007109862531682359</v>
       </c>
       <c r="E17">
-        <v>0.04829800390868981</v>
+        <v>0.07252762679352115</v>
       </c>
       <c r="F17">
-        <v>7.754182985099447e-17</v>
+        <v>-1.4696966627184697e-16</v>
       </c>
       <c r="G17">
         <v>0.0</v>
       </c>
       <c r="H17">
-        <v>-0.005486957601275591</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>-0.007562411629084261</v>
+      </c>
+      <c r="I17">
+        <v>-0.031031263605579062</v>
+      </c>
+      <c r="J17">
+        <v>-0.0016044724506381431</v>
+      </c>
+      <c r="K17">
+        <v>0.0</v>
+      </c>
+      <c r="L17">
+        <v>-0.02963146289178835</v>
+      </c>
+      <c r="M17">
+        <v>-0.013216045753206389</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.07858684516753045</v>
+        <v>0.11607232508361541</v>
       </c>
       <c r="C18">
         <v>0.0</v>
       </c>
       <c r="D18">
-        <v>-0.03501458328618973</v>
+        <v>-0.00931441898106726</v>
       </c>
       <c r="E18">
-        <v>0.04357036423279956</v>
+        <v>0.0661556808140292</v>
       </c>
       <c r="F18">
-        <v>1.0891540188502129e-16</v>
+        <v>-9.168724583972224e-17</v>
       </c>
       <c r="G18">
         <v>0.0</v>
       </c>
       <c r="H18">
-        <v>-0.005157450582039444</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>-0.007158400918384182</v>
+      </c>
+      <c r="I18">
+        <v>-0.030668314714014204</v>
+      </c>
+      <c r="J18">
+        <v>-0.001399800713790176</v>
+      </c>
+      <c r="K18">
+        <v>0.0</v>
+      </c>
+      <c r="L18">
+        <v>-0.029481687221753414</v>
+      </c>
+      <c r="M18">
+        <v>-0.011670893687095087</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.07141682222775211</v>
+        <v>0.10511209411254013</v>
       </c>
       <c r="C19">
         <v>0.0</v>
       </c>
       <c r="D19">
-        <v>-0.034873669993865056</v>
+        <v>-0.010756344511751635</v>
       </c>
       <c r="E19">
-        <v>0.039853069796671414</v>
+        <v>0.06106905665507224</v>
       </c>
       <c r="F19">
-        <v>1.4038729023343552e-16</v>
+        <v>-3.7034320309053016e-17</v>
       </c>
       <c r="G19">
         <v>0.0</v>
       </c>
       <c r="H19">
-        <v>-0.00488635412461131</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>-0.00683386790670013</v>
+      </c>
+      <c r="I19">
+        <v>-0.030111165452324277</v>
+      </c>
+      <c r="J19">
+        <v>-0.0011866274922603818</v>
+      </c>
+      <c r="K19">
+        <v>0.0</v>
+      </c>
+      <c r="L19">
+        <v>-0.02914065025515533</v>
+      </c>
+      <c r="M19">
+        <v>-0.010292920032365337</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.06459311261489223</v>
+        <v>0.09477441002674511</v>
       </c>
       <c r="C20">
         <v>0.0</v>
       </c>
       <c r="D20">
-        <v>-0.034355238990845194</v>
+        <v>-0.011614831036960739</v>
       </c>
       <c r="E20">
-        <v>0.03687948637375892</v>
+        <v>0.05692335170514526</v>
       </c>
       <c r="F20">
-        <v>1.714681770280525e-16</v>
+        <v>1.6350040134988204e-17</v>
       </c>
       <c r="G20">
         <v>0.0</v>
       </c>
       <c r="H20">
-        <v>-0.0046656525878128055</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>-0.006576814916789152</v>
+      </c>
+      <c r="I20">
+        <v>-0.029384068461090804</v>
+      </c>
+      <c r="J20">
+        <v>-0.0009705151971686997</v>
+      </c>
+      <c r="K20">
+        <v>0.0</v>
+      </c>
+      <c r="L20">
+        <v>-0.02862806138518663</v>
+      </c>
+      <c r="M20">
+        <v>-0.009059586050294492</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.0581879455947522</v>
+        <v>0.08513351486885028</v>
       </c>
       <c r="C21">
         <v>0.0</v>
       </c>
       <c r="D21">
-        <v>-0.03353132816914686</v>
+        <v>-0.012024424659352481</v>
       </c>
       <c r="E21">
-        <v>0.03445175174577457</v>
+        <v>0.05346317943625842</v>
       </c>
       <c r="F21">
-        <v>2.0176831827986297e-16</v>
+        <v>6.796731470489094e-17</v>
       </c>
       <c r="G21">
         <v>0.0</v>
       </c>
       <c r="H21">
-        <v>-0.004487732397470871</v>
+        <v>-0.006376045364124454</v>
+      </c>
+      <c r="I21">
+        <v>-0.02850875233416359</v>
+      </c>
+      <c r="J21">
+        <v>-0.0007560070759040482</v>
+      </c>
+      <c r="K21">
+        <v>0.0</v>
+      </c>
+      <c r="L21">
+        <v>-0.027961997848348297</v>
+      </c>
+      <c r="M21">
+        <v>-0.007955326113146494</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>0.07621238223928459</v>
+      </c>
+      <c r="C22">
+        <v>0.0</v>
+      </c>
+      <c r="D22">
+        <v>-0.012090214066508773</v>
+      </c>
+      <c r="E22">
+        <v>0.05049741171846571</v>
+      </c>
+      <c r="F22">
+        <v>1.1744027465637388e-16</v>
+      </c>
+      <c r="G22">
+        <v>0.0</v>
+      </c>
+      <c r="H22">
+        <v>-0.006221321657146216</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
+  <dimension ref="A1:W21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:23">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" t="s">
+        <v>200</v>
+      </c>
+      <c r="L1" t="s">
+        <v>201</v>
+      </c>
+      <c r="M1" t="s">
+        <v>202</v>
+      </c>
+      <c r="N1" t="s">
+        <v>203</v>
+      </c>
+      <c r="O1" t="s">
+        <v>204</v>
+      </c>
+      <c r="P1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>206</v>
+      </c>
+      <c r="R1" t="s">
+        <v>207</v>
+      </c>
+      <c r="S1" t="s">
+        <v>208</v>
+      </c>
+      <c r="T1" t="s">
+        <v>209</v>
+      </c>
+      <c r="V1" t="s">
+        <v>5</v>
+      </c>
+      <c r="W1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.0</v>
+      </c>
+      <c r="C2">
+        <v>-0.9052392657323787</v>
+      </c>
+      <c r="D2">
+        <v>0.9681399006074287</v>
+      </c>
+      <c r="E2">
+        <v>-1.0</v>
+      </c>
+      <c r="F2">
+        <v>-0.01413114937975354</v>
+      </c>
+      <c r="G2">
+        <v>0.010611389448048958</v>
+      </c>
+      <c r="H2">
+        <v>-4.748347915873213e-15</v>
+      </c>
+      <c r="I2">
+        <v>0.293966292813274</v>
+      </c>
+      <c r="J2">
+        <v>0.0</v>
+      </c>
+      <c r="K2">
+        <v>1.485218579098167e-15</v>
+      </c>
+      <c r="L2">
+        <v>-0.08040185016545286</v>
+      </c>
+      <c r="M2">
+        <v>0.00577910790065508</v>
+      </c>
+      <c r="N2">
+        <v>-1.0</v>
+      </c>
+      <c r="O2">
+        <v>-1.300438309001632</v>
+      </c>
+      <c r="P2">
+        <v>0.01691563407698074</v>
+      </c>
+      <c r="Q2">
+        <v>-3.1764938580195055</v>
+      </c>
+      <c r="R2">
+        <v>-1.0</v>
+      </c>
+      <c r="S2">
+        <v>-1.0</v>
+      </c>
+      <c r="T2">
+        <v>4.5087075869680536e-17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>-0.25661611979210086</v>
+      </c>
+      <c r="C3">
+        <v>-0.9050688766126486</v>
+      </c>
+      <c r="D3">
+        <v>0.661562881766815</v>
+      </c>
+      <c r="E3">
+        <v>-1.0</v>
+      </c>
+      <c r="F3">
+        <v>-0.016915634076980258</v>
+      </c>
+      <c r="G3">
+        <v>-0.03186432239033837</v>
+      </c>
+      <c r="H3">
+        <v>-5.3791489454505824e-15</v>
+      </c>
+      <c r="I3">
+        <v>0.06325583478741865</v>
+      </c>
+      <c r="J3">
+        <v>0.0</v>
+      </c>
+      <c r="K3">
+        <v>1.459966730155892e-15</v>
+      </c>
+      <c r="L3">
+        <v>-0.09476073426764205</v>
+      </c>
+      <c r="M3">
+        <v>0.0064720161883647775</v>
+      </c>
+      <c r="N3">
+        <v>-1.0</v>
+      </c>
+      <c r="O3">
+        <v>-0.4303211772063297</v>
+      </c>
+      <c r="P3">
+        <v>-0.16045476866356317</v>
+      </c>
+      <c r="Q3">
+        <v>-2.3399162031955485</v>
+      </c>
+      <c r="R3">
+        <v>-0.1644474583019147</v>
+      </c>
+      <c r="S3">
+        <v>-0.9999999999999999</v>
+      </c>
+      <c r="T3">
+        <v>-1.2006389061474226e-16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>-0.15033445389395944</v>
+      </c>
+      <c r="C4">
+        <v>-0.9086031713999636</v>
+      </c>
+      <c r="D4">
+        <v>0.38221670065155294</v>
+      </c>
+      <c r="E4">
+        <v>-1.0</v>
+      </c>
+      <c r="F4">
+        <v>-0.01741746642483185</v>
+      </c>
+      <c r="G4">
+        <v>-0.1307158788307793</v>
+      </c>
+      <c r="H4">
+        <v>-5.818305649211937e-15</v>
+      </c>
+      <c r="I4">
+        <v>-0.24234210056676064</v>
+      </c>
+      <c r="J4">
+        <v>0.0</v>
+      </c>
+      <c r="K4">
+        <v>1.4252250825956042e-15</v>
+      </c>
+      <c r="L4">
+        <v>-0.09493112338737889</v>
+      </c>
+      <c r="M4">
+        <v>0.005870605597528342</v>
+      </c>
+      <c r="N4">
+        <v>-1.0</v>
+      </c>
+      <c r="O4">
+        <v>-0.3875986598402924</v>
+      </c>
+      <c r="P4">
+        <v>-0.3962673948995753</v>
+      </c>
+      <c r="Q4">
+        <v>-1.8379967551838206</v>
+      </c>
+      <c r="R4">
+        <v>-0.1817890425383521</v>
+      </c>
+      <c r="S4">
+        <v>-1.0</v>
+      </c>
+      <c r="T4">
+        <v>-2.4823694109419566e-16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>-0.11633708234053922</v>
+      </c>
+      <c r="C5">
+        <v>-0.9135571947895866</v>
+      </c>
+      <c r="D5">
+        <v>0.10240916673370665</v>
+      </c>
+      <c r="E5">
+        <v>-1.0</v>
+      </c>
+      <c r="F5">
+        <v>-0.017374125841632445</v>
+      </c>
+      <c r="G5">
+        <v>-0.2691110903402725</v>
+      </c>
+      <c r="H5">
+        <v>-6.090418604880365e-15</v>
+      </c>
+      <c r="I5">
+        <v>-0.45311682283775634</v>
+      </c>
+      <c r="J5">
+        <v>0.0</v>
+      </c>
+      <c r="K5">
+        <v>1.3831794292525924e-15</v>
+      </c>
+      <c r="L5">
+        <v>-0.09139682860006812</v>
+      </c>
+      <c r="M5">
+        <v>0.0048651298028423995</v>
+      </c>
+      <c r="N5">
+        <v>-1.0000000000000002</v>
+      </c>
+      <c r="O5">
+        <v>-0.24997531697629544</v>
+      </c>
+      <c r="P5">
+        <v>-0.5594916702932204</v>
+      </c>
+      <c r="Q5">
+        <v>-1.505705246087438</v>
+      </c>
+      <c r="R5">
+        <v>-0.08260789907318522</v>
+      </c>
+      <c r="S5">
+        <v>-1.0000000000000002</v>
+      </c>
+      <c r="T5">
+        <v>-3.4343469768482743e-16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>-0.08906487405434146</v>
+      </c>
+      <c r="C6">
+        <v>-0.9192954503986281</v>
+      </c>
+      <c r="D6">
+        <v>-0.135456549530828</v>
+      </c>
+      <c r="E6">
+        <v>-1.0</v>
+      </c>
+      <c r="F6">
+        <v>-0.01707253891919418</v>
+      </c>
+      <c r="G6">
+        <v>-0.3930452374105372</v>
+      </c>
+      <c r="H6">
+        <v>-6.2190208917890676e-15</v>
+      </c>
+      <c r="I6">
+        <v>-0.58858301151456</v>
+      </c>
+      <c r="J6">
+        <v>0.0</v>
+      </c>
+      <c r="K6">
+        <v>1.3357185412306094e-15</v>
+      </c>
+      <c r="L6">
+        <v>-0.08644280521045197</v>
+      </c>
+      <c r="M6">
+        <v>0.0037689465803442124</v>
+      </c>
+      <c r="N6">
+        <v>-0.9999999999999998</v>
+      </c>
+      <c r="O6">
+        <v>-0.15602608614441268</v>
+      </c>
+      <c r="P6">
+        <v>-0.6649870094715363</v>
+      </c>
+      <c r="Q6">
+        <v>-1.2504215444989601</v>
+      </c>
+      <c r="R6">
+        <v>-0.015638695049281635</v>
+      </c>
+      <c r="S6">
+        <v>-1.0</v>
+      </c>
+      <c r="T6">
+        <v>-4.096415612004622e-16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>-0.0662202549382754</v>
+      </c>
+      <c r="C7">
+        <v>-0.9255267684593391</v>
+      </c>
+      <c r="D7">
+        <v>-0.31260461262184863</v>
+      </c>
+      <c r="E7">
+        <v>-1.0</v>
+      </c>
+      <c r="F7">
+        <v>-0.016526036745515102</v>
+      </c>
+      <c r="G7">
+        <v>-0.4759843533789608</v>
+      </c>
+      <c r="H7">
+        <v>-6.2261913106385175e-15</v>
+      </c>
+      <c r="I7">
+        <v>-0.6778753841761269</v>
+      </c>
+      <c r="J7">
+        <v>0.0</v>
+      </c>
+      <c r="K7">
+        <v>1.2844545829858365e-15</v>
+      </c>
+      <c r="L7">
+        <v>-0.08070454960141288</v>
+      </c>
+      <c r="M7">
+        <v>0.002755647131150306</v>
+      </c>
+      <c r="N7">
+        <v>-1.0</v>
+      </c>
+      <c r="O7">
+        <v>-0.0904417367180636</v>
+      </c>
+      <c r="P7">
+        <v>-0.7350899114635326</v>
+      </c>
+      <c r="Q7">
+        <v>-1.01978897436764</v>
+      </c>
+      <c r="R7">
+        <v>0.02876402916085786</v>
+      </c>
+      <c r="S7">
+        <v>-0.9999999999999999</v>
+      </c>
+      <c r="T7">
+        <v>-4.50718655276338e-16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>-0.32142721498078364</v>
+      </c>
+      <c r="C8">
+        <v>1.3414080441414482</v>
+      </c>
+      <c r="D8">
+        <v>-0.4268481637496183</v>
+      </c>
+      <c r="E8">
+        <v>-0.33531927654145866</v>
+      </c>
+      <c r="F8">
+        <v>-0.015715621463581707</v>
+      </c>
+      <c r="G8">
+        <v>-0.509228971285405</v>
+      </c>
+      <c r="H8">
+        <v>-6.132302703677181e-15</v>
+      </c>
+      <c r="I8">
+        <v>-0.07475322826127526</v>
+      </c>
+      <c r="J8">
+        <v>0.0</v>
+      </c>
+      <c r="K8">
+        <v>1.2307465784418506e-15</v>
+      </c>
+      <c r="L8">
+        <v>-0.07447323154070251</v>
+      </c>
+      <c r="M8">
+        <v>0.0019374155489657041</v>
+      </c>
+      <c r="N8">
+        <v>0.03635145783199292</v>
+      </c>
+      <c r="O8">
+        <v>0.6194520057701742</v>
+      </c>
+      <c r="P8">
+        <v>0.25242038313511095</v>
+      </c>
+      <c r="Q8">
+        <v>-0.7834310456132124</v>
+      </c>
+      <c r="R8">
+        <v>1.091729446652716</v>
+      </c>
+      <c r="S8">
+        <v>1.2734464728070378</v>
+      </c>
+      <c r="T8">
+        <v>-4.703276363848557e-16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.0</v>
+      </c>
+      <c r="C9">
+        <v>1.342653275460827</v>
+      </c>
+      <c r="D9">
+        <v>-0.2899290309981144</v>
+      </c>
+      <c r="E9">
+        <v>-0.21682340529141533</v>
+      </c>
+      <c r="F9">
+        <v>-0.014638909287259121</v>
+      </c>
+      <c r="G9">
+        <v>-0.1920202389789131</v>
+      </c>
+      <c r="H9">
+        <v>-5.95587947588401e-15</v>
+      </c>
+      <c r="I9">
+        <v>-0.0003884190598680559</v>
+      </c>
+      <c r="J9">
+        <v>0.0</v>
+      </c>
+      <c r="K9">
+        <v>1.1757253026558572e-15</v>
+      </c>
+      <c r="L9">
+        <v>-0.06796157133445065</v>
+      </c>
+      <c r="M9">
+        <v>0.0013812611296645967</v>
+      </c>
+      <c r="N9">
+        <v>0.12921754417741121</v>
+      </c>
+      <c r="O9">
+        <v>0.0</v>
+      </c>
+      <c r="P9">
+        <v>0.30989248609914577</v>
+      </c>
+      <c r="Q9">
+        <v>0.1338662711154739</v>
+      </c>
+      <c r="R9">
+        <v>0.0</v>
+      </c>
+      <c r="S9">
+        <v>1.2810045803204857</v>
+      </c>
+      <c r="T9">
+        <v>-4.718786361864179e-16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.0</v>
+      </c>
+      <c r="C10">
+        <v>1.086818092717859</v>
+      </c>
+      <c r="D10">
+        <v>-0.1866280114390827</v>
+      </c>
+      <c r="E10">
+        <v>-0.18902929303563276</v>
+      </c>
+      <c r="F10">
+        <v>-0.013449013874046038</v>
+      </c>
+      <c r="G10">
+        <v>0.011473420303155235</v>
+      </c>
+      <c r="H10">
+        <v>-5.713541401188098e-15</v>
+      </c>
+      <c r="I10">
+        <v>-0.005133512329801582</v>
+      </c>
+      <c r="J10">
+        <v>0.0</v>
+      </c>
+      <c r="K10">
+        <v>1.1203183827245261e-15</v>
+      </c>
+      <c r="L10">
+        <v>-0.06164869514037899</v>
+      </c>
+      <c r="M10">
+        <v>0.0010320168600286752</v>
+      </c>
+      <c r="N10">
+        <v>0.09281887756465035</v>
+      </c>
+      <c r="O10">
+        <v>0.0</v>
+      </c>
+      <c r="P10">
+        <v>0.24713842664744773</v>
+      </c>
+      <c r="Q10">
+        <v>0.6708481598313336</v>
+      </c>
+      <c r="R10">
+        <v>0.0</v>
+      </c>
+      <c r="S10">
+        <v>1.030942153310926</v>
+      </c>
+      <c r="T10">
+        <v>-4.584979772835131e-16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.0</v>
+      </c>
+      <c r="C11">
+        <v>0.8753826214960259</v>
+      </c>
+      <c r="D11">
+        <v>-0.12771769960939094</v>
+      </c>
+      <c r="E11">
+        <v>-0.17430464489742342</v>
+      </c>
+      <c r="F11">
+        <v>-0.012273975098444636</v>
+      </c>
+      <c r="G11">
+        <v>0.10976997965989511</v>
+      </c>
+      <c r="H11">
+        <v>-5.420013811365651e-15</v>
+      </c>
+      <c r="I11">
+        <v>-0.01486052308658145</v>
+      </c>
+      <c r="J11">
+        <v>0.0</v>
+      </c>
+      <c r="K11">
+        <v>1.065274741776018e-15</v>
+      </c>
+      <c r="L11">
+        <v>-0.055875939406966856</v>
+      </c>
+      <c r="M11">
+        <v>0.0008257253275572897</v>
+      </c>
+      <c r="N11">
+        <v>0.0564656832109975</v>
+      </c>
+      <c r="O11">
+        <v>0.0</v>
+      </c>
+      <c r="P11">
+        <v>0.1908110132772078</v>
+      </c>
+      <c r="Q11">
+        <v>0.900240675818676</v>
+      </c>
+      <c r="R11">
+        <v>0.0</v>
+      </c>
+      <c r="S11">
+        <v>0.8245778752789112</v>
+      </c>
+      <c r="T11">
+        <v>-4.3301173041301315e-16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.0</v>
+      </c>
+      <c r="C12">
+        <v>0.7251580193976521</v>
+      </c>
+      <c r="D12">
+        <v>-0.09508155121341409</v>
+      </c>
+      <c r="E12">
+        <v>-0.16167964518980515</v>
+      </c>
+      <c r="F12">
+        <v>-0.01118589910661117</v>
+      </c>
+      <c r="G12">
+        <v>0.1495199508970184</v>
+      </c>
+      <c r="H12">
+        <v>-5.0881872199663204e-15</v>
+      </c>
+      <c r="I12">
+        <v>-0.020859084333534228</v>
+      </c>
+      <c r="J12">
+        <v>0.0</v>
+      </c>
+      <c r="K12">
+        <v>1.0111877997415131e-15</v>
+      </c>
+      <c r="L12">
+        <v>-0.05080474621714511</v>
+      </c>
+      <c r="M12">
+        <v>0.0007171203238718381</v>
+      </c>
+      <c r="N12">
+        <v>0.03246778428510973</v>
+      </c>
+      <c r="O12">
+        <v>0.0</v>
+      </c>
+      <c r="P12">
+        <v>0.15149212646966237</v>
+      </c>
+      <c r="Q12">
+        <v>0.9636687953744474</v>
+      </c>
+      <c r="R12">
+        <v>0.0</v>
+      </c>
+      <c r="S12">
+        <v>0.6786817445489453</v>
+      </c>
+      <c r="T12">
+        <v>-3.979416485401561e-16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.0</v>
+      </c>
+      <c r="C13">
+        <v>0.6184168634141056</v>
+      </c>
+      <c r="D13">
+        <v>-0.07594118759622955</v>
+      </c>
+      <c r="E13">
+        <v>-0.15043234364362912</v>
+      </c>
+      <c r="F13">
+        <v>-0.01021669738224655</v>
+      </c>
+      <c r="G13">
+        <v>0.16049780056471308</v>
+      </c>
+      <c r="H13">
+        <v>-4.72921222665598e-15</v>
+      </c>
+      <c r="I13">
+        <v>-0.023960668606128846</v>
+      </c>
+      <c r="J13">
+        <v>0.0</v>
+      </c>
+      <c r="K13">
+        <v>9.585170600904135e-16</v>
+      </c>
+      <c r="L13">
+        <v>-0.04647627484873401</v>
+      </c>
+      <c r="M13">
+        <v>0.0006770687568986135</v>
+      </c>
+      <c r="N13">
+        <v>0.01729056859543368</v>
+      </c>
+      <c r="O13">
+        <v>0.0</v>
+      </c>
+      <c r="P13">
+        <v>0.12444684763273535</v>
+      </c>
+      <c r="Q13">
+        <v>0.947477959475338</v>
+      </c>
+      <c r="R13">
+        <v>0.0</v>
+      </c>
+      <c r="S13">
+        <v>0.5755513070359216</v>
+      </c>
+      <c r="T13">
+        <v>-3.5551049288211273e-16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>0.0</v>
+      </c>
+      <c r="C14">
+        <v>0.5404283904458609</v>
+      </c>
+      <c r="D14">
+        <v>-0.0635486380644424</v>
+      </c>
+      <c r="E14">
+        <v>-0.14073440612023572</v>
+      </c>
+      <c r="F14">
+        <v>-0.009375346955349115</v>
+      </c>
+      <c r="G14">
+        <v>0.15807983378839663</v>
+      </c>
+      <c r="H14">
+        <v>-4.352618103282998e-15</v>
+      </c>
+      <c r="I14">
+        <v>-0.025457289392786728</v>
+      </c>
+      <c r="J14">
+        <v>0.0</v>
+      </c>
+      <c r="K14">
+        <v>9.0760787360947e-16</v>
+      </c>
+      <c r="L14">
+        <v>-0.04286555637820762</v>
+      </c>
+      <c r="M14">
+        <v>0.000686394931765014</v>
+      </c>
+      <c r="N14">
+        <v>0.007412129983506349</v>
+      </c>
+      <c r="O14">
+        <v>0.0</v>
+      </c>
+      <c r="P14">
+        <v>0.10527842914313104</v>
+      </c>
+      <c r="Q14">
+        <v>0.8957636284726316</v>
+      </c>
+      <c r="R14">
+        <v>0.0</v>
+      </c>
+      <c r="S14">
+        <v>0.5005134811262363</v>
+      </c>
+      <c r="T14">
+        <v>-3.076542318857994e-16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>0.0</v>
+      </c>
+      <c r="C15">
+        <v>0.4817982033686391</v>
+      </c>
+      <c r="D15">
+        <v>-0.054617087271392264</v>
+      </c>
+      <c r="E15">
+        <v>-0.13251129629382138</v>
+      </c>
+      <c r="F15">
+        <v>-0.008658871647518815</v>
+      </c>
+      <c r="G15">
+        <v>0.1497205073739659</v>
+      </c>
+      <c r="H15">
+        <v>-3.966445739574202e-15</v>
+      </c>
+      <c r="I15">
+        <v>-0.026107079521606846</v>
+      </c>
+      <c r="J15">
+        <v>0.0</v>
+      </c>
+      <c r="K15">
+        <v>8.58709289444294e-16</v>
+      </c>
+      <c r="L15">
+        <v>-0.03991490931964535</v>
+      </c>
+      <c r="M15">
+        <v>0.0007316394567861879</v>
+      </c>
+      <c r="N15">
+        <v>0.0007360314313030469</v>
+      </c>
+      <c r="O15">
+        <v>0.0</v>
+      </c>
+      <c r="P15">
+        <v>0.09123351500585693</v>
+      </c>
+      <c r="Q15">
+        <v>0.8298521301499666</v>
+      </c>
+      <c r="R15">
+        <v>0.0</v>
+      </c>
+      <c r="S15">
+        <v>0.44424580942170055</v>
+      </c>
+      <c r="T15">
+        <v>-2.560390285301014e-16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.0</v>
+      </c>
+      <c r="C16">
+        <v>0.4366238442871805</v>
+      </c>
+      <c r="D16">
+        <v>-0.04758413666166646</v>
+      </c>
+      <c r="E16">
+        <v>-0.12550992997104138</v>
+      </c>
+      <c r="F16">
+        <v>-0.008058405359832108</v>
+      </c>
+      <c r="G16">
+        <v>0.1389619919126751</v>
+      </c>
+      <c r="H16">
+        <v>-3.577387609018251e-15</v>
+      </c>
+      <c r="I16">
+        <v>-0.026285283078346433</v>
+      </c>
+      <c r="J16">
+        <v>0.0</v>
+      </c>
+      <c r="K16">
+        <v>8.119899893854588e-16</v>
+      </c>
+      <c r="L16">
+        <v>-0.0375523939469565</v>
+      </c>
+      <c r="M16">
+        <v>0.000802718696996974</v>
+      </c>
+      <c r="N16">
+        <v>-0.003889122939751438</v>
+      </c>
+      <c r="O16">
+        <v>0.0</v>
+      </c>
+      <c r="P16">
+        <v>0.08065991723176327</v>
+      </c>
+      <c r="Q16">
+        <v>0.7598752475964856</v>
+      </c>
+      <c r="R16">
+        <v>0.0</v>
+      </c>
+      <c r="S16">
+        <v>0.4009221257836246</v>
+      </c>
+      <c r="T16">
+        <v>-2.0208132342173716e-16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>0.0</v>
+      </c>
+      <c r="C17">
+        <v>0.40103636978371526</v>
+      </c>
+      <c r="D17">
+        <v>-0.041706041964552354</v>
+      </c>
+      <c r="E17">
+        <v>-0.11943132506086479</v>
+      </c>
+      <c r="F17">
+        <v>-0.007562411629084261</v>
+      </c>
+      <c r="G17">
+        <v>0.1274809751644383</v>
+      </c>
+      <c r="H17">
+        <v>-3.1909291091707866e-15</v>
+      </c>
+      <c r="I17">
+        <v>-0.02616898444270438</v>
+      </c>
+      <c r="J17">
+        <v>0.0</v>
+      </c>
+      <c r="K17">
+        <v>7.675523614222594e-16</v>
+      </c>
+      <c r="L17">
+        <v>-0.03570171850357122</v>
+      </c>
+      <c r="M17">
+        <v>0.0008917141447645979</v>
+      </c>
+      <c r="N17">
+        <v>-0.007109862531682359</v>
+      </c>
+      <c r="O17">
+        <v>0.0</v>
+      </c>
+      <c r="P17">
+        <v>0.07252762679352115</v>
+      </c>
+      <c r="Q17">
+        <v>0.6906149433032079</v>
+      </c>
+      <c r="R17">
+        <v>0.0</v>
+      </c>
+      <c r="S17">
+        <v>0.36674879385082393</v>
+      </c>
+      <c r="T17">
+        <v>-1.4696966627184697e-16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.0</v>
+      </c>
+      <c r="C18">
+        <v>0.3723706803376171</v>
+      </c>
+      <c r="D18">
+        <v>-0.03662051111390226</v>
+      </c>
+      <c r="E18">
+        <v>-0.11400111332981608</v>
+      </c>
+      <c r="F18">
+        <v>-0.007158400918384182</v>
+      </c>
+      <c r="G18">
+        <v>0.11607232508361541</v>
+      </c>
+      <c r="H18">
+        <v>-2.811487052786614e-15</v>
+      </c>
+      <c r="I18">
+        <v>-0.025843035833772954</v>
+      </c>
+      <c r="J18">
+        <v>0.0</v>
+      </c>
+      <c r="K18">
+        <v>7.254448089823672e-16</v>
+      </c>
+      <c r="L18">
+        <v>-0.03428757593290447</v>
+      </c>
+      <c r="M18">
+        <v>0.0009922425475876132</v>
+      </c>
+      <c r="N18">
+        <v>-0.00931441898106726</v>
+      </c>
+      <c r="O18">
+        <v>0.0</v>
+      </c>
+      <c r="P18">
+        <v>0.0661556808140292</v>
+      </c>
+      <c r="Q18">
+        <v>0.6243059012374765</v>
+      </c>
+      <c r="R18">
+        <v>0.0</v>
+      </c>
+      <c r="S18">
+        <v>0.33913213797309316</v>
+      </c>
+      <c r="T18">
+        <v>-9.168724583972224e-17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.0</v>
+      </c>
+      <c r="C19">
+        <v>0.3487184850955369</v>
+      </c>
+      <c r="D19">
+        <v>-0.032141761034904154</v>
+      </c>
+      <c r="E19">
+        <v>-0.10899552505862764</v>
+      </c>
+      <c r="F19">
+        <v>-0.00683386790670013</v>
+      </c>
+      <c r="G19">
+        <v>0.10511209411254013</v>
+      </c>
+      <c r="H19">
+        <v>-2.442542261379695e-15</v>
+      </c>
+      <c r="I19">
+        <v>-0.025351851210866826</v>
+      </c>
+      <c r="J19">
+        <v>0.0</v>
+      </c>
+      <c r="K19">
+        <v>6.85672417796208e-16</v>
+      </c>
+      <c r="L19">
+        <v>-0.03323854236453495</v>
+      </c>
+      <c r="M19">
+        <v>0.0010991078371503501</v>
+      </c>
+      <c r="N19">
+        <v>-0.010756344511751635</v>
+      </c>
+      <c r="O19">
+        <v>0.0</v>
+      </c>
+      <c r="P19">
+        <v>0.06106905665507224</v>
+      </c>
+      <c r="Q19">
+        <v>0.5619574797877019</v>
+      </c>
+      <c r="R19">
+        <v>0.0</v>
+      </c>
+      <c r="S19">
+        <v>0.3162298539971159</v>
+      </c>
+      <c r="T19">
+        <v>-3.7034320309053016e-17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>0.0</v>
+      </c>
+      <c r="C20">
+        <v>0.3286809863978689</v>
+      </c>
+      <c r="D20">
+        <v>-0.028165670032337484</v>
+      </c>
+      <c r="E20">
+        <v>-0.10424529474024744</v>
+      </c>
+      <c r="F20">
+        <v>-0.006576814916789152</v>
+      </c>
+      <c r="G20">
+        <v>0.09477441002674511</v>
+      </c>
+      <c r="H20">
+        <v>-2.0867641687792137e-15</v>
+      </c>
+      <c r="I20">
+        <v>-0.024723052520219828</v>
+      </c>
+      <c r="J20">
+        <v>0.0</v>
+      </c>
+      <c r="K20">
+        <v>6.482061166984758e-16</v>
+      </c>
+      <c r="L20">
+        <v>-0.032488631098430074</v>
+      </c>
+      <c r="M20">
+        <v>0.0012080873199841746</v>
+      </c>
+      <c r="N20">
+        <v>-0.011614831036960739</v>
+      </c>
+      <c r="O20">
+        <v>0.0</v>
+      </c>
+      <c r="P20">
+        <v>0.05692335170514526</v>
+      </c>
+      <c r="Q20">
+        <v>0.5039768198912442</v>
+      </c>
+      <c r="R20">
+        <v>0.0</v>
+      </c>
+      <c r="S20">
+        <v>0.2967029198221135</v>
+      </c>
+      <c r="T20">
+        <v>1.6350040134988204e-17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.0</v>
+      </c>
+      <c r="C21">
+        <v>0.3112228747784288</v>
+      </c>
+      <c r="D21">
+        <v>-0.024626194880877153</v>
+      </c>
+      <c r="E21">
+        <v>-0.09963034839537782</v>
+      </c>
+      <c r="F21">
+        <v>-0.006376045364124454</v>
+      </c>
+      <c r="G21">
+        <v>0.08513351486885028</v>
+      </c>
+      <c r="H21">
+        <v>-1.7461261073911644e-15</v>
+      </c>
+      <c r="I21">
+        <v>-0.02397770756111911</v>
+      </c>
+      <c r="J21">
+        <v>0.0</v>
+      </c>
+      <c r="K21">
+        <v>6.129904748104142e-16</v>
+      </c>
+      <c r="L21">
+        <v>-0.03197806657576289</v>
+      </c>
+      <c r="M21">
+        <v>0.001315782595724113</v>
+      </c>
+      <c r="N21">
+        <v>-0.012024424659352481</v>
+      </c>
+      <c r="O21">
+        <v>0.0</v>
+      </c>
+      <c r="P21">
+        <v>0.05346317943625842</v>
+      </c>
+      <c r="Q21">
+        <v>0.4504654531108905</v>
+      </c>
+      <c r="R21">
+        <v>0.0</v>
+      </c>
+      <c r="S21">
+        <v>0.2795692939551048</v>
+      </c>
+      <c r="T21">
+        <v>6.796731470489094e-17</v>
       </c>
     </row>
   </sheetData>

--- a/irf/irf/Paper IRFs.xlsx
+++ b/irf/irf/Paper IRFs.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="332">
   <si>
     <t>t</t>
   </si>
@@ -881,6 +881,156 @@
   </si>
   <si>
     <t>2026-03-30T11:36:06.554</t>
+  </si>
+  <si>
+    <t>2026-04-14T02:10:10.983</t>
+  </si>
+  <si>
+    <t>2026-04-14T02:10:17.64</t>
+  </si>
+  <si>
+    <t>2026-04-14T02:10:20.711</t>
+  </si>
+  <si>
+    <t>2026-04-14T02:10:23.804</t>
+  </si>
+  <si>
+    <t>2026-04-14T02:10:27.776</t>
+  </si>
+  <si>
+    <t>2026-04-14T02:10:31.172</t>
+  </si>
+  <si>
+    <t>2026-04-14T02:18:50.253</t>
+  </si>
+  <si>
+    <t>2026-04-14T02:18:55.77</t>
+  </si>
+  <si>
+    <t>2026-04-14T02:18:56.632</t>
+  </si>
+  <si>
+    <t>2026-04-14T02:18:57.474</t>
+  </si>
+  <si>
+    <t>2026-04-14T02:18:59.394</t>
+  </si>
+  <si>
+    <t>2026-04-14T02:19:14.006</t>
+  </si>
+  <si>
+    <t>2026-04-14T02:30:18.697</t>
+  </si>
+  <si>
+    <t>2026-04-14T02:30:24.477</t>
+  </si>
+  <si>
+    <t>2026-04-14T02:30:25.355</t>
+  </si>
+  <si>
+    <t>2026-04-14T02:30:26.696</t>
+  </si>
+  <si>
+    <t>2026-04-14T02:30:28.878</t>
+  </si>
+  <si>
+    <t>2026-04-14T02:30:43.57</t>
+  </si>
+  <si>
+    <t>2026-04-14T09:06:25.014</t>
+  </si>
+  <si>
+    <t>2026-04-14T09:06:30.297</t>
+  </si>
+  <si>
+    <t>2026-04-14T09:06:31.315</t>
+  </si>
+  <si>
+    <t>2026-04-14T09:06:32.278</t>
+  </si>
+  <si>
+    <t>2026-04-14T09:06:34.191</t>
+  </si>
+  <si>
+    <t>2026-04-14T09:06:49.085</t>
+  </si>
+  <si>
+    <t>2026-04-14T09:59:26.383</t>
+  </si>
+  <si>
+    <t>2026-04-14T09:59:27.836</t>
+  </si>
+  <si>
+    <t>2026-04-14T09:59:29.15</t>
+  </si>
+  <si>
+    <t>2026-04-14T09:59:30.292</t>
+  </si>
+  <si>
+    <t>2026-04-14T09:59:31.441</t>
+  </si>
+  <si>
+    <t>2026-04-14T09:59:34.922</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:10:05.385</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:10:12.288</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:19:52.692</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:19:54.907</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:19:56.189</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:19:57.322</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:19:58.267</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:20:01.733</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:22:50.827</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:22:56.645</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:22:57.746</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:22:58.732</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:23:00.924</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:23:16.48</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:55:00.888</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:55:06.947</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:55:08.023</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:55:08.945</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:55:11.106</t>
+  </si>
+  <si>
+    <t>2026-04-14T10:55:26.555</t>
   </si>
 </sst>
 </file>
@@ -3005,7 +3155,7 @@
         <v>5</v>
       </c>
       <c r="W1" t="s">
-        <v>274</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -3037,7 +3187,7 @@
         <v>0.01691563407698074</v>
       </c>
       <c r="J2">
-        <v>-0.08040185016545286</v>
+        <v>-0.3216074006618114</v>
       </c>
       <c r="K2">
         <v>-1.0</v>
@@ -3067,7 +3217,7 @@
         <v>2.2111564327550956e-15</v>
       </c>
       <c r="T2">
-        <v>-0.01413114937975354</v>
+        <v>-0.05652459751901416</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -3099,7 +3249,7 @@
         <v>-0.16045476866356317</v>
       </c>
       <c r="J3">
-        <v>-0.09476073426764205</v>
+        <v>-0.3790429370705682</v>
       </c>
       <c r="K3">
         <v>-0.9999999999999999</v>
@@ -3129,7 +3279,7 @@
         <v>2.6608334657322267e-15</v>
       </c>
       <c r="T3">
-        <v>-0.016915634076980258</v>
+        <v>-0.06766253630792103</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -3161,7 +3311,7 @@
         <v>-0.3962673948995753</v>
       </c>
       <c r="J4">
-        <v>-0.09493112338737889</v>
+        <v>-0.37972449354951554</v>
       </c>
       <c r="K4">
         <v>-1.0</v>
@@ -3191,7 +3341,7 @@
         <v>3.282663855239666e-15</v>
       </c>
       <c r="T4">
-        <v>-0.01741746642483185</v>
+        <v>-0.0696698656993274</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -3223,7 +3373,7 @@
         <v>-0.5594916702932204</v>
       </c>
       <c r="J5">
-        <v>-0.09139682860006812</v>
+        <v>-0.3655873144002725</v>
       </c>
       <c r="K5">
         <v>-1.0000000000000002</v>
@@ -3253,7 +3403,7 @@
         <v>3.849757773399015e-15</v>
       </c>
       <c r="T5">
-        <v>-0.017374125841632445</v>
+        <v>-0.06949650336652978</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -3285,7 +3435,7 @@
         <v>-0.6649870094715363</v>
       </c>
       <c r="J6">
-        <v>-0.08644280521045197</v>
+        <v>-0.3457712208418079</v>
       </c>
       <c r="K6">
         <v>-1.0</v>
@@ -3315,7 +3465,7 @@
         <v>4.367580875500832e-15</v>
       </c>
       <c r="T6">
-        <v>-0.01707253891919418</v>
+        <v>-0.06829015567677672</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -3347,7 +3497,7 @@
         <v>-0.7350899114635326</v>
       </c>
       <c r="J7">
-        <v>-0.08070454960141288</v>
+        <v>-0.3228181984056515</v>
       </c>
       <c r="K7">
         <v>-0.9999999999999999</v>
@@ -3377,7 +3527,7 @@
         <v>4.839569422838582e-15</v>
       </c>
       <c r="T7">
-        <v>-0.016526036745515102</v>
+        <v>-0.06610414698206041</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -3409,7 +3559,7 @@
         <v>0.25242038313511095</v>
       </c>
       <c r="J8">
-        <v>-0.07447323154070251</v>
+        <v>-0.29789292616281005</v>
       </c>
       <c r="K8">
         <v>1.2734464728070378</v>
@@ -3439,7 +3589,7 @@
         <v>4.764069600892054e-15</v>
       </c>
       <c r="T8">
-        <v>-0.015715621463581707</v>
+        <v>-0.06286248585432683</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -3471,7 +3621,7 @@
         <v>0.30989248609914577</v>
       </c>
       <c r="J9">
-        <v>-0.06796157133445065</v>
+        <v>-0.2718462853378026</v>
       </c>
       <c r="K9">
         <v>1.2810045803204857</v>
@@ -3501,7 +3651,7 @@
         <v>4.64532180302989e-15</v>
       </c>
       <c r="T9">
-        <v>-0.014638909287259121</v>
+        <v>-0.058555637149036485</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -3533,7 +3683,7 @@
         <v>0.24713842664744773</v>
       </c>
       <c r="J10">
-        <v>-0.06164869514037899</v>
+        <v>-0.24659478056151596</v>
       </c>
       <c r="K10">
         <v>1.030942153310926</v>
@@ -3563,7 +3713,7 @@
         <v>4.491998523377305e-15</v>
       </c>
       <c r="T10">
-        <v>-0.013449013874046038</v>
+        <v>-0.05379605549618415</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -3595,7 +3745,7 @@
         <v>0.1908110132772078</v>
       </c>
       <c r="J11">
-        <v>-0.055875939406966856</v>
+        <v>-0.22350375762786742</v>
       </c>
       <c r="K11">
         <v>0.8245778752789112</v>
@@ -3625,7 +3775,7 @@
         <v>4.3117861602909845e-15</v>
       </c>
       <c r="T11">
-        <v>-0.012273975098444636</v>
+        <v>-0.04909590039377854</v>
       </c>
     </row>
     <row r="12" spans="1:23">
@@ -3657,7 +3807,7 @@
         <v>0.15149212646966237</v>
       </c>
       <c r="J12">
-        <v>-0.05080474621714511</v>
+        <v>-0.20321898486858045</v>
       </c>
       <c r="K12">
         <v>0.6786817445489453</v>
@@ -3687,7 +3837,7 @@
         <v>4.1114168903484515e-15</v>
       </c>
       <c r="T12">
-        <v>-0.01118589910661117</v>
+        <v>-0.04474359642644468</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -3719,7 +3869,7 @@
         <v>0.12444684763273535</v>
       </c>
       <c r="J13">
-        <v>-0.04647627484873401</v>
+        <v>-0.18590509939493605</v>
       </c>
       <c r="K13">
         <v>0.5755513070359216</v>
@@ -3749,7 +3899,7 @@
         <v>3.896718652643837e-15</v>
       </c>
       <c r="T13">
-        <v>-0.01021669738224655</v>
+        <v>-0.0408667895289862</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -3781,7 +3931,7 @@
         <v>0.10527842914313104</v>
       </c>
       <c r="J14">
-        <v>-0.04286555637820762</v>
+        <v>-0.17146222551283047</v>
       </c>
       <c r="K14">
         <v>0.5005134811262363</v>
@@ -3811,7 +3961,7 @@
         <v>3.672677208093998e-15</v>
       </c>
       <c r="T14">
-        <v>-0.009375346955349115</v>
+        <v>-0.03750138782139646</v>
       </c>
     </row>
     <row r="15" spans="1:23">
@@ -3843,7 +3993,7 @@
         <v>0.09123351500585693</v>
       </c>
       <c r="J15">
-        <v>-0.03991490931964535</v>
+        <v>-0.1596596372785814</v>
       </c>
       <c r="K15">
         <v>0.44424580942170055</v>
@@ -3873,7 +4023,7 @@
         <v>3.4435054511492708e-15</v>
       </c>
       <c r="T15">
-        <v>-0.008658871647518815</v>
+        <v>-0.03463548659007526</v>
       </c>
     </row>
     <row r="16" spans="1:23">
@@ -3905,7 +4055,7 @@
         <v>0.08065991723176327</v>
       </c>
       <c r="J16">
-        <v>-0.0375523939469565</v>
+        <v>-0.150209575787826</v>
       </c>
       <c r="K16">
         <v>0.4009221257836246</v>
@@ -3935,7 +4085,7 @@
         <v>3.2127161953212456e-15</v>
       </c>
       <c r="T16">
-        <v>-0.008058405359832108</v>
+        <v>-0.03223362143932843</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -3967,7 +4117,7 @@
         <v>0.07252762679352115</v>
       </c>
       <c r="J17">
-        <v>-0.03570171850357122</v>
+        <v>-0.14280687401428488</v>
       </c>
       <c r="K17">
         <v>0.36674879385082393</v>
@@ -3997,7 +4147,7 @@
         <v>2.9831955381432905e-15</v>
       </c>
       <c r="T17">
-        <v>-0.007562411629084261</v>
+        <v>-0.030249646516337044</v>
       </c>
     </row>
     <row r="18" spans="1:23">
@@ -4029,7 +4179,7 @@
         <v>0.0661556808140292</v>
       </c>
       <c r="J18">
-        <v>-0.03428757593290447</v>
+        <v>-0.13715030373161788</v>
       </c>
       <c r="K18">
         <v>0.33913213797309316</v>
@@ -4059,7 +4209,7 @@
         <v>2.7572746488062356e-15</v>
       </c>
       <c r="T18">
-        <v>-0.007158400918384182</v>
+        <v>-0.028633603673536727</v>
       </c>
     </row>
     <row r="19" spans="1:23">
@@ -4091,7 +4241,7 @@
         <v>0.06106905665507224</v>
       </c>
       <c r="J19">
-        <v>-0.03323854236453495</v>
+        <v>-0.1329541694581398</v>
       </c>
       <c r="K19">
         <v>0.3162298539971159</v>
@@ -4121,7 +4271,7 @@
         <v>2.5367984281668596e-15</v>
       </c>
       <c r="T19">
-        <v>-0.00683386790670013</v>
+        <v>-0.02733547162680052</v>
       </c>
     </row>
     <row r="20" spans="1:23">
@@ -4153,7 +4303,7 @@
         <v>0.05692335170514526</v>
       </c>
       <c r="J20">
-        <v>-0.032488631098430074</v>
+        <v>-0.1299545243937203</v>
       </c>
       <c r="K20">
         <v>0.2967029198221135</v>
@@ -4183,7 +4333,7 @@
         <v>2.3231899821690162e-15</v>
       </c>
       <c r="T20">
-        <v>-0.006576814916789152</v>
+        <v>-0.026307259667156607</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -4215,7 +4365,7 @@
         <v>0.05346317943625842</v>
       </c>
       <c r="J21">
-        <v>-0.03197806657576289</v>
+        <v>-0.12791226630305155</v>
       </c>
       <c r="K21">
         <v>0.2795692939551048</v>
@@ -4245,7 +4395,7 @@
         <v>2.117510241676413e-15</v>
       </c>
       <c r="T21">
-        <v>-0.006376045364124454</v>
+        <v>-0.025504181456497816</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -6093,7 +6243,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>281</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -6655,7 +6805,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>270</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -7246,7 +7396,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>273</v>
+        <v>329</v>
       </c>
       <c r="L1" t="s">
         <v>163</v>

--- a/irf/irf/Paper IRFs.xlsx
+++ b/irf/irf/Paper IRFs.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="368">
   <si>
     <t>t</t>
   </si>
@@ -1031,6 +1031,114 @@
   </si>
   <si>
     <t>2026-04-14T10:55:26.555</t>
+  </si>
+  <si>
+    <t>2026-04-14T11:59:14.519</t>
+  </si>
+  <si>
+    <t>2026-04-14T11:59:20.125</t>
+  </si>
+  <si>
+    <t>2026-04-14T11:59:23.861</t>
+  </si>
+  <si>
+    <t>2026-04-14T11:59:27.342</t>
+  </si>
+  <si>
+    <t>2026-04-14T11:59:30.857</t>
+  </si>
+  <si>
+    <t>2026-04-14T11:59:34.39</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:00:34.765</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:00:36.453</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:00:37.658</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:00:38.752</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:00:39.638</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:00:43.021</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:16:48.605</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:16:55.076</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:16:56.174</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:16:57.2</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:16:59.497</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:17:16.214</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:25:32.521</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:25:34.131</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:25:35.237</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:25:36.232</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:25:37.041</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:25:40.9</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:31:14.111</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:31:15.741</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:31:17.053</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:31:18.199</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:31:19.135</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:31:22.585</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:31:38.622</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:31:40.073</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:31:41.299</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:31:42.387</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:31:43.249</t>
+  </si>
+  <si>
+    <t>2026-04-14T12:31:46.589</t>
   </si>
 </sst>
 </file>
@@ -3155,7 +3263,7 @@
         <v>5</v>
       </c>
       <c r="W1" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -6243,7 +6351,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -6805,7 +6913,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>326</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -7396,7 +7504,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>329</v>
+        <v>365</v>
       </c>
       <c r="L1" t="s">
         <v>163</v>

--- a/irf/irf/Paper IRFs.xlsx
+++ b/irf/irf/Paper IRFs.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="404">
   <si>
     <t>t</t>
   </si>
@@ -1139,6 +1139,114 @@
   </si>
   <si>
     <t>2026-04-14T12:31:46.589</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:30:23.897</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:30:27.787</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:30:28.625</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:30:29.361</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:30:31.049</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:30:44.895</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:32:20.433</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:32:39.408</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:32:40.439</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:32:41.267</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:33:37.085</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:33:38.18</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:33:39.282</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:33:40.222</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:40:51.774</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:40:53.698</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:40:54.868</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:40:55.881</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:40:57.63</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:51:28.728</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:51:29.893</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:51:30.622</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:51:31.297</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:51:31.844</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:51:34.888</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:51:38.005</t>
+  </si>
+  <si>
+    <t>2026-04-20T13:58:33.816</t>
+  </si>
+  <si>
+    <t>2026-04-20T14:04:39.798</t>
+  </si>
+  <si>
+    <t>2026-04-20T14:04:41.246</t>
+  </si>
+  <si>
+    <t>2026-04-20T14:04:42.147</t>
+  </si>
+  <si>
+    <t>2026-04-20T14:04:42.977</t>
+  </si>
+  <si>
+    <t>2026-04-20T14:04:43.981</t>
+  </si>
+  <si>
+    <t>2026-04-20T14:04:47.25</t>
+  </si>
+  <si>
+    <t>2026-04-20T14:04:50.483</t>
+  </si>
+  <si>
+    <t>2026-04-20T17:26:57.816</t>
+  </si>
+  <si>
+    <t>2026-04-20T17:29:01.142</t>
   </si>
 </sst>
 </file>
@@ -3263,7 +3371,7 @@
         <v>5</v>
       </c>
       <c r="W1" t="s">
-        <v>366</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -6351,7 +6459,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>367</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -6515,25 +6623,25 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0.0</v>
+        <v>-0.9958730269125541</v>
       </c>
       <c r="C8">
         <v>0.0</v>
       </c>
       <c r="D8">
-        <v>0.05430946582074303</v>
+        <v>-0.5866107928575495</v>
       </c>
       <c r="E8">
-        <v>0.5955077290089377</v>
+        <v>-0.6186637106485435</v>
       </c>
       <c r="F8">
-        <v>0.10761627645382683</v>
+        <v>0.0</v>
       </c>
       <c r="G8">
-        <v>0.11295997038794492</v>
+        <v>-0.24825380861455953</v>
       </c>
       <c r="H8">
-        <v>-0.18876390832992718</v>
+        <v>-0.7478901386079544</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -6541,25 +6649,25 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0.0</v>
+        <v>-0.9893436474399769</v>
       </c>
       <c r="C9">
         <v>0.0</v>
       </c>
       <c r="D9">
-        <v>0.04461029027889063</v>
+        <v>-0.5765181469087142</v>
       </c>
       <c r="E9">
-        <v>0.014798565807075535</v>
+        <v>-0.6124770735420583</v>
       </c>
       <c r="F9">
-        <v>-0.05094247202841195</v>
+        <v>0.0</v>
       </c>
       <c r="G9">
-        <v>0.01777562068919533</v>
+        <v>-0.24798288830460627</v>
       </c>
       <c r="H9">
-        <v>0.001799603566086494</v>
+        <v>-0.7417068308544201</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -6567,25 +6675,25 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0.0</v>
+        <v>-0.9813873499246519</v>
       </c>
       <c r="C10">
         <v>0.0</v>
       </c>
       <c r="D10">
-        <v>0.04023509098759547</v>
+        <v>-0.5658605984050505</v>
       </c>
       <c r="E10">
-        <v>0.011620584958082124</v>
+        <v>-0.6063523028066381</v>
       </c>
       <c r="F10">
-        <v>-0.00026855910909260466</v>
+        <v>0.0</v>
       </c>
       <c r="G10">
-        <v>-0.002701021584600503</v>
+        <v>-0.2476368165855634</v>
       </c>
       <c r="H10">
-        <v>0.006795764727261841</v>
+        <v>-0.7341352632659007</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -6593,25 +6701,25 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0.0</v>
+        <v>-0.9725820907630567</v>
       </c>
       <c r="C11">
         <v>0.0</v>
       </c>
       <c r="D11">
-        <v>0.0374521315957541</v>
+        <v>-0.554965128543292</v>
       </c>
       <c r="E11">
-        <v>0.0073251223202478195</v>
+        <v>-0.6002887797785719</v>
       </c>
       <c r="F11">
-        <v>-0.0003704221983866593</v>
+        <v>0.0</v>
       </c>
       <c r="G11">
-        <v>-0.008039085965597648</v>
+        <v>-0.24725208665875784</v>
       </c>
       <c r="H11">
-        <v>0.009001503908673051</v>
+        <v>-0.7257456000448612</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -6619,25 +6727,25 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0.0</v>
+        <v>-0.9632904630745115</v>
       </c>
       <c r="C12">
         <v>0.0</v>
       </c>
       <c r="D12">
-        <v>0.03537776930919301</v>
+        <v>-0.544030514366866</v>
       </c>
       <c r="E12">
-        <v>0.00399912698299723</v>
+        <v>-0.5942858919807864</v>
       </c>
       <c r="F12">
-        <v>-0.0002883021280007282</v>
+        <v>0.0</v>
       </c>
       <c r="G12">
-        <v>-0.009969189323753357</v>
+        <v>-0.24683649071820193</v>
       </c>
       <c r="H12">
-        <v>0.010227436034322045</v>
+        <v>-0.7168989812888351</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -6645,25 +6753,25 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>-2.168404344971009e-19</v>
+        <v>-0.9537512735010617</v>
       </c>
       <c r="C13">
         <v>0.0</v>
       </c>
       <c r="D13">
-        <v>0.033723609910747104</v>
+        <v>-0.5331846605155302</v>
       </c>
       <c r="E13">
-        <v>0.0017396134227807057</v>
+        <v>-0.5883430330609787</v>
       </c>
       <c r="F13">
-        <v>-0.0001967240511480421</v>
+        <v>0.0</v>
       </c>
       <c r="G13">
-        <v>-0.010887739849668903</v>
+        <v>-0.24639148178568276</v>
       </c>
       <c r="H13">
-        <v>0.010935576880075447</v>
+        <v>-0.7078342879826931</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -6671,25 +6779,25 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0.0</v>
+        <v>-0.944126764832759</v>
       </c>
       <c r="C14">
         <v>0.0</v>
       </c>
       <c r="D14">
-        <v>0.03234838012833448</v>
+        <v>-0.5225129094914045</v>
       </c>
       <c r="E14">
-        <v>0.00033011483787131996</v>
+        <v>-0.5824596027303691</v>
       </c>
       <c r="F14">
-        <v>-0.00012338692650097345</v>
+        <v>0.0</v>
       </c>
       <c r="G14">
-        <v>-0.011349724808897944</v>
+        <v>-0.24591698551837507</v>
       </c>
       <c r="H14">
-        <v>0.011300181029315418</v>
+        <v>-0.6987142511861258</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -6697,25 +6805,25 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>0.0</v>
+        <v>-0.9345284645124325</v>
       </c>
       <c r="C15">
         <v>0.0</v>
       </c>
       <c r="D15">
-        <v>0.031163015963138807</v>
+        <v>-0.5120728859064029</v>
       </c>
       <c r="E15">
-        <v>-0.00045021286855274765</v>
+        <v>-0.5766350067030657</v>
       </c>
       <c r="F15">
-        <v>-6.887059121252602e-5</v>
+        <v>0.0</v>
       </c>
       <c r="G15">
-        <v>-0.01153134500686401</v>
+        <v>-0.24541251364663957</v>
       </c>
       <c r="H15">
-        <v>0.011419763887938784</v>
+        <v>-0.6896509915808791</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -6723,25 +6831,25 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>0.0</v>
+        <v>-0.9250325002723385</v>
       </c>
       <c r="C16">
         <v>0.0</v>
       </c>
       <c r="D16">
-        <v>0.030106257729127735</v>
+        <v>-0.5019029430779196</v>
       </c>
       <c r="E16">
-        <v>-0.0007795040050729072</v>
+        <v>-0.5708686566360353</v>
       </c>
       <c r="F16">
-        <v>-2.9585268713728415e-5</v>
+        <v>0.0</v>
       </c>
       <c r="G16">
-        <v>-0.01151906677284669</v>
+        <v>-0.24487747293155987</v>
       </c>
       <c r="H16">
-        <v>0.011362816898953416</v>
+        <v>-0.680721218312466</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -6749,25 +6857,25 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>3.3881317890172014e-21</v>
+        <v>-0.9156894500187448</v>
       </c>
       <c r="C17">
         <v>0.0</v>
       </c>
       <c r="D17">
-        <v>0.029135370774065753</v>
+        <v>-0.4920274284952785</v>
       </c>
       <c r="E17">
-        <v>-0.0007940943470241392</v>
+        <v>-0.5651599700696751</v>
       </c>
       <c r="F17">
-        <v>-1.984094979805785e-6</v>
+        <v>0.0</v>
       </c>
       <c r="G17">
-        <v>-0.011369476509090388</v>
+        <v>-0.24431128195987886</v>
       </c>
       <c r="H17">
-        <v>0.011180182428426402</v>
+        <v>-0.6719760198082324</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -6775,25 +6883,25 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>2.710505431213761e-20</v>
+        <v>-0.9065311338491762</v>
       </c>
       <c r="C18">
         <v>0.0</v>
       </c>
       <c r="D18">
-        <v>0.02822089803791056</v>
+        <v>-0.4824602539420317</v>
       </c>
       <c r="E18">
-        <v>-0.000596486093397393</v>
+        <v>-0.5595083703689785</v>
       </c>
       <c r="F18">
-        <v>1.6810879433808528e-5</v>
+        <v>0.0</v>
       </c>
       <c r="G18">
-        <v>-0.011123756751115134</v>
+        <v>-0.2437134302105187</v>
       </c>
       <c r="H18">
-        <v>0.010910162658695524</v>
+        <v>-0.6634476216645744</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -6801,25 +6909,25 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>0.0</v>
+        <v>-0.8975755388716936</v>
       </c>
       <c r="C19">
         <v>0.0</v>
       </c>
       <c r="D19">
-        <v>0.02734303434734894</v>
+        <v>-0.47320747818397885</v>
       </c>
       <c r="E19">
-        <v>-0.0002629184194522731</v>
+        <v>-0.553913286665289</v>
       </c>
       <c r="F19">
-        <v>2.9036587207160657e-5</v>
+        <v>0.0</v>
       </c>
       <c r="G19">
-        <v>-0.010812701421975254</v>
+        <v>-0.24308351218460802</v>
       </c>
       <c r="H19">
-        <v>0.010581607058097325</v>
+        <v>-0.6551542920219513</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -6827,25 +6935,25 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>0.0</v>
+        <v>-0.8888305041511774</v>
       </c>
       <c r="C20">
         <v>0.0</v>
       </c>
       <c r="D20">
-        <v>0.026488958211201827</v>
+        <v>-0.46426925740083674</v>
       </c>
       <c r="E20">
-        <v>0.00015050757965148163</v>
+        <v>-0.5483741537986364</v>
       </c>
       <c r="F20">
-        <v>3.641036360737823e-5</v>
+        <v>0.0</v>
       </c>
       <c r="G20">
-        <v>-0.010459395758219208</v>
+        <v>-0.2424212468497485</v>
       </c>
       <c r="H20">
-        <v>0.010216134446380577</v>
+        <v>-0.6471040170938326</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -6853,25 +6961,25 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>0.0</v>
+        <v>-0.8802965249783314</v>
       </c>
       <c r="C21">
         <v>0.0</v>
       </c>
       <c r="D21">
-        <v>0.025650841016062707</v>
+        <v>-0.45564135543590795</v>
       </c>
       <c r="E21">
-        <v>0.000603046136270709</v>
+        <v>-0.54289041226065</v>
       </c>
       <c r="F21">
-        <v>4.024348083985214e-5</v>
+        <v>0.0</v>
       </c>
       <c r="G21">
-        <v>-0.010081057297520044</v>
+        <v>-0.24172648705735095</v>
       </c>
       <c r="H21">
-        <v>0.009829820315255597</v>
+        <v>-0.6392973031690994</v>
       </c>
     </row>
   </sheetData>
@@ -6913,7 +7021,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>362</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -7504,7 +7612,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>365</v>
+        <v>398</v>
       </c>
       <c r="L1" t="s">
         <v>163</v>

--- a/irf/irf/Paper IRFs.xlsx
+++ b/irf/irf/Paper IRFs.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="425">
   <si>
     <t>t</t>
   </si>
@@ -1247,6 +1247,69 @@
   </si>
   <si>
     <t>2026-04-20T17:29:01.142</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:21:38.785</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:21:43.994</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:21:45.008</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:21:45.954</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:21:47.68</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:21:54.791</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:21:58.443</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:36:48.938</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:36:53.714</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:36:54.577</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:36:55.324</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:36:57.045</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:37:07.914</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:37:17.177</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:49:52.318</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:49:57.115</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:49:57.913</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:49:58.613</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:50:00.184</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:50:12.908</t>
+  </si>
+  <si>
+    <t>2026-04-23T18:50:22.024</t>
   </si>
 </sst>
 </file>
@@ -3371,7 +3434,7 @@
         <v>5</v>
       </c>
       <c r="W1" t="s">
-        <v>399</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -6459,7 +6522,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -7021,7 +7084,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>395</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -7612,7 +7675,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="L1" t="s">
         <v>163</v>

--- a/irf/irf/Paper IRFs.xlsx
+++ b/irf/irf/Paper IRFs.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="432">
   <si>
     <t>t</t>
   </si>
@@ -1310,6 +1310,27 @@
   </si>
   <si>
     <t>2026-04-23T18:50:22.024</t>
+  </si>
+  <si>
+    <t>2026-06-30T22:34:40.907</t>
+  </si>
+  <si>
+    <t>2026-06-30T22:34:46.854</t>
+  </si>
+  <si>
+    <t>2026-06-30T22:34:48.095</t>
+  </si>
+  <si>
+    <t>2026-06-30T22:34:48.904</t>
+  </si>
+  <si>
+    <t>2026-06-30T22:34:50.845</t>
+  </si>
+  <si>
+    <t>2026-06-30T22:35:05.44</t>
+  </si>
+  <si>
+    <t>2026-06-30T22:35:15.283</t>
   </si>
 </sst>
 </file>
@@ -3434,7 +3455,7 @@
         <v>5</v>
       </c>
       <c r="W1" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -6522,7 +6543,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -7084,7 +7105,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -7675,7 +7696,7 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="L1" t="s">
         <v>163</v>
